--- a/database.xlsx
+++ b/database.xlsx
@@ -1,58 +1,595 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <workbookPr codeName="ThisWorkbook"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7730575-770B-4A2C-9CC4-42ADDB3396FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-25800" yWindow="1548" windowWidth="23016" windowHeight="13656" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet name="DB" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="165">
+  <si>
+    <t>425-81-02924</t>
+  </si>
+  <si>
+    <t>430-81-04069</t>
+  </si>
+  <si>
+    <t>252-88-03722</t>
+  </si>
+  <si>
+    <t>346-88-03537</t>
+  </si>
+  <si>
+    <t>848-87-03604</t>
+  </si>
+  <si>
+    <t>496-88-03415</t>
+  </si>
+  <si>
+    <t>474-81-03532</t>
+  </si>
+  <si>
+    <t>213-86-44710</t>
+  </si>
+  <si>
+    <t>736-81-03575</t>
+  </si>
+  <si>
+    <t>146-86-04102</t>
+  </si>
+  <si>
+    <t>162-86-03269</t>
+  </si>
+  <si>
+    <t>625-87-03506</t>
+  </si>
+  <si>
+    <t>650-86-03238</t>
+  </si>
+  <si>
+    <t>703-81-03202</t>
+  </si>
+  <si>
+    <t>198-87-03270</t>
+  </si>
+  <si>
+    <t>421-87-03199</t>
+  </si>
+  <si>
+    <t>611-84-00095</t>
+  </si>
+  <si>
+    <t>294-88-03051</t>
+  </si>
+  <si>
+    <t>454-86-03998</t>
+  </si>
+  <si>
+    <t>567-88-03298</t>
+  </si>
+  <si>
+    <t>321-86-03228</t>
+  </si>
+  <si>
+    <t>350-81-02222</t>
+  </si>
+  <si>
+    <t>371-88-03697</t>
+  </si>
+  <si>
+    <t>281-81-03982</t>
+  </si>
+  <si>
+    <t>580-81-03875</t>
+  </si>
+  <si>
+    <t>873-81-03383</t>
+  </si>
+  <si>
+    <t>496-87-03645</t>
+  </si>
+  <si>
+    <t>492-87-03094</t>
+  </si>
+  <si>
+    <t>555-88-03733</t>
+  </si>
+  <si>
+    <t>779-88-03213</t>
+  </si>
+  <si>
+    <t>534-88-03774</t>
+  </si>
+  <si>
+    <t>698-81-03690</t>
+  </si>
+  <si>
+    <t>733-87-03530</t>
+  </si>
+  <si>
+    <t>692-86-03597</t>
+  </si>
+  <si>
+    <t>648-81-03297</t>
+  </si>
+  <si>
+    <t>733-87-03471</t>
+  </si>
+  <si>
+    <t>802-03-02536</t>
+  </si>
+  <si>
+    <t>394-81-03798</t>
+  </si>
+  <si>
+    <t>111-46-71007</t>
+  </si>
+  <si>
+    <t>865-88-03232</t>
+  </si>
+  <si>
+    <t>779-87-03803</t>
+  </si>
+  <si>
+    <t>769-87-03903</t>
+  </si>
+  <si>
+    <t>512-86-03917</t>
+  </si>
+  <si>
+    <t>140-88-03341</t>
+  </si>
+  <si>
+    <t>317-81-50111</t>
+  </si>
+  <si>
+    <t>851-81-03966</t>
+  </si>
+  <si>
+    <t>358-87-03440</t>
+  </si>
+  <si>
+    <t>838-88-03695</t>
+  </si>
+  <si>
+    <t>808-86-02949</t>
+  </si>
+  <si>
+    <t>169-81-03246</t>
+  </si>
+  <si>
+    <t>426-88-03376</t>
+  </si>
+  <si>
+    <t>156-86-03565</t>
+  </si>
+  <si>
+    <t>692-86-03659</t>
+  </si>
+  <si>
+    <t>주식회사 케이룽쇼핑</t>
+  </si>
+  <si>
+    <t>회사명</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>통관고유번호</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>케이룽쇼1241011</t>
+  </si>
+  <si>
+    <t>지아무일렉트로닉커머스 유한회사</t>
+  </si>
+  <si>
+    <t>지아무일1261011</t>
+  </si>
+  <si>
+    <t>루아젠트레이딩 유한회사</t>
+  </si>
+  <si>
+    <t>루아젠트1261018</t>
+  </si>
+  <si>
+    <t>유한회사 루미숨</t>
+  </si>
+  <si>
+    <t>루미숨**1251014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">연락처 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>메일주소</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fuyuye92@outlook.kr</t>
+  </si>
+  <si>
+    <t>010-5632-8595</t>
+  </si>
+  <si>
+    <t>대표자</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>FU YUYE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>디앤센슈즈 유한회사</t>
+  </si>
+  <si>
+    <t>디앤센슈1251018</t>
+  </si>
+  <si>
+    <t>유한회사 엘리노스</t>
+  </si>
+  <si>
+    <t>아비오르 유한회사</t>
+  </si>
+  <si>
+    <t>아비오르1251015</t>
+  </si>
+  <si>
+    <t>엘루미스 유한회사</t>
+  </si>
+  <si>
+    <t>엘루미스1251017</t>
+  </si>
+  <si>
+    <t>밍시트레이딩 유한회사</t>
+  </si>
+  <si>
+    <t>위세얼커머스 주식회사</t>
+  </si>
+  <si>
+    <t>위세얼커1251011</t>
+  </si>
+  <si>
+    <t>유한회사 엘에스트레이드</t>
+  </si>
+  <si>
+    <t>엘에스트1242014</t>
+  </si>
+  <si>
+    <t>클리어하우스 유한회사</t>
+  </si>
+  <si>
+    <t>클리어하1251017</t>
+  </si>
+  <si>
+    <t>유한회사 루무라이프</t>
+  </si>
+  <si>
+    <t>루무라이1251011</t>
+  </si>
+  <si>
+    <t>원기화 유한회사</t>
+  </si>
+  <si>
+    <t>원기화**1241016</t>
+  </si>
+  <si>
+    <t>유한회사 장원제이원</t>
+  </si>
+  <si>
+    <t>장원제이1251015</t>
+  </si>
+  <si>
+    <t>(주)키미랭</t>
+  </si>
+  <si>
+    <t>키미랭**1241015</t>
+  </si>
+  <si>
+    <t>하이커우모쥐무역유한회사(영업소)</t>
+  </si>
+  <si>
+    <t>하이커우4241012</t>
+  </si>
+  <si>
+    <t>주식회사 펀드랩스</t>
+  </si>
+  <si>
+    <t>펀드랩스1231013</t>
+  </si>
+  <si>
+    <t>얼라이브마켓 유한회사</t>
+  </si>
+  <si>
+    <t>얼라이브1261017</t>
+  </si>
+  <si>
+    <t>프렌드샵 유한회사</t>
+  </si>
+  <si>
+    <t>프렌드샵1261016</t>
+  </si>
+  <si>
+    <t>수샹 유한회사</t>
+  </si>
+  <si>
+    <t>수샹****1251017</t>
+  </si>
+  <si>
+    <t>주식회사 아이너프</t>
+  </si>
+  <si>
+    <t>아이너프1211019</t>
+  </si>
+  <si>
+    <t>루비나트레이드 유한회사</t>
+  </si>
+  <si>
+    <t>루비나트1261015</t>
+  </si>
+  <si>
+    <t>루밸런스코리아 유한회사</t>
+  </si>
+  <si>
+    <t>루밸런스1261014</t>
+  </si>
+  <si>
+    <t>화션 유한회사</t>
+  </si>
+  <si>
+    <t>화션****1251014</t>
+  </si>
+  <si>
+    <t>주식회사 종해이커머스</t>
+  </si>
+  <si>
+    <t>종해이커1241010</t>
+  </si>
+  <si>
+    <t>주식회사 룸핏</t>
+  </si>
+  <si>
+    <t>룸핏****1251010</t>
+  </si>
+  <si>
+    <t>주식회사 고우젠무역</t>
+  </si>
+  <si>
+    <t>고우젠무1241014</t>
+  </si>
+  <si>
+    <t>클라우드쇼핑이지딜리버리 유한회사</t>
+  </si>
+  <si>
+    <t>클라우드1253019</t>
+  </si>
+  <si>
+    <t>천천무역 유한회사</t>
+  </si>
+  <si>
+    <t>천천무역1241014</t>
+  </si>
+  <si>
+    <t>딩그르 유한회사</t>
+  </si>
+  <si>
+    <t>딩그르**1261010</t>
+  </si>
+  <si>
+    <t>카이라이테크놀로지 유한회사</t>
+  </si>
+  <si>
+    <t>카이라이1251010</t>
+  </si>
+  <si>
+    <t>큐비트레이드 유한회사</t>
+  </si>
+  <si>
+    <t>큐비트레1251015</t>
+  </si>
+  <si>
+    <t>유한회사 스페락스</t>
+  </si>
+  <si>
+    <t>스페락스1241017</t>
+  </si>
+  <si>
+    <t>누리홈 유한회사</t>
+  </si>
+  <si>
+    <t>누리홈**1251015</t>
+  </si>
+  <si>
+    <t>케이엘피</t>
+  </si>
+  <si>
+    <t>케이엘피5231014</t>
+  </si>
+  <si>
+    <t>라이트커머스 유한회사</t>
+  </si>
+  <si>
+    <t>라이트커1251014</t>
+  </si>
+  <si>
+    <t>온리 온라인</t>
+  </si>
+  <si>
+    <t>온리온라5241018</t>
+  </si>
+  <si>
+    <t>정진트레이드 유한회사</t>
+  </si>
+  <si>
+    <t>정진트레1251012</t>
+  </si>
+  <si>
+    <t>하보스 유한회사</t>
+  </si>
+  <si>
+    <t>하보스**1251017</t>
+  </si>
+  <si>
+    <t>원조 유한회사</t>
+  </si>
+  <si>
+    <t>원조****1251016</t>
+  </si>
+  <si>
+    <t>마일후크로스보더이커머스 유한회사</t>
+  </si>
+  <si>
+    <t>마일후크1261018</t>
+  </si>
+  <si>
+    <t>유한회사 순문트레이드</t>
+  </si>
+  <si>
+    <t>순문트레1241010</t>
+  </si>
+  <si>
+    <t>지아무역 주식회사</t>
+  </si>
+  <si>
+    <t>지아무역1231010</t>
+  </si>
+  <si>
+    <t>유한회사 첸양</t>
+  </si>
+  <si>
+    <t>첸양****1261015</t>
+  </si>
+  <si>
+    <t>새톱커머스 주식회사</t>
+  </si>
+  <si>
+    <t>새톱커머1251016</t>
+  </si>
+  <si>
+    <t>제나트 유한회사</t>
+  </si>
+  <si>
+    <t>제나트**1261015</t>
+  </si>
+  <si>
+    <t>우젱무역유한회사</t>
+  </si>
+  <si>
+    <t>우젱무역1241019</t>
+  </si>
+  <si>
+    <t>심해창트레이드 주식회사</t>
+  </si>
+  <si>
+    <t>심해창트1241015</t>
+  </si>
+  <si>
+    <t>올리브티비지니스 유한회사</t>
+  </si>
+  <si>
+    <t>올리브티1251012</t>
+  </si>
+  <si>
+    <t>티엔온 유한회사</t>
+  </si>
+  <si>
+    <t>티엔온**1261014</t>
+  </si>
+  <si>
+    <t>메친트레1251017</t>
+  </si>
+  <si>
+    <t>유한회사 메친트레이딩</t>
+  </si>
+  <si>
+    <t>수정일자</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>사업자 번호</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
-      <sz val="12"/>
+      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -60,18 +597,52 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="FFEEEEEE"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFEEEEEE"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+  <cellXfs count="8">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -396,193 +967,790 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C16"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE6138A4-676B-44A6-82D7-1ADA43310F48}">
+  <dimension ref="A1:G54"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="15.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="24.83203125" customWidth="1"/>
+    <col min="1" max="1" width="14" customWidth="1"/>
+    <col min="2" max="2" width="30.69921875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.8984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.09765625" customWidth="1"/>
+    <col min="5" max="5" width="18.09765625" style="4" customWidth="1"/>
+    <col min="6" max="6" width="19.59765625" style="2" customWidth="1"/>
+    <col min="7" max="7" width="10.8984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>사업자번호</v>
-      </c>
-      <c r="B1" t="str">
-        <v>통관고유번호</v>
-      </c>
-      <c r="C1" t="str">
-        <v>사업자명</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>155-39-01347</v>
-      </c>
-      <c r="B2" t="str">
-        <v/>
-      </c>
-      <c r="C2" t="str">
-        <v>라워스</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>308-86-03448</v>
-      </c>
-      <c r="B3" t="str">
-        <v/>
-      </c>
-      <c r="C3" t="str">
-        <v>주식회사 제이지디글로벌</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>321-86-03228</v>
-      </c>
-      <c r="B4" t="str">
-        <v/>
-      </c>
-      <c r="C4" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>350-81-02222</v>
-      </c>
-      <c r="B5" t="str">
-        <v/>
-      </c>
-      <c r="C5" t="str">
-        <v>주식회사 아이너프</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>527-88-03626</v>
-      </c>
-      <c r="B6" t="str">
-        <v/>
-      </c>
-      <c r="C6" t="str">
-        <v>주식회사 앤드류플래닝컴퍼니</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>580-81-03875</v>
-      </c>
-      <c r="B7" t="str">
-        <v/>
-      </c>
-      <c r="C7" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>589-19-02503</v>
-      </c>
-      <c r="B8" t="str">
-        <v/>
-      </c>
-      <c r="C8" t="str">
-        <v>쓸리보</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>612-88-02231</v>
-      </c>
-      <c r="B9" t="str">
-        <v/>
-      </c>
-      <c r="C9" t="str">
-        <v>주식회사 세한국제인터내셔널</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>625-87-03506</v>
-      </c>
-      <c r="B10" t="str">
-        <v/>
-      </c>
-      <c r="C10" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>697-87-01600</v>
-      </c>
-      <c r="B11" t="str">
-        <v/>
-      </c>
-      <c r="C11" t="str">
-        <v>주식회사 디스이즈</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>731-02-03686</v>
-      </c>
-      <c r="B12" t="str">
-        <v/>
-      </c>
-      <c r="C12" t="str">
-        <v>라비앙하우스</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>775-05-03877</v>
-      </c>
-      <c r="B13" t="str">
-        <v/>
-      </c>
-      <c r="C13" t="str">
-        <v>로비엔트</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>819-08-02465</v>
-      </c>
-      <c r="B14" t="str">
-        <v/>
-      </c>
-      <c r="C14" t="str">
-        <v>스카이미너리즈</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>829-88-03051</v>
-      </c>
-      <c r="B15" t="str">
-        <v/>
-      </c>
-      <c r="C15" t="str">
-        <v>유한회사 엘민커머스(Elmin Commerce Co.,Ltd.)</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>865-88-03232</v>
-      </c>
-      <c r="B16" t="str">
-        <v/>
-      </c>
-      <c r="C16" t="str">
-        <v>정진트레이드 유한회사</v>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A1" t="s">
+        <v>164</v>
+      </c>
+      <c r="B1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D1" t="s">
+        <v>67</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C2" t="s">
+        <v>56</v>
+      </c>
+      <c r="G2" s="7">
+        <v>46203</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s">
+        <v>57</v>
+      </c>
+      <c r="C3" t="s">
+        <v>58</v>
+      </c>
+      <c r="G3" s="7">
+        <v>46203</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A4" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" t="s">
+        <v>59</v>
+      </c>
+      <c r="C4" t="s">
+        <v>60</v>
+      </c>
+      <c r="G4" s="7">
+        <v>46203</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>61</v>
+      </c>
+      <c r="C5" t="s">
+        <v>62</v>
+      </c>
+      <c r="D5" t="s">
+        <v>68</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="G5" s="7">
+        <v>46203</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" t="s">
+        <v>69</v>
+      </c>
+      <c r="C6" t="s">
+        <v>70</v>
+      </c>
+      <c r="G6" s="7">
+        <v>46203</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A7" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" t="s">
+        <v>71</v>
+      </c>
+      <c r="C7" t="s">
+        <v>71</v>
+      </c>
+      <c r="G7" s="7">
+        <v>46203</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A8" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" t="s">
+        <v>76</v>
+      </c>
+      <c r="C8" t="s">
+        <v>76</v>
+      </c>
+      <c r="G8" s="7">
+        <v>46203</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A9" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C9" t="s">
+        <v>73</v>
+      </c>
+      <c r="G9" s="7">
+        <v>46203</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A10" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" t="s">
+        <v>74</v>
+      </c>
+      <c r="C10" t="s">
+        <v>75</v>
+      </c>
+      <c r="G10" s="7">
+        <v>46203</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A11" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11" t="s">
+        <v>77</v>
+      </c>
+      <c r="C11" t="s">
+        <v>78</v>
+      </c>
+      <c r="G11" s="7">
+        <v>46203</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A12" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B12" t="s">
+        <v>79</v>
+      </c>
+      <c r="C12" t="s">
+        <v>80</v>
+      </c>
+      <c r="G12" s="7">
+        <v>46203</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A13" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B13" t="s">
+        <v>81</v>
+      </c>
+      <c r="C13" t="s">
+        <v>82</v>
+      </c>
+      <c r="G13" s="7">
+        <v>46203</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A14" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B14" t="s">
+        <v>83</v>
+      </c>
+      <c r="C14" t="s">
+        <v>84</v>
+      </c>
+      <c r="G14" s="7">
+        <v>46203</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A15" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B15" t="s">
+        <v>85</v>
+      </c>
+      <c r="C15" t="s">
+        <v>86</v>
+      </c>
+      <c r="G15" s="7">
+        <v>46203</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A16" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16" t="s">
+        <v>87</v>
+      </c>
+      <c r="C16" t="s">
+        <v>88</v>
+      </c>
+      <c r="G16" s="7">
+        <v>46203</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A17" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17" t="s">
+        <v>89</v>
+      </c>
+      <c r="C17" t="s">
+        <v>90</v>
+      </c>
+      <c r="G17" s="7">
+        <v>46203</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A18" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B18" t="s">
+        <v>91</v>
+      </c>
+      <c r="C18" t="s">
+        <v>92</v>
+      </c>
+      <c r="G18" s="7">
+        <v>46203</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A19" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B19" t="s">
+        <v>93</v>
+      </c>
+      <c r="C19" t="s">
+        <v>94</v>
+      </c>
+      <c r="G19" s="7">
+        <v>46203</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A20" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B20" t="s">
+        <v>95</v>
+      </c>
+      <c r="C20" t="s">
+        <v>96</v>
+      </c>
+      <c r="G20" s="7">
+        <v>46203</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A21" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B21" t="s">
+        <v>97</v>
+      </c>
+      <c r="C21" t="s">
+        <v>98</v>
+      </c>
+      <c r="G21" s="7">
+        <v>46203</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A22" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B22" t="s">
+        <v>99</v>
+      </c>
+      <c r="C22" t="s">
+        <v>100</v>
+      </c>
+      <c r="G22" s="7">
+        <v>46203</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A23" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B23" t="s">
+        <v>101</v>
+      </c>
+      <c r="C23" t="s">
+        <v>102</v>
+      </c>
+      <c r="G23" s="7">
+        <v>46203</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A24" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B24" t="s">
+        <v>103</v>
+      </c>
+      <c r="C24" t="s">
+        <v>104</v>
+      </c>
+      <c r="G24" s="7">
+        <v>46203</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A25" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B25" t="s">
+        <v>105</v>
+      </c>
+      <c r="C25" t="s">
+        <v>106</v>
+      </c>
+      <c r="G25" s="7">
+        <v>46203</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A26" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B26" t="s">
+        <v>107</v>
+      </c>
+      <c r="C26" t="s">
+        <v>108</v>
+      </c>
+      <c r="G26" s="7">
+        <v>46203</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A27" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B27" t="s">
+        <v>109</v>
+      </c>
+      <c r="C27" t="s">
+        <v>110</v>
+      </c>
+      <c r="G27" s="7">
+        <v>46203</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A28" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B28" t="s">
+        <v>111</v>
+      </c>
+      <c r="C28" t="s">
+        <v>112</v>
+      </c>
+      <c r="G28" s="7">
+        <v>46203</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A29" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B29" t="s">
+        <v>113</v>
+      </c>
+      <c r="C29" t="s">
+        <v>114</v>
+      </c>
+      <c r="G29" s="7">
+        <v>46203</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A30" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B30" t="s">
+        <v>115</v>
+      </c>
+      <c r="C30" t="s">
+        <v>116</v>
+      </c>
+      <c r="G30" s="7">
+        <v>46203</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A31" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B31" t="s">
+        <v>117</v>
+      </c>
+      <c r="C31" t="s">
+        <v>118</v>
+      </c>
+      <c r="G31" s="7">
+        <v>46203</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A32" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B32" t="s">
+        <v>119</v>
+      </c>
+      <c r="C32" t="s">
+        <v>120</v>
+      </c>
+      <c r="G32" s="7">
+        <v>46203</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A33" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B33" t="s">
+        <v>121</v>
+      </c>
+      <c r="C33" t="s">
+        <v>122</v>
+      </c>
+      <c r="G33" s="7">
+        <v>46203</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A34" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B34" t="s">
+        <v>123</v>
+      </c>
+      <c r="C34" t="s">
+        <v>124</v>
+      </c>
+      <c r="G34" s="7">
+        <v>46203</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A35" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G35" s="7">
+        <v>46203</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A36" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B36" t="s">
+        <v>125</v>
+      </c>
+      <c r="C36" t="s">
+        <v>126</v>
+      </c>
+      <c r="G36" s="7">
+        <v>46203</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A37" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B37" t="s">
+        <v>127</v>
+      </c>
+      <c r="C37" t="s">
+        <v>128</v>
+      </c>
+      <c r="G37" s="7">
+        <v>46203</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A38" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B38" t="s">
+        <v>129</v>
+      </c>
+      <c r="C38" t="s">
+        <v>130</v>
+      </c>
+      <c r="G38" s="7">
+        <v>46203</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A39" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B39" t="s">
+        <v>131</v>
+      </c>
+      <c r="C39" t="s">
+        <v>132</v>
+      </c>
+      <c r="G39" s="7">
+        <v>46203</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A40" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B40" t="s">
+        <v>133</v>
+      </c>
+      <c r="C40" t="s">
+        <v>134</v>
+      </c>
+      <c r="G40" s="7">
+        <v>46203</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A41" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B41" t="s">
+        <v>135</v>
+      </c>
+      <c r="C41" t="s">
+        <v>136</v>
+      </c>
+      <c r="G41" s="7">
+        <v>46203</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A42" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B42" t="s">
+        <v>137</v>
+      </c>
+      <c r="C42" t="s">
+        <v>138</v>
+      </c>
+      <c r="G42" s="7">
+        <v>46203</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A43" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B43" t="s">
+        <v>139</v>
+      </c>
+      <c r="C43" t="s">
+        <v>140</v>
+      </c>
+      <c r="G43" s="7">
+        <v>46203</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A44" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B44" t="s">
+        <v>141</v>
+      </c>
+      <c r="C44" t="s">
+        <v>142</v>
+      </c>
+      <c r="G44" s="7">
+        <v>46203</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A45" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B45" t="s">
+        <v>143</v>
+      </c>
+      <c r="C45" t="s">
+        <v>144</v>
+      </c>
+      <c r="G45" s="7">
+        <v>46203</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A46" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B46" t="s">
+        <v>145</v>
+      </c>
+      <c r="C46" t="s">
+        <v>146</v>
+      </c>
+      <c r="G46" s="7">
+        <v>46203</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A47" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B47" t="s">
+        <v>147</v>
+      </c>
+      <c r="C47" t="s">
+        <v>148</v>
+      </c>
+      <c r="G47" s="7">
+        <v>46203</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A48" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="B48" t="s">
+        <v>149</v>
+      </c>
+      <c r="C48" t="s">
+        <v>150</v>
+      </c>
+      <c r="G48" s="7">
+        <v>46203</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A49" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B49" t="s">
+        <v>151</v>
+      </c>
+      <c r="C49" t="s">
+        <v>152</v>
+      </c>
+      <c r="G49" s="7">
+        <v>46203</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A50" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B50" t="s">
+        <v>153</v>
+      </c>
+      <c r="C50" t="s">
+        <v>154</v>
+      </c>
+      <c r="G50" s="7">
+        <v>46203</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A51" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B51" t="s">
+        <v>155</v>
+      </c>
+      <c r="C51" t="s">
+        <v>156</v>
+      </c>
+      <c r="G51" s="7">
+        <v>46203</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A52" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B52" t="s">
+        <v>157</v>
+      </c>
+      <c r="C52" t="s">
+        <v>158</v>
+      </c>
+      <c r="G52" s="7">
+        <v>46203</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A53" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B53" t="s">
+        <v>159</v>
+      </c>
+      <c r="C53" t="s">
+        <v>160</v>
+      </c>
+      <c r="G53" s="7">
+        <v>46203</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A54" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B54" t="s">
+        <v>162</v>
+      </c>
+      <c r="C54" t="s">
+        <v>161</v>
+      </c>
+      <c r="D54" s="7"/>
+      <c r="G54" s="7">
+        <v>46203</v>
       </c>
     </row>
   </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C16"/>
-  </ignoredErrors>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/database.xlsx
+++ b/database.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FEBFDD9-BD41-458C-A6E7-7D2203B9B463}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AB58472-007A-4448-8B56-B157E6200D84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-24012" yWindow="1488" windowWidth="23016" windowHeight="13656" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-26820" yWindow="1308" windowWidth="23016" windowHeight="13656" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="171">
   <si>
     <t>425-81-02924</t>
   </si>
@@ -541,6 +541,15 @@
   </si>
   <si>
     <t>세한국제1221010</t>
+  </si>
+  <si>
+    <t>308-86-03448</t>
+  </si>
+  <si>
+    <t>주식회사 제이지디글로벌</t>
+  </si>
+  <si>
+    <t>제이지디1251011</t>
   </si>
 </sst>
 </file>
@@ -989,7 +998,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE6138A4-676B-44A6-82D7-1ADA43310F48}">
-  <dimension ref="A1:G55"/>
+  <dimension ref="A1:G56"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -1784,6 +1793,20 @@
         <v>46203</v>
       </c>
     </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A56" t="s">
+        <v>168</v>
+      </c>
+      <c r="B56" t="s">
+        <v>169</v>
+      </c>
+      <c r="C56" t="s">
+        <v>170</v>
+      </c>
+      <c r="G56" s="7">
+        <v>46203</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A1:B1048576">

--- a/database.xlsx
+++ b/database.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AB58472-007A-4448-8B56-B157E6200D84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D42EA567-53A8-41FB-B3C0-C397473A42FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-26820" yWindow="1308" windowWidth="23016" windowHeight="13656" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2412" yWindow="17172" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="189">
   <si>
     <t>425-81-02924</t>
   </si>
@@ -550,6 +550,60 @@
   </si>
   <si>
     <t>제이지디1251011</t>
+  </si>
+  <si>
+    <t>라워스</t>
+  </si>
+  <si>
+    <t>155-39-01347</t>
+  </si>
+  <si>
+    <t>라워스**5241014</t>
+  </si>
+  <si>
+    <t>로비엔트</t>
+  </si>
+  <si>
+    <t>775-05-03877</t>
+  </si>
+  <si>
+    <t>로비엔트5261019</t>
+  </si>
+  <si>
+    <t>스카이미너리즈</t>
+  </si>
+  <si>
+    <t>819-08-02465</t>
+  </si>
+  <si>
+    <t>스카이미5231013</t>
+  </si>
+  <si>
+    <t>유한회사 엘민커머스</t>
+  </si>
+  <si>
+    <t>829-88-03051</t>
+  </si>
+  <si>
+    <t>엘민커머1241017</t>
+  </si>
+  <si>
+    <t>731-02-03686</t>
+  </si>
+  <si>
+    <t>라비앙하우스</t>
+  </si>
+  <si>
+    <t>라비앙하5251015</t>
+  </si>
+  <si>
+    <t>589-19-02503</t>
+  </si>
+  <si>
+    <t>쓸리보</t>
+  </si>
+  <si>
+    <t>쓸리보**5251019</t>
   </si>
 </sst>
 </file>
@@ -998,7 +1052,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE6138A4-676B-44A6-82D7-1ADA43310F48}">
-  <dimension ref="A1:G56"/>
+  <dimension ref="A1:G62"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -1807,6 +1861,90 @@
         <v>46203</v>
       </c>
     </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A57" t="s">
+        <v>172</v>
+      </c>
+      <c r="B57" t="s">
+        <v>171</v>
+      </c>
+      <c r="C57" t="s">
+        <v>173</v>
+      </c>
+      <c r="G57" s="7">
+        <v>46203</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A58" t="s">
+        <v>175</v>
+      </c>
+      <c r="B58" t="s">
+        <v>174</v>
+      </c>
+      <c r="C58" t="s">
+        <v>176</v>
+      </c>
+      <c r="G58" s="7">
+        <v>46203</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A59" t="s">
+        <v>178</v>
+      </c>
+      <c r="B59" t="s">
+        <v>177</v>
+      </c>
+      <c r="C59" t="s">
+        <v>179</v>
+      </c>
+      <c r="G59" s="7">
+        <v>46203</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A60" t="s">
+        <v>181</v>
+      </c>
+      <c r="B60" t="s">
+        <v>180</v>
+      </c>
+      <c r="C60" t="s">
+        <v>182</v>
+      </c>
+      <c r="G60" s="7">
+        <v>46203</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A61" t="s">
+        <v>183</v>
+      </c>
+      <c r="B61" t="s">
+        <v>184</v>
+      </c>
+      <c r="C61" t="s">
+        <v>185</v>
+      </c>
+      <c r="G61" s="7">
+        <v>46203</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A62" t="s">
+        <v>186</v>
+      </c>
+      <c r="B62" t="s">
+        <v>187</v>
+      </c>
+      <c r="C62" t="s">
+        <v>188</v>
+      </c>
+      <c r="G62" s="7">
+        <v>46203</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A1:B1048576">

--- a/database.xlsx
+++ b/database.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D42EA567-53A8-41FB-B3C0-C397473A42FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4662C168-8AF3-4EE6-B872-DD16A14C26C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2412" yWindow="17172" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-30828" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="189">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="204">
   <si>
     <t>425-81-02924</t>
   </si>
@@ -604,6 +604,51 @@
   </si>
   <si>
     <t>쓸리보**5251019</t>
+  </si>
+  <si>
+    <t>571-81-04069</t>
+  </si>
+  <si>
+    <t>오로라링크 유한회사</t>
+  </si>
+  <si>
+    <t>오로라링1261019</t>
+  </si>
+  <si>
+    <t>344-13-02645</t>
+  </si>
+  <si>
+    <t>모모타로</t>
+  </si>
+  <si>
+    <t>모모타로5231012</t>
+  </si>
+  <si>
+    <t>하임하이</t>
+  </si>
+  <si>
+    <t>343-16-01760</t>
+  </si>
+  <si>
+    <t>하임하이5221012</t>
+  </si>
+  <si>
+    <t>104-34-15402</t>
+  </si>
+  <si>
+    <t>엠티</t>
+  </si>
+  <si>
+    <t>엠티****5231010</t>
+  </si>
+  <si>
+    <t>그린홈컴퍼니</t>
+  </si>
+  <si>
+    <t>801-03-03153</t>
+  </si>
+  <si>
+    <t>그린홈컴5231012</t>
   </si>
 </sst>
 </file>
@@ -1052,7 +1097,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE6138A4-676B-44A6-82D7-1ADA43310F48}">
-  <dimension ref="A1:G62"/>
+  <dimension ref="A1:G67"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -1945,6 +1990,76 @@
         <v>46203</v>
       </c>
     </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A63" t="s">
+        <v>189</v>
+      </c>
+      <c r="B63" t="s">
+        <v>190</v>
+      </c>
+      <c r="C63" t="s">
+        <v>191</v>
+      </c>
+      <c r="G63" s="7">
+        <v>46203</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A64" t="s">
+        <v>192</v>
+      </c>
+      <c r="B64" t="s">
+        <v>193</v>
+      </c>
+      <c r="C64" t="s">
+        <v>194</v>
+      </c>
+      <c r="G64" s="7">
+        <v>46203</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A65" t="s">
+        <v>196</v>
+      </c>
+      <c r="B65" t="s">
+        <v>195</v>
+      </c>
+      <c r="C65" t="s">
+        <v>197</v>
+      </c>
+      <c r="G65" s="7">
+        <v>46203</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A66" t="s">
+        <v>198</v>
+      </c>
+      <c r="B66" t="s">
+        <v>199</v>
+      </c>
+      <c r="C66" t="s">
+        <v>200</v>
+      </c>
+      <c r="G66" s="7">
+        <v>46203</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A67" t="s">
+        <v>202</v>
+      </c>
+      <c r="B67" t="s">
+        <v>201</v>
+      </c>
+      <c r="C67" t="s">
+        <v>203</v>
+      </c>
+      <c r="G67" s="7">
+        <v>46203</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A1:B1048576">

--- a/database.xlsx
+++ b/database.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD94DA9D-29BC-466D-B048-7C29D77C6490}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A7ABB26-C60D-4450-8D89-60F1BFE832B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-30828" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28284" yWindow="768" windowWidth="26376" windowHeight="15420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2358" uniqueCount="1931">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2366" uniqueCount="1939">
   <si>
     <t>425-81-02924</t>
   </si>
@@ -6215,13 +6215,44 @@
   </si>
   <si>
     <t>서울 금천구 가산디지털2로 166 (가산동, 에이스 K1타워) 1004호</t>
+  </si>
+  <si>
+    <t>212-86-17336</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>복용성세 유한회사</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CHEN TIEJU</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>010-2287-9565</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>flsscq@163.com</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>서울특별시 관악구 은천로 25. 7층 29호(봉천동)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>복용성세1261010</t>
+  </si>
+  <si>
+    <t>08717</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -6303,6 +6334,14 @@
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -6350,10 +6389,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -6439,21 +6479,20 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="14" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="하이퍼링크" xfId="1" builtinId="8"/>
   </cellStyles>
   <dxfs count="2">
     <dxf>
@@ -6811,7 +6850,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE6138A4-676B-44A6-82D7-1ADA43310F48}">
-  <dimension ref="A1:K279"/>
+  <dimension ref="A1:K280"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -9899,10 +9938,10 @@
       <c r="F93" s="28" t="s">
         <v>1433</v>
       </c>
-      <c r="G93" s="38">
-        <v>46212</v>
-      </c>
-      <c r="H93" s="39" t="s">
+      <c r="G93" s="37">
+        <v>46212</v>
+      </c>
+      <c r="H93" s="38" t="s">
         <v>1434</v>
       </c>
       <c r="I93" s="7" t="s">
@@ -9916,7 +9955,7 @@
       <c r="B94" t="s">
         <v>876</v>
       </c>
-      <c r="C94" s="37" t="s">
+      <c r="C94" t="s">
         <v>1436</v>
       </c>
       <c r="D94" s="6" t="s">
@@ -9925,16 +9964,16 @@
       <c r="E94" s="6" t="s">
         <v>1063</v>
       </c>
-      <c r="F94" s="40" t="s">
+      <c r="F94" s="6" t="s">
         <v>1437</v>
       </c>
-      <c r="G94" s="41">
-        <v>46212</v>
-      </c>
-      <c r="H94" s="42" t="s">
+      <c r="G94" s="2">
+        <v>46212</v>
+      </c>
+      <c r="H94" s="39" t="s">
         <v>1438</v>
       </c>
-      <c r="I94" s="37" t="s">
+      <c r="I94" t="s">
         <v>1439</v>
       </c>
     </row>
@@ -9945,7 +9984,7 @@
       <c r="B95" t="s">
         <v>877</v>
       </c>
-      <c r="C95" s="37" t="s">
+      <c r="C95" t="s">
         <v>1440</v>
       </c>
       <c r="D95" s="6" t="s">
@@ -9954,16 +9993,16 @@
       <c r="E95" s="6" t="s">
         <v>1064</v>
       </c>
-      <c r="F95" s="40" t="s">
+      <c r="F95" s="6" t="s">
         <v>1441</v>
       </c>
-      <c r="G95" s="41">
-        <v>46212</v>
-      </c>
-      <c r="H95" s="42" t="s">
+      <c r="G95" s="2">
+        <v>46212</v>
+      </c>
+      <c r="H95" s="39" t="s">
         <v>1442</v>
       </c>
-      <c r="I95" s="37" t="s">
+      <c r="I95" t="s">
         <v>1443</v>
       </c>
     </row>
@@ -9974,7 +10013,7 @@
       <c r="B96" t="s">
         <v>878</v>
       </c>
-      <c r="C96" s="37" t="s">
+      <c r="C96" t="s">
         <v>1444</v>
       </c>
       <c r="D96" s="6" t="s">
@@ -9983,16 +10022,16 @@
       <c r="E96" s="6" t="s">
         <v>1065</v>
       </c>
-      <c r="F96" s="40" t="s">
+      <c r="F96" s="6" t="s">
         <v>1445</v>
       </c>
-      <c r="G96" s="41">
-        <v>46212</v>
-      </c>
-      <c r="H96" s="42" t="s">
+      <c r="G96" s="2">
+        <v>46212</v>
+      </c>
+      <c r="H96" s="39" t="s">
         <v>1446</v>
       </c>
-      <c r="I96" s="37" t="s">
+      <c r="I96" t="s">
         <v>1447</v>
       </c>
     </row>
@@ -10003,7 +10042,7 @@
       <c r="B97" t="s">
         <v>879</v>
       </c>
-      <c r="C97" s="37" t="s">
+      <c r="C97" t="s">
         <v>1448</v>
       </c>
       <c r="D97" s="6" t="s">
@@ -10012,16 +10051,16 @@
       <c r="E97" s="6" t="s">
         <v>1066</v>
       </c>
-      <c r="F97" s="40" t="s">
+      <c r="F97" s="6" t="s">
         <v>1449</v>
       </c>
-      <c r="G97" s="41">
-        <v>46212</v>
-      </c>
-      <c r="H97" s="42" t="s">
+      <c r="G97" s="2">
+        <v>46212</v>
+      </c>
+      <c r="H97" s="39" t="s">
         <v>1450</v>
       </c>
-      <c r="I97" s="37" t="s">
+      <c r="I97" t="s">
         <v>1451</v>
       </c>
     </row>
@@ -10032,7 +10071,7 @@
       <c r="B98" t="s">
         <v>880</v>
       </c>
-      <c r="C98" s="37" t="s">
+      <c r="C98" t="s">
         <v>1452</v>
       </c>
       <c r="D98" s="6" t="s">
@@ -10041,16 +10080,16 @@
       <c r="E98" s="6" t="s">
         <v>1067</v>
       </c>
-      <c r="F98" s="40" t="s">
+      <c r="F98" s="6" t="s">
         <v>1453</v>
       </c>
-      <c r="G98" s="41">
-        <v>46212</v>
-      </c>
-      <c r="H98" s="42" t="s">
+      <c r="G98" s="2">
+        <v>46212</v>
+      </c>
+      <c r="H98" s="39" t="s">
         <v>1454</v>
       </c>
-      <c r="I98" s="37" t="s">
+      <c r="I98" t="s">
         <v>1455</v>
       </c>
     </row>
@@ -10061,7 +10100,7 @@
       <c r="B99" t="s">
         <v>881</v>
       </c>
-      <c r="C99" s="37" t="s">
+      <c r="C99" t="s">
         <v>1456</v>
       </c>
       <c r="D99" s="6" t="s">
@@ -10070,16 +10109,16 @@
       <c r="E99" s="6" t="s">
         <v>1068</v>
       </c>
-      <c r="F99" s="40" t="s">
+      <c r="F99" s="6" t="s">
         <v>1457</v>
       </c>
-      <c r="G99" s="41">
-        <v>46212</v>
-      </c>
-      <c r="H99" s="42" t="s">
+      <c r="G99" s="2">
+        <v>46212</v>
+      </c>
+      <c r="H99" s="39" t="s">
         <v>1458</v>
       </c>
-      <c r="I99" s="37" t="s">
+      <c r="I99" t="s">
         <v>1459</v>
       </c>
     </row>
@@ -10090,7 +10129,7 @@
       <c r="B100" t="s">
         <v>882</v>
       </c>
-      <c r="C100" s="37" t="s">
+      <c r="C100" t="s">
         <v>1432</v>
       </c>
       <c r="D100" s="6" t="s">
@@ -10099,16 +10138,16 @@
       <c r="E100" s="6" t="s">
         <v>1069</v>
       </c>
-      <c r="F100" s="40" t="s">
+      <c r="F100" s="6" t="s">
         <v>1460</v>
       </c>
-      <c r="G100" s="41">
-        <v>46212</v>
-      </c>
-      <c r="H100" s="42" t="s">
+      <c r="G100" s="2">
+        <v>46212</v>
+      </c>
+      <c r="H100" s="39" t="s">
         <v>1461</v>
       </c>
-      <c r="I100" s="37" t="s">
+      <c r="I100" t="s">
         <v>1462</v>
       </c>
     </row>
@@ -10119,7 +10158,7 @@
       <c r="B101" t="s">
         <v>883</v>
       </c>
-      <c r="C101" s="37" t="s">
+      <c r="C101" t="s">
         <v>1463</v>
       </c>
       <c r="D101" s="6" t="s">
@@ -10128,16 +10167,16 @@
       <c r="E101" s="6" t="s">
         <v>1070</v>
       </c>
-      <c r="F101" s="40" t="s">
+      <c r="F101" s="6" t="s">
         <v>1464</v>
       </c>
-      <c r="G101" s="41">
-        <v>46212</v>
-      </c>
-      <c r="H101" s="42" t="s">
+      <c r="G101" s="2">
+        <v>46212</v>
+      </c>
+      <c r="H101" s="39" t="s">
         <v>1465</v>
       </c>
-      <c r="I101" s="37" t="s">
+      <c r="I101" t="s">
         <v>1466</v>
       </c>
     </row>
@@ -10148,7 +10187,7 @@
       <c r="B102" t="s">
         <v>884</v>
       </c>
-      <c r="C102" s="37" t="s">
+      <c r="C102" t="s">
         <v>1448</v>
       </c>
       <c r="D102" s="6" t="s">
@@ -10157,16 +10196,16 @@
       <c r="E102" s="6" t="s">
         <v>1071</v>
       </c>
-      <c r="F102" s="40" t="s">
+      <c r="F102" s="6" t="s">
         <v>1467</v>
       </c>
-      <c r="G102" s="41">
-        <v>46212</v>
-      </c>
-      <c r="H102" s="42" t="s">
+      <c r="G102" s="2">
+        <v>46212</v>
+      </c>
+      <c r="H102" s="39" t="s">
         <v>1468</v>
       </c>
-      <c r="I102" s="37" t="s">
+      <c r="I102" t="s">
         <v>1469</v>
       </c>
     </row>
@@ -10177,7 +10216,7 @@
       <c r="B103" t="s">
         <v>885</v>
       </c>
-      <c r="C103" s="37" t="s">
+      <c r="C103" t="s">
         <v>1432</v>
       </c>
       <c r="D103" s="6" t="s">
@@ -10186,16 +10225,16 @@
       <c r="E103" s="6" t="s">
         <v>1072</v>
       </c>
-      <c r="F103" s="40" t="s">
+      <c r="F103" s="6" t="s">
         <v>1470</v>
       </c>
-      <c r="G103" s="41">
-        <v>46212</v>
-      </c>
-      <c r="H103" s="42" t="s">
+      <c r="G103" s="2">
+        <v>46212</v>
+      </c>
+      <c r="H103" s="39" t="s">
         <v>1471</v>
       </c>
-      <c r="I103" s="37" t="s">
+      <c r="I103" t="s">
         <v>1472</v>
       </c>
     </row>
@@ -10206,7 +10245,7 @@
       <c r="B104" t="s">
         <v>886</v>
       </c>
-      <c r="C104" s="37" t="s">
+      <c r="C104" t="s">
         <v>1448</v>
       </c>
       <c r="D104" s="6" t="s">
@@ -10215,16 +10254,16 @@
       <c r="E104" s="6" t="s">
         <v>1073</v>
       </c>
-      <c r="F104" s="40" t="s">
+      <c r="F104" s="6" t="s">
         <v>1473</v>
       </c>
-      <c r="G104" s="41">
-        <v>46212</v>
-      </c>
-      <c r="H104" s="42" t="s">
+      <c r="G104" s="2">
+        <v>46212</v>
+      </c>
+      <c r="H104" s="39" t="s">
         <v>1474</v>
       </c>
-      <c r="I104" s="37" t="s">
+      <c r="I104" t="s">
         <v>1475</v>
       </c>
     </row>
@@ -10235,7 +10274,7 @@
       <c r="B105" t="s">
         <v>887</v>
       </c>
-      <c r="C105" s="37" t="s">
+      <c r="C105" t="s">
         <v>1448</v>
       </c>
       <c r="D105" s="6" t="s">
@@ -10244,16 +10283,16 @@
       <c r="E105" s="6" t="s">
         <v>1074</v>
       </c>
-      <c r="F105" s="40" t="s">
+      <c r="F105" s="6" t="s">
         <v>1476</v>
       </c>
-      <c r="G105" s="41">
-        <v>46212</v>
-      </c>
-      <c r="H105" s="42" t="s">
+      <c r="G105" s="2">
+        <v>46212</v>
+      </c>
+      <c r="H105" s="39" t="s">
         <v>1477</v>
       </c>
-      <c r="I105" s="37" t="s">
+      <c r="I105" t="s">
         <v>1478</v>
       </c>
     </row>
@@ -10264,7 +10303,7 @@
       <c r="B106" t="s">
         <v>888</v>
       </c>
-      <c r="C106" s="37" t="s">
+      <c r="C106" t="s">
         <v>1448</v>
       </c>
       <c r="D106" s="6" t="s">
@@ -10273,16 +10312,16 @@
       <c r="E106" s="6" t="s">
         <v>1075</v>
       </c>
-      <c r="F106" s="40" t="s">
+      <c r="F106" s="6" t="s">
         <v>1479</v>
       </c>
-      <c r="G106" s="41">
-        <v>46212</v>
-      </c>
-      <c r="H106" s="42" t="s">
+      <c r="G106" s="2">
+        <v>46212</v>
+      </c>
+      <c r="H106" s="39" t="s">
         <v>1480</v>
       </c>
-      <c r="I106" s="37" t="s">
+      <c r="I106" t="s">
         <v>1481</v>
       </c>
     </row>
@@ -10293,7 +10332,7 @@
       <c r="B107" t="s">
         <v>889</v>
       </c>
-      <c r="C107" s="37" t="s">
+      <c r="C107" t="s">
         <v>1448</v>
       </c>
       <c r="D107" s="6" t="s">
@@ -10302,16 +10341,16 @@
       <c r="E107" s="6" t="s">
         <v>1076</v>
       </c>
-      <c r="F107" s="40" t="s">
+      <c r="F107" s="6" t="s">
         <v>1482</v>
       </c>
-      <c r="G107" s="41">
-        <v>46212</v>
-      </c>
-      <c r="H107" s="42" t="s">
+      <c r="G107" s="2">
+        <v>46212</v>
+      </c>
+      <c r="H107" s="39" t="s">
         <v>1483</v>
       </c>
-      <c r="I107" s="37" t="s">
+      <c r="I107" t="s">
         <v>1484</v>
       </c>
     </row>
@@ -10322,7 +10361,7 @@
       <c r="B108" t="s">
         <v>890</v>
       </c>
-      <c r="C108" s="37" t="s">
+      <c r="C108" t="s">
         <v>1463</v>
       </c>
       <c r="D108" s="6" t="s">
@@ -10331,16 +10370,16 @@
       <c r="E108" s="6" t="s">
         <v>1077</v>
       </c>
-      <c r="F108" s="40" t="s">
+      <c r="F108" s="6" t="s">
         <v>1485</v>
       </c>
-      <c r="G108" s="41">
-        <v>46212</v>
-      </c>
-      <c r="H108" s="42" t="s">
+      <c r="G108" s="2">
+        <v>46212</v>
+      </c>
+      <c r="H108" s="39" t="s">
         <v>1486</v>
       </c>
-      <c r="I108" s="37" t="s">
+      <c r="I108" t="s">
         <v>1487</v>
       </c>
     </row>
@@ -10351,7 +10390,7 @@
       <c r="B109" t="s">
         <v>891</v>
       </c>
-      <c r="C109" s="37" t="s">
+      <c r="C109" t="s">
         <v>1448</v>
       </c>
       <c r="D109" s="6" t="s">
@@ -10360,16 +10399,16 @@
       <c r="E109" s="6" t="s">
         <v>1078</v>
       </c>
-      <c r="F109" s="40" t="s">
+      <c r="F109" s="6" t="s">
         <v>1488</v>
       </c>
-      <c r="G109" s="41">
-        <v>46212</v>
-      </c>
-      <c r="H109" s="42" t="s">
+      <c r="G109" s="2">
+        <v>46212</v>
+      </c>
+      <c r="H109" s="39" t="s">
         <v>1489</v>
       </c>
-      <c r="I109" s="37" t="s">
+      <c r="I109" t="s">
         <v>1490</v>
       </c>
     </row>
@@ -10380,7 +10419,7 @@
       <c r="B110" t="s">
         <v>892</v>
       </c>
-      <c r="C110" s="37" t="s">
+      <c r="C110" t="s">
         <v>1444</v>
       </c>
       <c r="D110" s="6" t="s">
@@ -10389,16 +10428,16 @@
       <c r="E110" s="6" t="s">
         <v>1079</v>
       </c>
-      <c r="F110" s="40" t="s">
+      <c r="F110" s="6" t="s">
         <v>1491</v>
       </c>
-      <c r="G110" s="41">
-        <v>46212</v>
-      </c>
-      <c r="H110" s="42" t="s">
+      <c r="G110" s="2">
+        <v>46212</v>
+      </c>
+      <c r="H110" s="39" t="s">
         <v>1492</v>
       </c>
-      <c r="I110" s="37" t="s">
+      <c r="I110" t="s">
         <v>1493</v>
       </c>
     </row>
@@ -10409,7 +10448,7 @@
       <c r="B111" t="s">
         <v>893</v>
       </c>
-      <c r="C111" s="37" t="s">
+      <c r="C111" t="s">
         <v>1444</v>
       </c>
       <c r="D111" s="6" t="s">
@@ -10418,16 +10457,16 @@
       <c r="E111" s="6" t="s">
         <v>1080</v>
       </c>
-      <c r="F111" s="40" t="s">
+      <c r="F111" s="6" t="s">
         <v>1494</v>
       </c>
-      <c r="G111" s="41">
-        <v>46212</v>
-      </c>
-      <c r="H111" s="42" t="s">
+      <c r="G111" s="2">
+        <v>46212</v>
+      </c>
+      <c r="H111" s="39" t="s">
         <v>1495</v>
       </c>
-      <c r="I111" s="37" t="s">
+      <c r="I111" t="s">
         <v>1496</v>
       </c>
     </row>
@@ -10438,7 +10477,7 @@
       <c r="B112" t="s">
         <v>894</v>
       </c>
-      <c r="C112" s="37" t="s">
+      <c r="C112" t="s">
         <v>1497</v>
       </c>
       <c r="D112" s="6" t="s">
@@ -10447,16 +10486,16 @@
       <c r="E112" s="6" t="s">
         <v>1081</v>
       </c>
-      <c r="F112" s="40" t="s">
+      <c r="F112" s="6" t="s">
         <v>1498</v>
       </c>
-      <c r="G112" s="41">
-        <v>46212</v>
-      </c>
-      <c r="H112" s="42" t="s">
+      <c r="G112" s="2">
+        <v>46212</v>
+      </c>
+      <c r="H112" s="39" t="s">
         <v>1499</v>
       </c>
-      <c r="I112" s="37" t="s">
+      <c r="I112" t="s">
         <v>1500</v>
       </c>
     </row>
@@ -10467,7 +10506,7 @@
       <c r="B113" t="s">
         <v>895</v>
       </c>
-      <c r="C113" s="37" t="s">
+      <c r="C113" t="s">
         <v>1501</v>
       </c>
       <c r="D113" s="6" t="s">
@@ -10476,16 +10515,16 @@
       <c r="E113" s="6" t="s">
         <v>1082</v>
       </c>
-      <c r="F113" s="40" t="s">
+      <c r="F113" s="6" t="s">
         <v>1502</v>
       </c>
-      <c r="G113" s="41">
-        <v>46212</v>
-      </c>
-      <c r="H113" s="42" t="s">
+      <c r="G113" s="2">
+        <v>46212</v>
+      </c>
+      <c r="H113" s="39" t="s">
         <v>1503</v>
       </c>
-      <c r="I113" s="37" t="s">
+      <c r="I113" t="s">
         <v>1504</v>
       </c>
     </row>
@@ -10496,7 +10535,7 @@
       <c r="B114" t="s">
         <v>896</v>
       </c>
-      <c r="C114" s="37" t="s">
+      <c r="C114" t="s">
         <v>1448</v>
       </c>
       <c r="D114" s="6" t="s">
@@ -10505,16 +10544,16 @@
       <c r="E114" s="6" t="s">
         <v>1083</v>
       </c>
-      <c r="F114" s="40" t="s">
+      <c r="F114" s="6" t="s">
         <v>1505</v>
       </c>
-      <c r="G114" s="41">
-        <v>46212</v>
-      </c>
-      <c r="H114" s="42" t="s">
+      <c r="G114" s="2">
+        <v>46212</v>
+      </c>
+      <c r="H114" s="39" t="s">
         <v>1506</v>
       </c>
-      <c r="I114" s="37" t="s">
+      <c r="I114" t="s">
         <v>1507</v>
       </c>
     </row>
@@ -10525,7 +10564,7 @@
       <c r="B115" t="s">
         <v>897</v>
       </c>
-      <c r="C115" s="37" t="s">
+      <c r="C115" t="s">
         <v>1452</v>
       </c>
       <c r="D115" s="6" t="s">
@@ -10534,16 +10573,16 @@
       <c r="E115" s="6" t="s">
         <v>1084</v>
       </c>
-      <c r="F115" s="40" t="s">
+      <c r="F115" s="6" t="s">
         <v>1511</v>
       </c>
-      <c r="G115" s="41">
-        <v>46212</v>
-      </c>
-      <c r="H115" s="42" t="s">
+      <c r="G115" s="2">
+        <v>46212</v>
+      </c>
+      <c r="H115" s="39" t="s">
         <v>1512</v>
       </c>
-      <c r="I115" s="37" t="s">
+      <c r="I115" t="s">
         <v>1513</v>
       </c>
     </row>
@@ -10554,7 +10593,7 @@
       <c r="B116" t="s">
         <v>898</v>
       </c>
-      <c r="C116" s="37" t="s">
+      <c r="C116" t="s">
         <v>1508</v>
       </c>
       <c r="D116" s="6" t="s">
@@ -10563,16 +10602,16 @@
       <c r="E116" s="6" t="s">
         <v>1085</v>
       </c>
-      <c r="F116" s="40" t="s">
+      <c r="F116" s="6" t="s">
         <v>1505</v>
       </c>
-      <c r="G116" s="41">
-        <v>46212</v>
-      </c>
-      <c r="H116" s="42" t="s">
+      <c r="G116" s="2">
+        <v>46212</v>
+      </c>
+      <c r="H116" s="39" t="s">
         <v>1514</v>
       </c>
-      <c r="I116" s="37" t="s">
+      <c r="I116" t="s">
         <v>1515</v>
       </c>
     </row>
@@ -10583,7 +10622,7 @@
       <c r="B117" t="s">
         <v>899</v>
       </c>
-      <c r="C117" s="37" t="s">
+      <c r="C117" t="s">
         <v>1501</v>
       </c>
       <c r="D117" s="6" t="s">
@@ -10592,16 +10631,16 @@
       <c r="E117" s="6" t="s">
         <v>1086</v>
       </c>
-      <c r="F117" s="40" t="s">
+      <c r="F117" s="6" t="s">
         <v>1516</v>
       </c>
-      <c r="G117" s="41">
-        <v>46212</v>
-      </c>
-      <c r="H117" s="42" t="s">
+      <c r="G117" s="2">
+        <v>46212</v>
+      </c>
+      <c r="H117" s="39" t="s">
         <v>1517</v>
       </c>
-      <c r="I117" s="37" t="s">
+      <c r="I117" t="s">
         <v>1518</v>
       </c>
     </row>
@@ -10612,7 +10651,7 @@
       <c r="B118" t="s">
         <v>900</v>
       </c>
-      <c r="C118" s="37" t="s">
+      <c r="C118" t="s">
         <v>1452</v>
       </c>
       <c r="D118" s="6" t="s">
@@ -10621,16 +10660,16 @@
       <c r="E118" s="6" t="s">
         <v>1087</v>
       </c>
-      <c r="F118" s="40" t="s">
+      <c r="F118" s="6" t="s">
         <v>1511</v>
       </c>
-      <c r="G118" s="41">
-        <v>46212</v>
-      </c>
-      <c r="H118" s="42" t="s">
+      <c r="G118" s="2">
+        <v>46212</v>
+      </c>
+      <c r="H118" s="39" t="s">
         <v>1519</v>
       </c>
-      <c r="I118" s="37" t="s">
+      <c r="I118" t="s">
         <v>1520</v>
       </c>
     </row>
@@ -10641,7 +10680,7 @@
       <c r="B119" t="s">
         <v>901</v>
       </c>
-      <c r="C119" s="37" t="s">
+      <c r="C119" t="s">
         <v>1452</v>
       </c>
       <c r="D119" s="6" t="s">
@@ -10650,16 +10689,16 @@
       <c r="E119" s="6" t="s">
         <v>1088</v>
       </c>
-      <c r="F119" s="40" t="s">
+      <c r="F119" s="6" t="s">
         <v>1521</v>
       </c>
-      <c r="G119" s="41">
-        <v>46212</v>
-      </c>
-      <c r="H119" s="42" t="s">
+      <c r="G119" s="2">
+        <v>46212</v>
+      </c>
+      <c r="H119" s="39" t="s">
         <v>1522</v>
       </c>
-      <c r="I119" s="37" t="s">
+      <c r="I119" t="s">
         <v>1523</v>
       </c>
     </row>
@@ -10670,7 +10709,7 @@
       <c r="B120" t="s">
         <v>902</v>
       </c>
-      <c r="C120" s="37" t="s">
+      <c r="C120" t="s">
         <v>1452</v>
       </c>
       <c r="D120" s="6" t="s">
@@ -10679,16 +10718,16 @@
       <c r="E120" s="6" t="s">
         <v>1089</v>
       </c>
-      <c r="F120" s="40" t="s">
+      <c r="F120" s="6" t="s">
         <v>1524</v>
       </c>
-      <c r="G120" s="41">
-        <v>46212</v>
-      </c>
-      <c r="H120" s="42" t="s">
+      <c r="G120" s="2">
+        <v>46212</v>
+      </c>
+      <c r="H120" s="39" t="s">
         <v>1525</v>
       </c>
-      <c r="I120" s="37" t="s">
+      <c r="I120" t="s">
         <v>1526</v>
       </c>
     </row>
@@ -10699,7 +10738,7 @@
       <c r="B121" t="s">
         <v>903</v>
       </c>
-      <c r="C121" s="37" t="s">
+      <c r="C121" t="s">
         <v>1448</v>
       </c>
       <c r="D121" s="6" t="s">
@@ -10708,16 +10747,16 @@
       <c r="E121" s="6" t="s">
         <v>1090</v>
       </c>
-      <c r="F121" s="40" t="s">
+      <c r="F121" s="6" t="s">
         <v>1527</v>
       </c>
-      <c r="G121" s="41">
-        <v>46212</v>
-      </c>
-      <c r="H121" s="42" t="s">
+      <c r="G121" s="2">
+        <v>46212</v>
+      </c>
+      <c r="H121" s="39" t="s">
         <v>1528</v>
       </c>
-      <c r="I121" s="37" t="s">
+      <c r="I121" t="s">
         <v>1529</v>
       </c>
     </row>
@@ -10728,7 +10767,7 @@
       <c r="B122" t="s">
         <v>904</v>
       </c>
-      <c r="C122" s="37" t="s">
+      <c r="C122" t="s">
         <v>1501</v>
       </c>
       <c r="D122" s="6" t="s">
@@ -10737,16 +10776,16 @@
       <c r="E122" s="6" t="s">
         <v>1091</v>
       </c>
-      <c r="F122" s="40" t="s">
+      <c r="F122" s="6" t="s">
         <v>1530</v>
       </c>
-      <c r="G122" s="41">
-        <v>46212</v>
-      </c>
-      <c r="H122" s="42" t="s">
+      <c r="G122" s="2">
+        <v>46212</v>
+      </c>
+      <c r="H122" s="39" t="s">
         <v>1531</v>
       </c>
-      <c r="I122" s="37" t="s">
+      <c r="I122" t="s">
         <v>1532</v>
       </c>
     </row>
@@ -10757,7 +10796,7 @@
       <c r="B123" t="s">
         <v>905</v>
       </c>
-      <c r="C123" s="37" t="s">
+      <c r="C123" t="s">
         <v>1463</v>
       </c>
       <c r="D123" s="6" t="s">
@@ -10766,16 +10805,16 @@
       <c r="E123" s="6" t="s">
         <v>1092</v>
       </c>
-      <c r="F123" s="40" t="s">
+      <c r="F123" s="6" t="s">
         <v>1533</v>
       </c>
-      <c r="G123" s="41">
-        <v>46212</v>
-      </c>
-      <c r="H123" s="42" t="s">
+      <c r="G123" s="2">
+        <v>46212</v>
+      </c>
+      <c r="H123" s="39" t="s">
         <v>1534</v>
       </c>
-      <c r="I123" s="37" t="s">
+      <c r="I123" t="s">
         <v>1535</v>
       </c>
     </row>
@@ -10786,7 +10825,7 @@
       <c r="B124" t="s">
         <v>906</v>
       </c>
-      <c r="C124" s="37" t="s">
+      <c r="C124" t="s">
         <v>1452</v>
       </c>
       <c r="D124" s="6" t="s">
@@ -10795,16 +10834,16 @@
       <c r="E124" s="6" t="s">
         <v>1093</v>
       </c>
-      <c r="F124" s="40" t="s">
+      <c r="F124" s="6" t="s">
         <v>1536</v>
       </c>
-      <c r="G124" s="41">
-        <v>46212</v>
-      </c>
-      <c r="H124" s="42" t="s">
+      <c r="G124" s="2">
+        <v>46212</v>
+      </c>
+      <c r="H124" s="39" t="s">
         <v>1537</v>
       </c>
-      <c r="I124" s="37" t="s">
+      <c r="I124" t="s">
         <v>1538</v>
       </c>
     </row>
@@ -10815,7 +10854,7 @@
       <c r="B125" t="s">
         <v>907</v>
       </c>
-      <c r="C125" s="37" t="s">
+      <c r="C125" t="s">
         <v>1456</v>
       </c>
       <c r="D125" s="6" t="s">
@@ -10824,16 +10863,16 @@
       <c r="E125" s="6" t="s">
         <v>1094</v>
       </c>
-      <c r="F125" s="40" t="s">
+      <c r="F125" s="6" t="s">
         <v>1539</v>
       </c>
-      <c r="G125" s="41">
-        <v>46212</v>
-      </c>
-      <c r="H125" s="42" t="s">
+      <c r="G125" s="2">
+        <v>46212</v>
+      </c>
+      <c r="H125" s="39" t="s">
         <v>1540</v>
       </c>
-      <c r="I125" s="37" t="s">
+      <c r="I125" t="s">
         <v>1541</v>
       </c>
     </row>
@@ -10844,7 +10883,7 @@
       <c r="B126" t="s">
         <v>908</v>
       </c>
-      <c r="C126" s="37" t="s">
+      <c r="C126" t="s">
         <v>1463</v>
       </c>
       <c r="D126" s="6" t="s">
@@ -10853,16 +10892,16 @@
       <c r="E126" s="6" t="s">
         <v>1095</v>
       </c>
-      <c r="F126" s="40" t="s">
+      <c r="F126" s="6" t="s">
         <v>1542</v>
       </c>
-      <c r="G126" s="41">
-        <v>46212</v>
-      </c>
-      <c r="H126" s="42" t="s">
+      <c r="G126" s="2">
+        <v>46212</v>
+      </c>
+      <c r="H126" s="39" t="s">
         <v>1468</v>
       </c>
-      <c r="I126" s="37" t="s">
+      <c r="I126" t="s">
         <v>1543</v>
       </c>
     </row>
@@ -10873,7 +10912,7 @@
       <c r="B127" t="s">
         <v>909</v>
       </c>
-      <c r="C127" s="37" t="s">
+      <c r="C127" t="s">
         <v>1448</v>
       </c>
       <c r="D127" s="6" t="s">
@@ -10882,16 +10921,16 @@
       <c r="E127" s="6" t="s">
         <v>1096</v>
       </c>
-      <c r="F127" s="40" t="s">
+      <c r="F127" s="6" t="s">
         <v>1544</v>
       </c>
-      <c r="G127" s="41">
-        <v>46212</v>
-      </c>
-      <c r="H127" s="42" t="s">
+      <c r="G127" s="2">
+        <v>46212</v>
+      </c>
+      <c r="H127" s="39" t="s">
         <v>1545</v>
       </c>
-      <c r="I127" s="37" t="s">
+      <c r="I127" t="s">
         <v>1546</v>
       </c>
     </row>
@@ -10902,7 +10941,7 @@
       <c r="B128" t="s">
         <v>910</v>
       </c>
-      <c r="C128" s="37" t="s">
+      <c r="C128" t="s">
         <v>1444</v>
       </c>
       <c r="D128" s="6" t="s">
@@ -10911,16 +10950,16 @@
       <c r="E128" s="6" t="s">
         <v>1097</v>
       </c>
-      <c r="F128" s="40" t="s">
+      <c r="F128" s="6" t="s">
         <v>1547</v>
       </c>
-      <c r="G128" s="41">
-        <v>46212</v>
-      </c>
-      <c r="H128" s="42" t="s">
+      <c r="G128" s="2">
+        <v>46212</v>
+      </c>
+      <c r="H128" s="39" t="s">
         <v>1509</v>
       </c>
-      <c r="I128" s="37" t="s">
+      <c r="I128" t="s">
         <v>1548</v>
       </c>
     </row>
@@ -10931,7 +10970,7 @@
       <c r="B129" t="s">
         <v>911</v>
       </c>
-      <c r="C129" s="37" t="s">
+      <c r="C129" t="s">
         <v>1456</v>
       </c>
       <c r="D129" s="6" t="s">
@@ -10940,16 +10979,16 @@
       <c r="E129" s="6" t="s">
         <v>1098</v>
       </c>
-      <c r="F129" s="40" t="s">
+      <c r="F129" s="6" t="s">
         <v>1549</v>
       </c>
-      <c r="G129" s="41">
-        <v>46212</v>
-      </c>
-      <c r="H129" s="42" t="s">
+      <c r="G129" s="2">
+        <v>46212</v>
+      </c>
+      <c r="H129" s="39" t="s">
         <v>1550</v>
       </c>
-      <c r="I129" s="37" t="s">
+      <c r="I129" t="s">
         <v>1551</v>
       </c>
     </row>
@@ -10960,7 +10999,7 @@
       <c r="B130" t="s">
         <v>912</v>
       </c>
-      <c r="C130" s="37" t="s">
+      <c r="C130" t="s">
         <v>1448</v>
       </c>
       <c r="D130" s="6" t="s">
@@ -10969,16 +11008,16 @@
       <c r="E130" s="6" t="s">
         <v>1099</v>
       </c>
-      <c r="F130" s="40" t="s">
+      <c r="F130" s="6" t="s">
         <v>1552</v>
       </c>
-      <c r="G130" s="41">
-        <v>46212</v>
-      </c>
-      <c r="H130" s="42" t="s">
+      <c r="G130" s="2">
+        <v>46212</v>
+      </c>
+      <c r="H130" s="39" t="s">
         <v>1553</v>
       </c>
-      <c r="I130" s="37" t="s">
+      <c r="I130" t="s">
         <v>1554</v>
       </c>
     </row>
@@ -10989,7 +11028,7 @@
       <c r="B131" t="s">
         <v>913</v>
       </c>
-      <c r="C131" s="37" t="s">
+      <c r="C131" t="s">
         <v>1452</v>
       </c>
       <c r="D131" s="6" t="s">
@@ -10998,16 +11037,16 @@
       <c r="E131" s="6" t="s">
         <v>1100</v>
       </c>
-      <c r="F131" s="40" t="s">
+      <c r="F131" s="6" t="s">
         <v>1505</v>
       </c>
-      <c r="G131" s="41">
-        <v>46212</v>
-      </c>
-      <c r="H131" s="42" t="s">
+      <c r="G131" s="2">
+        <v>46212</v>
+      </c>
+      <c r="H131" s="39" t="s">
         <v>1555</v>
       </c>
-      <c r="I131" s="37" t="s">
+      <c r="I131" t="s">
         <v>1556</v>
       </c>
     </row>
@@ -11018,7 +11057,7 @@
       <c r="B132" t="s">
         <v>914</v>
       </c>
-      <c r="C132" s="37" t="s">
+      <c r="C132" t="s">
         <v>1497</v>
       </c>
       <c r="D132" s="6" t="s">
@@ -11027,16 +11066,16 @@
       <c r="E132" s="6" t="s">
         <v>1101</v>
       </c>
-      <c r="F132" s="40" t="s">
+      <c r="F132" s="6" t="s">
         <v>1557</v>
       </c>
-      <c r="G132" s="41">
-        <v>46212</v>
-      </c>
-      <c r="H132" s="42" t="s">
+      <c r="G132" s="2">
+        <v>46212</v>
+      </c>
+      <c r="H132" s="39" t="s">
         <v>1558</v>
       </c>
-      <c r="I132" s="37" t="s">
+      <c r="I132" t="s">
         <v>1559</v>
       </c>
     </row>
@@ -11047,7 +11086,7 @@
       <c r="B133" t="s">
         <v>915</v>
       </c>
-      <c r="C133" s="37" t="s">
+      <c r="C133" t="s">
         <v>1456</v>
       </c>
       <c r="D133" s="6" t="s">
@@ -11056,16 +11095,16 @@
       <c r="E133" s="6" t="s">
         <v>1102</v>
       </c>
-      <c r="F133" s="40" t="s">
+      <c r="F133" s="6" t="s">
         <v>1560</v>
       </c>
-      <c r="G133" s="41">
-        <v>46212</v>
-      </c>
-      <c r="H133" s="42" t="s">
+      <c r="G133" s="2">
+        <v>46212</v>
+      </c>
+      <c r="H133" s="39" t="s">
         <v>1514</v>
       </c>
-      <c r="I133" s="37" t="s">
+      <c r="I133" t="s">
         <v>1561</v>
       </c>
     </row>
@@ -11076,7 +11115,7 @@
       <c r="B134" t="s">
         <v>916</v>
       </c>
-      <c r="C134" s="37" t="s">
+      <c r="C134" t="s">
         <v>1448</v>
       </c>
       <c r="D134" s="6" t="s">
@@ -11085,16 +11124,16 @@
       <c r="E134" s="6" t="s">
         <v>1103</v>
       </c>
-      <c r="F134" s="40" t="s">
+      <c r="F134" s="6" t="s">
         <v>1562</v>
       </c>
-      <c r="G134" s="41">
-        <v>46212</v>
-      </c>
-      <c r="H134" s="42" t="s">
+      <c r="G134" s="2">
+        <v>46212</v>
+      </c>
+      <c r="H134" s="39" t="s">
         <v>1563</v>
       </c>
-      <c r="I134" s="37" t="s">
+      <c r="I134" t="s">
         <v>1564</v>
       </c>
     </row>
@@ -11105,7 +11144,7 @@
       <c r="B135" t="s">
         <v>917</v>
       </c>
-      <c r="C135" s="37" t="s">
+      <c r="C135" t="s">
         <v>1565</v>
       </c>
       <c r="D135" s="6" t="s">
@@ -11114,16 +11153,16 @@
       <c r="E135" s="6" t="s">
         <v>1104</v>
       </c>
-      <c r="F135" s="40" t="s">
+      <c r="F135" s="6" t="s">
         <v>1566</v>
       </c>
-      <c r="G135" s="41">
-        <v>46212</v>
-      </c>
-      <c r="H135" s="42" t="s">
+      <c r="G135" s="2">
+        <v>46212</v>
+      </c>
+      <c r="H135" s="39" t="s">
         <v>1567</v>
       </c>
-      <c r="I135" s="37" t="s">
+      <c r="I135" t="s">
         <v>1568</v>
       </c>
     </row>
@@ -11134,7 +11173,7 @@
       <c r="B136" t="s">
         <v>918</v>
       </c>
-      <c r="C136" s="37" t="s">
+      <c r="C136" t="s">
         <v>1456</v>
       </c>
       <c r="D136" s="6" t="s">
@@ -11143,16 +11182,16 @@
       <c r="E136" s="6" t="s">
         <v>1105</v>
       </c>
-      <c r="F136" s="40" t="s">
+      <c r="F136" s="6" t="s">
         <v>1569</v>
       </c>
-      <c r="G136" s="41">
-        <v>46212</v>
-      </c>
-      <c r="H136" s="42" t="s">
+      <c r="G136" s="2">
+        <v>46212</v>
+      </c>
+      <c r="H136" s="39" t="s">
         <v>1570</v>
       </c>
-      <c r="I136" s="37" t="s">
+      <c r="I136" t="s">
         <v>1571</v>
       </c>
     </row>
@@ -11163,7 +11202,7 @@
       <c r="B137" t="s">
         <v>919</v>
       </c>
-      <c r="C137" s="37" t="s">
+      <c r="C137" t="s">
         <v>1448</v>
       </c>
       <c r="D137" s="6" t="s">
@@ -11172,16 +11211,16 @@
       <c r="E137" s="6" t="s">
         <v>1106</v>
       </c>
-      <c r="F137" s="40" t="s">
+      <c r="F137" s="6" t="s">
         <v>1572</v>
       </c>
-      <c r="G137" s="41">
-        <v>46212</v>
-      </c>
-      <c r="H137" s="42" t="s">
+      <c r="G137" s="2">
+        <v>46212</v>
+      </c>
+      <c r="H137" s="39" t="s">
         <v>1489</v>
       </c>
-      <c r="I137" s="37" t="s">
+      <c r="I137" t="s">
         <v>1573</v>
       </c>
     </row>
@@ -11192,7 +11231,7 @@
       <c r="B138" t="s">
         <v>920</v>
       </c>
-      <c r="C138" s="37" t="s">
+      <c r="C138" t="s">
         <v>1448</v>
       </c>
       <c r="D138" s="6" t="s">
@@ -11201,16 +11240,16 @@
       <c r="E138" s="6" t="s">
         <v>1107</v>
       </c>
-      <c r="F138" s="40" t="s">
+      <c r="F138" s="6" t="s">
         <v>1574</v>
       </c>
-      <c r="G138" s="41">
-        <v>46212</v>
-      </c>
-      <c r="H138" s="42" t="s">
+      <c r="G138" s="2">
+        <v>46212</v>
+      </c>
+      <c r="H138" s="39" t="s">
         <v>1575</v>
       </c>
-      <c r="I138" s="37" t="s">
+      <c r="I138" t="s">
         <v>1576</v>
       </c>
     </row>
@@ -11221,7 +11260,7 @@
       <c r="B139" t="s">
         <v>921</v>
       </c>
-      <c r="C139" s="37" t="s">
+      <c r="C139" t="s">
         <v>1448</v>
       </c>
       <c r="D139" s="6" t="s">
@@ -11230,16 +11269,16 @@
       <c r="E139" s="6" t="s">
         <v>1108</v>
       </c>
-      <c r="F139" s="40" t="s">
+      <c r="F139" s="6" t="s">
         <v>1577</v>
       </c>
-      <c r="G139" s="41">
-        <v>46212</v>
-      </c>
-      <c r="H139" s="42" t="s">
+      <c r="G139" s="2">
+        <v>46212</v>
+      </c>
+      <c r="H139" s="39" t="s">
         <v>1578</v>
       </c>
-      <c r="I139" s="37" t="s">
+      <c r="I139" t="s">
         <v>1579</v>
       </c>
     </row>
@@ -11250,7 +11289,7 @@
       <c r="B140" t="s">
         <v>922</v>
       </c>
-      <c r="C140" s="37" t="s">
+      <c r="C140" t="s">
         <v>1448</v>
       </c>
       <c r="D140" s="6" t="s">
@@ -11259,16 +11298,16 @@
       <c r="E140" s="6" t="s">
         <v>1109</v>
       </c>
-      <c r="F140" s="40" t="s">
+      <c r="F140" s="6" t="s">
         <v>1580</v>
       </c>
-      <c r="G140" s="41">
-        <v>46212</v>
-      </c>
-      <c r="H140" s="42" t="s">
+      <c r="G140" s="2">
+        <v>46212</v>
+      </c>
+      <c r="H140" s="39" t="s">
         <v>1558</v>
       </c>
-      <c r="I140" s="37" t="s">
+      <c r="I140" t="s">
         <v>1581</v>
       </c>
     </row>
@@ -11279,7 +11318,7 @@
       <c r="B141" t="s">
         <v>923</v>
       </c>
-      <c r="C141" s="37" t="s">
+      <c r="C141" t="s">
         <v>1456</v>
       </c>
       <c r="D141" s="6" t="s">
@@ -11288,16 +11327,16 @@
       <c r="E141" s="6" t="s">
         <v>1110</v>
       </c>
-      <c r="F141" s="40" t="s">
+      <c r="F141" s="6" t="s">
         <v>1582</v>
       </c>
-      <c r="G141" s="41">
-        <v>46212</v>
-      </c>
-      <c r="H141" s="42" t="s">
+      <c r="G141" s="2">
+        <v>46212</v>
+      </c>
+      <c r="H141" s="39" t="s">
         <v>1583</v>
       </c>
-      <c r="I141" s="37" t="s">
+      <c r="I141" t="s">
         <v>1584</v>
       </c>
     </row>
@@ -11308,7 +11347,7 @@
       <c r="B142" t="s">
         <v>924</v>
       </c>
-      <c r="C142" s="37" t="s">
+      <c r="C142" t="s">
         <v>1501</v>
       </c>
       <c r="D142" s="6" t="s">
@@ -11317,16 +11356,16 @@
       <c r="E142" s="6" t="s">
         <v>1111</v>
       </c>
-      <c r="F142" s="40" t="s">
+      <c r="F142" s="6" t="s">
         <v>1585</v>
       </c>
-      <c r="G142" s="41">
-        <v>46212</v>
-      </c>
-      <c r="H142" s="42" t="s">
+      <c r="G142" s="2">
+        <v>46212</v>
+      </c>
+      <c r="H142" s="39" t="s">
         <v>1586</v>
       </c>
-      <c r="I142" s="37" t="s">
+      <c r="I142" t="s">
         <v>1587</v>
       </c>
     </row>
@@ -11337,7 +11376,7 @@
       <c r="B143" t="s">
         <v>925</v>
       </c>
-      <c r="C143" s="37" t="s">
+      <c r="C143" t="s">
         <v>1501</v>
       </c>
       <c r="D143" s="6" t="s">
@@ -11346,16 +11385,16 @@
       <c r="E143" s="6" t="s">
         <v>1112</v>
       </c>
-      <c r="F143" s="40" t="s">
+      <c r="F143" s="6" t="s">
         <v>1588</v>
       </c>
-      <c r="G143" s="41">
-        <v>46212</v>
-      </c>
-      <c r="H143" s="42" t="s">
+      <c r="G143" s="2">
+        <v>46212</v>
+      </c>
+      <c r="H143" s="39" t="s">
         <v>1589</v>
       </c>
-      <c r="I143" s="37" t="s">
+      <c r="I143" t="s">
         <v>1590</v>
       </c>
     </row>
@@ -11366,7 +11405,7 @@
       <c r="B144" t="s">
         <v>926</v>
       </c>
-      <c r="C144" s="37" t="s">
+      <c r="C144" t="s">
         <v>1448</v>
       </c>
       <c r="D144" s="6" t="s">
@@ -11375,16 +11414,16 @@
       <c r="E144" s="6" t="s">
         <v>1113</v>
       </c>
-      <c r="F144" s="40" t="s">
+      <c r="F144" s="6" t="s">
         <v>1591</v>
       </c>
-      <c r="G144" s="41">
-        <v>46212</v>
-      </c>
-      <c r="H144" s="42" t="s">
+      <c r="G144" s="2">
+        <v>46212</v>
+      </c>
+      <c r="H144" s="39" t="s">
         <v>1468</v>
       </c>
-      <c r="I144" s="37" t="s">
+      <c r="I144" t="s">
         <v>1592</v>
       </c>
     </row>
@@ -11395,7 +11434,7 @@
       <c r="B145" t="s">
         <v>927</v>
       </c>
-      <c r="C145" s="37" t="s">
+      <c r="C145" t="s">
         <v>1456</v>
       </c>
       <c r="D145" s="6" t="s">
@@ -11404,16 +11443,16 @@
       <c r="E145" s="6" t="s">
         <v>1114</v>
       </c>
-      <c r="F145" s="40" t="s">
+      <c r="F145" s="6" t="s">
         <v>1593</v>
       </c>
-      <c r="G145" s="41">
-        <v>46212</v>
-      </c>
-      <c r="H145" s="42" t="s">
+      <c r="G145" s="2">
+        <v>46212</v>
+      </c>
+      <c r="H145" s="39" t="s">
         <v>1594</v>
       </c>
-      <c r="I145" s="37" t="s">
+      <c r="I145" t="s">
         <v>1595</v>
       </c>
     </row>
@@ -11424,7 +11463,7 @@
       <c r="B146" t="s">
         <v>928</v>
       </c>
-      <c r="C146" s="37" t="s">
+      <c r="C146" t="s">
         <v>1448</v>
       </c>
       <c r="D146" s="6" t="s">
@@ -11433,16 +11472,16 @@
       <c r="E146" s="6" t="s">
         <v>1115</v>
       </c>
-      <c r="F146" s="40" t="s">
+      <c r="F146" s="6" t="s">
         <v>1596</v>
       </c>
-      <c r="G146" s="41">
-        <v>46212</v>
-      </c>
-      <c r="H146" s="42" t="s">
+      <c r="G146" s="2">
+        <v>46212</v>
+      </c>
+      <c r="H146" s="39" t="s">
         <v>1597</v>
       </c>
-      <c r="I146" s="37" t="s">
+      <c r="I146" t="s">
         <v>1598</v>
       </c>
     </row>
@@ -11453,7 +11492,7 @@
       <c r="B147" t="s">
         <v>929</v>
       </c>
-      <c r="C147" s="37" t="s">
+      <c r="C147" t="s">
         <v>1456</v>
       </c>
       <c r="D147" s="6" t="s">
@@ -11462,16 +11501,16 @@
       <c r="E147" s="6" t="s">
         <v>1116</v>
       </c>
-      <c r="F147" s="40" t="s">
+      <c r="F147" s="6" t="s">
         <v>1599</v>
       </c>
-      <c r="G147" s="41">
-        <v>46212</v>
-      </c>
-      <c r="H147" s="42" t="s">
+      <c r="G147" s="2">
+        <v>46212</v>
+      </c>
+      <c r="H147" s="39" t="s">
         <v>1600</v>
       </c>
-      <c r="I147" s="37" t="s">
+      <c r="I147" t="s">
         <v>1601</v>
       </c>
     </row>
@@ -11482,7 +11521,7 @@
       <c r="B148" t="s">
         <v>930</v>
       </c>
-      <c r="C148" s="37" t="s">
+      <c r="C148" t="s">
         <v>1463</v>
       </c>
       <c r="D148" s="6" t="s">
@@ -11491,16 +11530,16 @@
       <c r="E148" s="6" t="s">
         <v>1117</v>
       </c>
-      <c r="F148" s="40" t="s">
+      <c r="F148" s="6" t="s">
         <v>1602</v>
       </c>
-      <c r="G148" s="41">
-        <v>46212</v>
-      </c>
-      <c r="H148" s="42" t="s">
+      <c r="G148" s="2">
+        <v>46212</v>
+      </c>
+      <c r="H148" s="39" t="s">
         <v>1477</v>
       </c>
-      <c r="I148" s="37" t="s">
+      <c r="I148" t="s">
         <v>1603</v>
       </c>
     </row>
@@ -11511,7 +11550,7 @@
       <c r="B149" t="s">
         <v>931</v>
       </c>
-      <c r="C149" s="37" t="s">
+      <c r="C149" t="s">
         <v>1448</v>
       </c>
       <c r="D149" s="6" t="s">
@@ -11520,16 +11559,16 @@
       <c r="E149" s="6" t="s">
         <v>1118</v>
       </c>
-      <c r="F149" s="40" t="s">
+      <c r="F149" s="6" t="s">
         <v>1604</v>
       </c>
-      <c r="G149" s="41">
-        <v>46212</v>
-      </c>
-      <c r="H149" s="42" t="s">
+      <c r="G149" s="2">
+        <v>46212</v>
+      </c>
+      <c r="H149" s="39" t="s">
         <v>1477</v>
       </c>
-      <c r="I149" s="37" t="s">
+      <c r="I149" t="s">
         <v>1605</v>
       </c>
     </row>
@@ -11540,7 +11579,7 @@
       <c r="B150" t="s">
         <v>932</v>
       </c>
-      <c r="C150" s="37" t="s">
+      <c r="C150" t="s">
         <v>1497</v>
       </c>
       <c r="D150" s="6" t="s">
@@ -11549,16 +11588,16 @@
       <c r="E150" s="6" t="s">
         <v>1119</v>
       </c>
-      <c r="F150" s="40" t="s">
+      <c r="F150" s="6" t="s">
         <v>1606</v>
       </c>
-      <c r="G150" s="41">
-        <v>46212</v>
-      </c>
-      <c r="H150" s="42" t="s">
+      <c r="G150" s="2">
+        <v>46212</v>
+      </c>
+      <c r="H150" s="39" t="s">
         <v>1509</v>
       </c>
-      <c r="I150" s="37" t="s">
+      <c r="I150" t="s">
         <v>1607</v>
       </c>
     </row>
@@ -11569,7 +11608,7 @@
       <c r="B151" t="s">
         <v>933</v>
       </c>
-      <c r="C151" s="37" t="s">
+      <c r="C151" t="s">
         <v>1508</v>
       </c>
       <c r="D151" s="6" t="s">
@@ -11578,16 +11617,16 @@
       <c r="E151" s="6" t="s">
         <v>1120</v>
       </c>
-      <c r="F151" s="40" t="s">
+      <c r="F151" s="6" t="s">
         <v>1608</v>
       </c>
-      <c r="G151" s="41">
-        <v>46212</v>
-      </c>
-      <c r="H151" s="42" t="s">
+      <c r="G151" s="2">
+        <v>46212</v>
+      </c>
+      <c r="H151" s="39" t="s">
         <v>1609</v>
       </c>
-      <c r="I151" s="37" t="s">
+      <c r="I151" t="s">
         <v>1610</v>
       </c>
     </row>
@@ -11598,7 +11637,7 @@
       <c r="B152" t="s">
         <v>934</v>
       </c>
-      <c r="C152" s="37" t="s">
+      <c r="C152" t="s">
         <v>1448</v>
       </c>
       <c r="D152" s="6" t="s">
@@ -11607,16 +11646,16 @@
       <c r="E152" s="6" t="s">
         <v>1121</v>
       </c>
-      <c r="F152" s="40" t="s">
+      <c r="F152" s="6" t="s">
         <v>1611</v>
       </c>
-      <c r="G152" s="41">
-        <v>46212</v>
-      </c>
-      <c r="H152" s="42" t="s">
+      <c r="G152" s="2">
+        <v>46212</v>
+      </c>
+      <c r="H152" s="39" t="s">
         <v>1612</v>
       </c>
-      <c r="I152" s="37" t="s">
+      <c r="I152" t="s">
         <v>1613</v>
       </c>
     </row>
@@ -11627,7 +11666,7 @@
       <c r="B153" t="s">
         <v>935</v>
       </c>
-      <c r="C153" s="37" t="s">
+      <c r="C153" t="s">
         <v>1452</v>
       </c>
       <c r="D153" s="6" t="s">
@@ -11636,16 +11675,16 @@
       <c r="E153" s="6" t="s">
         <v>1122</v>
       </c>
-      <c r="F153" s="40" t="s">
+      <c r="F153" s="6" t="s">
         <v>1614</v>
       </c>
-      <c r="G153" s="41">
-        <v>46212</v>
-      </c>
-      <c r="H153" s="42" t="s">
+      <c r="G153" s="2">
+        <v>46212</v>
+      </c>
+      <c r="H153" s="39" t="s">
         <v>1578</v>
       </c>
-      <c r="I153" s="37" t="s">
+      <c r="I153" t="s">
         <v>1615</v>
       </c>
     </row>
@@ -11656,7 +11695,7 @@
       <c r="B154" t="s">
         <v>936</v>
       </c>
-      <c r="C154" s="37" t="s">
+      <c r="C154" t="s">
         <v>1463</v>
       </c>
       <c r="D154" s="6" t="s">
@@ -11665,16 +11704,16 @@
       <c r="E154" s="6" t="s">
         <v>1123</v>
       </c>
-      <c r="F154" s="40" t="s">
+      <c r="F154" s="6" t="s">
         <v>1616</v>
       </c>
-      <c r="G154" s="41">
-        <v>46212</v>
-      </c>
-      <c r="H154" s="42" t="s">
+      <c r="G154" s="2">
+        <v>46212</v>
+      </c>
+      <c r="H154" s="39" t="s">
         <v>1617</v>
       </c>
-      <c r="I154" s="37" t="s">
+      <c r="I154" t="s">
         <v>1618</v>
       </c>
     </row>
@@ -11685,7 +11724,7 @@
       <c r="B155" t="s">
         <v>937</v>
       </c>
-      <c r="C155" s="37" t="s">
+      <c r="C155" t="s">
         <v>1463</v>
       </c>
       <c r="D155" s="6" t="s">
@@ -11694,16 +11733,16 @@
       <c r="E155" s="6" t="s">
         <v>1124</v>
       </c>
-      <c r="F155" s="40" t="s">
+      <c r="F155" s="6" t="s">
         <v>1619</v>
       </c>
-      <c r="G155" s="41">
-        <v>46212</v>
-      </c>
-      <c r="H155" s="42" t="s">
+      <c r="G155" s="2">
+        <v>46212</v>
+      </c>
+      <c r="H155" s="39" t="s">
         <v>1620</v>
       </c>
-      <c r="I155" s="37" t="s">
+      <c r="I155" t="s">
         <v>1621</v>
       </c>
     </row>
@@ -11714,7 +11753,7 @@
       <c r="B156" t="s">
         <v>938</v>
       </c>
-      <c r="C156" s="37" t="s">
+      <c r="C156" t="s">
         <v>1456</v>
       </c>
       <c r="D156" s="6" t="s">
@@ -11723,16 +11762,16 @@
       <c r="E156" s="6" t="s">
         <v>1125</v>
       </c>
-      <c r="F156" s="40" t="s">
+      <c r="F156" s="6" t="s">
         <v>1622</v>
       </c>
-      <c r="G156" s="41">
-        <v>46212</v>
-      </c>
-      <c r="H156" s="42" t="s">
+      <c r="G156" s="2">
+        <v>46212</v>
+      </c>
+      <c r="H156" s="39" t="s">
         <v>1578</v>
       </c>
-      <c r="I156" s="37" t="s">
+      <c r="I156" t="s">
         <v>1623</v>
       </c>
     </row>
@@ -11743,7 +11782,7 @@
       <c r="B157" t="s">
         <v>939</v>
       </c>
-      <c r="C157" s="37" t="s">
+      <c r="C157" t="s">
         <v>1624</v>
       </c>
       <c r="D157" s="6" t="s">
@@ -11752,16 +11791,16 @@
       <c r="E157" s="6" t="s">
         <v>1126</v>
       </c>
-      <c r="F157" s="40" t="s">
+      <c r="F157" s="6" t="s">
         <v>1625</v>
       </c>
-      <c r="G157" s="41">
-        <v>46212</v>
-      </c>
-      <c r="H157" s="42" t="s">
+      <c r="G157" s="2">
+        <v>46212</v>
+      </c>
+      <c r="H157" s="39" t="s">
         <v>1626</v>
       </c>
-      <c r="I157" s="37" t="s">
+      <c r="I157" t="s">
         <v>1627</v>
       </c>
     </row>
@@ -11772,7 +11811,7 @@
       <c r="B158" t="s">
         <v>940</v>
       </c>
-      <c r="C158" s="37" t="s">
+      <c r="C158" t="s">
         <v>1452</v>
       </c>
       <c r="D158" s="6" t="s">
@@ -11781,16 +11820,16 @@
       <c r="E158" s="6" t="s">
         <v>1127</v>
       </c>
-      <c r="F158" s="40" t="s">
+      <c r="F158" s="6" t="s">
         <v>1628</v>
       </c>
-      <c r="G158" s="41">
-        <v>46212</v>
-      </c>
-      <c r="H158" s="42" t="s">
+      <c r="G158" s="2">
+        <v>46212</v>
+      </c>
+      <c r="H158" s="39" t="s">
         <v>1483</v>
       </c>
-      <c r="I158" s="37" t="s">
+      <c r="I158" t="s">
         <v>1629</v>
       </c>
     </row>
@@ -11801,7 +11840,7 @@
       <c r="B159" t="s">
         <v>941</v>
       </c>
-      <c r="C159" s="37" t="s">
+      <c r="C159" t="s">
         <v>1497</v>
       </c>
       <c r="D159" s="6" t="s">
@@ -11810,16 +11849,16 @@
       <c r="E159" s="6" t="s">
         <v>1128</v>
       </c>
-      <c r="F159" s="40" t="s">
+      <c r="F159" s="6" t="s">
         <v>1630</v>
       </c>
-      <c r="G159" s="41">
-        <v>46212</v>
-      </c>
-      <c r="H159" s="42" t="s">
+      <c r="G159" s="2">
+        <v>46212</v>
+      </c>
+      <c r="H159" s="39" t="s">
         <v>1503</v>
       </c>
-      <c r="I159" s="37" t="s">
+      <c r="I159" t="s">
         <v>1631</v>
       </c>
     </row>
@@ -11830,7 +11869,7 @@
       <c r="B160" t="s">
         <v>942</v>
       </c>
-      <c r="C160" s="37" t="s">
+      <c r="C160" t="s">
         <v>1456</v>
       </c>
       <c r="D160" s="6" t="s">
@@ -11839,16 +11878,16 @@
       <c r="E160" s="6" t="s">
         <v>1129</v>
       </c>
-      <c r="F160" s="40" t="s">
+      <c r="F160" s="6" t="s">
         <v>1632</v>
       </c>
-      <c r="G160" s="41">
-        <v>46212</v>
-      </c>
-      <c r="H160" s="42" t="s">
+      <c r="G160" s="2">
+        <v>46212</v>
+      </c>
+      <c r="H160" s="39" t="s">
         <v>1633</v>
       </c>
-      <c r="I160" s="37" t="s">
+      <c r="I160" t="s">
         <v>1634</v>
       </c>
     </row>
@@ -11859,7 +11898,7 @@
       <c r="B161" t="s">
         <v>943</v>
       </c>
-      <c r="C161" s="37" t="s">
+      <c r="C161" t="s">
         <v>1463</v>
       </c>
       <c r="D161" s="6" t="s">
@@ -11868,16 +11907,16 @@
       <c r="E161" s="6" t="s">
         <v>1130</v>
       </c>
-      <c r="F161" s="40" t="s">
+      <c r="F161" s="6" t="s">
         <v>1635</v>
       </c>
-      <c r="G161" s="41">
-        <v>46212</v>
-      </c>
-      <c r="H161" s="42" t="s">
+      <c r="G161" s="2">
+        <v>46212</v>
+      </c>
+      <c r="H161" s="39" t="s">
         <v>1636</v>
       </c>
-      <c r="I161" s="37" t="s">
+      <c r="I161" t="s">
         <v>1637</v>
       </c>
     </row>
@@ -11888,7 +11927,7 @@
       <c r="B162" t="s">
         <v>944</v>
       </c>
-      <c r="C162" s="37" t="s">
+      <c r="C162" t="s">
         <v>1452</v>
       </c>
       <c r="D162" s="6" t="s">
@@ -11897,16 +11936,16 @@
       <c r="E162" s="6" t="s">
         <v>1131</v>
       </c>
-      <c r="F162" s="40" t="s">
+      <c r="F162" s="6" t="s">
         <v>1505</v>
       </c>
-      <c r="G162" s="41">
-        <v>46212</v>
-      </c>
-      <c r="H162" s="42" t="s">
+      <c r="G162" s="2">
+        <v>46212</v>
+      </c>
+      <c r="H162" s="39" t="s">
         <v>1578</v>
       </c>
-      <c r="I162" s="37" t="s">
+      <c r="I162" t="s">
         <v>1638</v>
       </c>
     </row>
@@ -11917,7 +11956,7 @@
       <c r="B163" t="s">
         <v>945</v>
       </c>
-      <c r="C163" s="37" t="s">
+      <c r="C163" t="s">
         <v>1463</v>
       </c>
       <c r="D163" s="6" t="s">
@@ -11926,16 +11965,16 @@
       <c r="E163" s="6" t="s">
         <v>1132</v>
       </c>
-      <c r="F163" s="40" t="s">
+      <c r="F163" s="6" t="s">
         <v>1639</v>
       </c>
-      <c r="G163" s="41">
-        <v>46212</v>
-      </c>
-      <c r="H163" s="42" t="s">
+      <c r="G163" s="2">
+        <v>46212</v>
+      </c>
+      <c r="H163" s="39" t="s">
         <v>1640</v>
       </c>
-      <c r="I163" s="37" t="s">
+      <c r="I163" t="s">
         <v>1641</v>
       </c>
     </row>
@@ -11946,7 +11985,7 @@
       <c r="B164" t="s">
         <v>946</v>
       </c>
-      <c r="C164" s="37" t="s">
+      <c r="C164" t="s">
         <v>1508</v>
       </c>
       <c r="D164" s="6" t="s">
@@ -11955,16 +11994,16 @@
       <c r="E164" s="6" t="s">
         <v>1133</v>
       </c>
-      <c r="F164" s="40" t="s">
+      <c r="F164" s="6" t="s">
         <v>1642</v>
       </c>
-      <c r="G164" s="41">
-        <v>46212</v>
-      </c>
-      <c r="H164" s="42" t="s">
+      <c r="G164" s="2">
+        <v>46212</v>
+      </c>
+      <c r="H164" s="39" t="s">
         <v>1643</v>
       </c>
-      <c r="I164" s="37" t="s">
+      <c r="I164" t="s">
         <v>1644</v>
       </c>
     </row>
@@ -11975,7 +12014,7 @@
       <c r="B165" t="s">
         <v>947</v>
       </c>
-      <c r="C165" s="37" t="s">
+      <c r="C165" t="s">
         <v>1448</v>
       </c>
       <c r="D165" s="6" t="s">
@@ -11984,16 +12023,16 @@
       <c r="E165" s="6" t="s">
         <v>1134</v>
       </c>
-      <c r="F165" s="40" t="s">
+      <c r="F165" s="6" t="s">
         <v>1645</v>
       </c>
-      <c r="G165" s="41">
-        <v>46212</v>
-      </c>
-      <c r="H165" s="42" t="s">
+      <c r="G165" s="2">
+        <v>46212</v>
+      </c>
+      <c r="H165" s="39" t="s">
         <v>1646</v>
       </c>
-      <c r="I165" s="37" t="s">
+      <c r="I165" t="s">
         <v>1647</v>
       </c>
     </row>
@@ -12004,7 +12043,7 @@
       <c r="B166" t="s">
         <v>948</v>
       </c>
-      <c r="C166" s="37" t="s">
+      <c r="C166" t="s">
         <v>1456</v>
       </c>
       <c r="D166" s="6" t="s">
@@ -12013,16 +12052,16 @@
       <c r="E166" s="6" t="s">
         <v>1135</v>
       </c>
-      <c r="F166" s="40" t="s">
+      <c r="F166" s="6" t="s">
         <v>1648</v>
       </c>
-      <c r="G166" s="41">
-        <v>46212</v>
-      </c>
-      <c r="H166" s="42" t="s">
+      <c r="G166" s="2">
+        <v>46212</v>
+      </c>
+      <c r="H166" s="39" t="s">
         <v>1649</v>
       </c>
-      <c r="I166" s="37" t="s">
+      <c r="I166" t="s">
         <v>1650</v>
       </c>
     </row>
@@ -12033,7 +12072,7 @@
       <c r="B167" t="s">
         <v>949</v>
       </c>
-      <c r="C167" s="37" t="s">
+      <c r="C167" t="s">
         <v>1456</v>
       </c>
       <c r="D167" s="6" t="s">
@@ -12042,16 +12081,16 @@
       <c r="E167" s="6" t="s">
         <v>1136</v>
       </c>
-      <c r="F167" s="40" t="s">
+      <c r="F167" s="6" t="s">
         <v>1651</v>
       </c>
-      <c r="G167" s="41">
-        <v>46212</v>
-      </c>
-      <c r="H167" s="42" t="s">
+      <c r="G167" s="2">
+        <v>46212</v>
+      </c>
+      <c r="H167" s="39" t="s">
         <v>1652</v>
       </c>
-      <c r="I167" s="37" t="s">
+      <c r="I167" t="s">
         <v>1653</v>
       </c>
     </row>
@@ -12062,7 +12101,7 @@
       <c r="B168" t="s">
         <v>950</v>
       </c>
-      <c r="C168" s="37" t="s">
+      <c r="C168" t="s">
         <v>1452</v>
       </c>
       <c r="D168" s="6" t="s">
@@ -12071,16 +12110,16 @@
       <c r="E168" s="6" t="s">
         <v>1137</v>
       </c>
-      <c r="F168" s="40" t="s">
+      <c r="F168" s="6" t="s">
         <v>1654</v>
       </c>
-      <c r="G168" s="41">
-        <v>46212</v>
-      </c>
-      <c r="H168" s="42" t="s">
+      <c r="G168" s="2">
+        <v>46212</v>
+      </c>
+      <c r="H168" s="39" t="s">
         <v>1655</v>
       </c>
-      <c r="I168" s="37" t="s">
+      <c r="I168" t="s">
         <v>1656</v>
       </c>
     </row>
@@ -12091,7 +12130,7 @@
       <c r="B169" t="s">
         <v>951</v>
       </c>
-      <c r="C169" s="37" t="s">
+      <c r="C169" t="s">
         <v>1565</v>
       </c>
       <c r="D169" s="6" t="s">
@@ -12100,16 +12139,16 @@
       <c r="E169" s="6" t="s">
         <v>1138</v>
       </c>
-      <c r="F169" s="40" t="s">
+      <c r="F169" s="6" t="s">
         <v>1657</v>
       </c>
-      <c r="G169" s="41">
-        <v>46212</v>
-      </c>
-      <c r="H169" s="42" t="s">
+      <c r="G169" s="2">
+        <v>46212</v>
+      </c>
+      <c r="H169" s="39" t="s">
         <v>1503</v>
       </c>
-      <c r="I169" s="37" t="s">
+      <c r="I169" t="s">
         <v>1658</v>
       </c>
     </row>
@@ -12120,7 +12159,7 @@
       <c r="B170" t="s">
         <v>952</v>
       </c>
-      <c r="C170" s="37" t="s">
+      <c r="C170" t="s">
         <v>1452</v>
       </c>
       <c r="D170" s="6" t="s">
@@ -12129,16 +12168,16 @@
       <c r="E170" s="6" t="s">
         <v>1139</v>
       </c>
-      <c r="F170" s="40" t="s">
+      <c r="F170" s="6" t="s">
         <v>1659</v>
       </c>
-      <c r="G170" s="41">
-        <v>46212</v>
-      </c>
-      <c r="H170" s="42" t="s">
+      <c r="G170" s="2">
+        <v>46212</v>
+      </c>
+      <c r="H170" s="39" t="s">
         <v>1468</v>
       </c>
-      <c r="I170" s="37" t="s">
+      <c r="I170" t="s">
         <v>1660</v>
       </c>
     </row>
@@ -12149,7 +12188,7 @@
       <c r="B171" t="s">
         <v>953</v>
       </c>
-      <c r="C171" s="37" t="s">
+      <c r="C171" t="s">
         <v>1501</v>
       </c>
       <c r="D171" s="6" t="s">
@@ -12158,16 +12197,16 @@
       <c r="E171" s="6" t="s">
         <v>1140</v>
       </c>
-      <c r="F171" s="40" t="s">
+      <c r="F171" s="6" t="s">
         <v>1663</v>
       </c>
-      <c r="G171" s="41">
-        <v>46212</v>
-      </c>
-      <c r="H171" s="42" t="s">
+      <c r="G171" s="2">
+        <v>46212</v>
+      </c>
+      <c r="H171" s="39" t="s">
         <v>354</v>
       </c>
-      <c r="I171" s="37" t="s">
+      <c r="I171" t="s">
         <v>1664</v>
       </c>
     </row>
@@ -12178,7 +12217,7 @@
       <c r="B172" t="s">
         <v>954</v>
       </c>
-      <c r="C172" s="37" t="s">
+      <c r="C172" t="s">
         <v>1452</v>
       </c>
       <c r="D172" s="6" t="s">
@@ -12187,16 +12226,16 @@
       <c r="E172" s="6" t="s">
         <v>1141</v>
       </c>
-      <c r="F172" s="40" t="s">
+      <c r="F172" s="6" t="s">
         <v>1665</v>
       </c>
-      <c r="G172" s="41">
-        <v>46212</v>
-      </c>
-      <c r="H172" s="42" t="s">
+      <c r="G172" s="2">
+        <v>46212</v>
+      </c>
+      <c r="H172" s="39" t="s">
         <v>1643</v>
       </c>
-      <c r="I172" s="37" t="s">
+      <c r="I172" t="s">
         <v>1666</v>
       </c>
     </row>
@@ -12207,7 +12246,7 @@
       <c r="B173" t="s">
         <v>955</v>
       </c>
-      <c r="C173" s="37" t="s">
+      <c r="C173" t="s">
         <v>1448</v>
       </c>
       <c r="D173" s="6" t="s">
@@ -12216,16 +12255,16 @@
       <c r="E173" s="6" t="s">
         <v>1142</v>
       </c>
-      <c r="F173" s="40" t="s">
+      <c r="F173" s="6" t="s">
         <v>1667</v>
       </c>
-      <c r="G173" s="41">
-        <v>46212</v>
-      </c>
-      <c r="H173" s="42" t="s">
+      <c r="G173" s="2">
+        <v>46212</v>
+      </c>
+      <c r="H173" s="39" t="s">
         <v>1586</v>
       </c>
-      <c r="I173" s="37" t="s">
+      <c r="I173" t="s">
         <v>1668</v>
       </c>
     </row>
@@ -12236,7 +12275,7 @@
       <c r="B174" t="s">
         <v>956</v>
       </c>
-      <c r="C174" s="37" t="s">
+      <c r="C174" t="s">
         <v>1463</v>
       </c>
       <c r="D174" s="6" t="s">
@@ -12245,16 +12284,16 @@
       <c r="E174" s="6" t="s">
         <v>1143</v>
       </c>
-      <c r="F174" s="40" t="s">
+      <c r="F174" s="6" t="s">
         <v>1669</v>
       </c>
-      <c r="G174" s="41">
-        <v>46212</v>
-      </c>
-      <c r="H174" s="42" t="s">
+      <c r="G174" s="2">
+        <v>46212</v>
+      </c>
+      <c r="H174" s="39" t="s">
         <v>1468</v>
       </c>
-      <c r="I174" s="37" t="s">
+      <c r="I174" t="s">
         <v>1670</v>
       </c>
     </row>
@@ -12265,7 +12304,7 @@
       <c r="B175" t="s">
         <v>957</v>
       </c>
-      <c r="C175" s="37" t="s">
+      <c r="C175" t="s">
         <v>1452</v>
       </c>
       <c r="D175" s="6" t="s">
@@ -12274,16 +12313,16 @@
       <c r="E175" s="6" t="s">
         <v>1144</v>
       </c>
-      <c r="F175" s="40" t="s">
+      <c r="F175" s="6" t="s">
         <v>1671</v>
       </c>
-      <c r="G175" s="41">
-        <v>46212</v>
-      </c>
-      <c r="H175" s="42" t="s">
+      <c r="G175" s="2">
+        <v>46212</v>
+      </c>
+      <c r="H175" s="39" t="s">
         <v>1672</v>
       </c>
-      <c r="I175" s="37" t="s">
+      <c r="I175" t="s">
         <v>1673</v>
       </c>
     </row>
@@ -12294,7 +12333,7 @@
       <c r="B176" t="s">
         <v>958</v>
       </c>
-      <c r="C176" s="37" t="s">
+      <c r="C176" t="s">
         <v>1456</v>
       </c>
       <c r="D176" s="6" t="s">
@@ -12303,16 +12342,16 @@
       <c r="E176" s="6" t="s">
         <v>1145</v>
       </c>
-      <c r="F176" s="40" t="s">
+      <c r="F176" s="6" t="s">
         <v>1674</v>
       </c>
-      <c r="G176" s="41">
-        <v>46212</v>
-      </c>
-      <c r="H176" s="42" t="s">
+      <c r="G176" s="2">
+        <v>46212</v>
+      </c>
+      <c r="H176" s="39" t="s">
         <v>1675</v>
       </c>
-      <c r="I176" s="37" t="s">
+      <c r="I176" t="s">
         <v>1676</v>
       </c>
     </row>
@@ -12323,7 +12362,7 @@
       <c r="B177" t="s">
         <v>959</v>
       </c>
-      <c r="C177" s="37" t="s">
+      <c r="C177" t="s">
         <v>1448</v>
       </c>
       <c r="D177" s="6" t="s">
@@ -12332,16 +12371,16 @@
       <c r="E177" s="6" t="s">
         <v>1146</v>
       </c>
-      <c r="F177" s="40" t="s">
+      <c r="F177" s="6" t="s">
         <v>1677</v>
       </c>
-      <c r="G177" s="41">
-        <v>46212</v>
-      </c>
-      <c r="H177" s="42" t="s">
+      <c r="G177" s="2">
+        <v>46212</v>
+      </c>
+      <c r="H177" s="39" t="s">
         <v>1678</v>
       </c>
-      <c r="I177" s="37" t="s">
+      <c r="I177" t="s">
         <v>1679</v>
       </c>
     </row>
@@ -12352,7 +12391,7 @@
       <c r="B178" t="s">
         <v>960</v>
       </c>
-      <c r="C178" s="37" t="s">
+      <c r="C178" t="s">
         <v>1497</v>
       </c>
       <c r="D178" s="6" t="s">
@@ -12361,16 +12400,16 @@
       <c r="E178" s="6" t="s">
         <v>1147</v>
       </c>
-      <c r="F178" s="40" t="s">
+      <c r="F178" s="6" t="s">
         <v>1680</v>
       </c>
-      <c r="G178" s="41">
-        <v>46212</v>
-      </c>
-      <c r="H178" s="42" t="s">
+      <c r="G178" s="2">
+        <v>46212</v>
+      </c>
+      <c r="H178" s="39" t="s">
         <v>1681</v>
       </c>
-      <c r="I178" s="37" t="s">
+      <c r="I178" t="s">
         <v>1682</v>
       </c>
     </row>
@@ -12381,7 +12420,7 @@
       <c r="B179" t="s">
         <v>961</v>
       </c>
-      <c r="C179" s="37" t="s">
+      <c r="C179" t="s">
         <v>1432</v>
       </c>
       <c r="D179" s="6" t="s">
@@ -12390,16 +12429,16 @@
       <c r="E179" s="6" t="s">
         <v>1148</v>
       </c>
-      <c r="F179" s="40" t="s">
+      <c r="F179" s="6" t="s">
         <v>1683</v>
       </c>
-      <c r="G179" s="41">
-        <v>46212</v>
-      </c>
-      <c r="H179" s="42" t="s">
+      <c r="G179" s="2">
+        <v>46212</v>
+      </c>
+      <c r="H179" s="39" t="s">
         <v>1684</v>
       </c>
-      <c r="I179" s="37" t="s">
+      <c r="I179" t="s">
         <v>1685</v>
       </c>
     </row>
@@ -12410,7 +12449,7 @@
       <c r="B180" t="s">
         <v>962</v>
       </c>
-      <c r="C180" s="37" t="s">
+      <c r="C180" t="s">
         <v>1456</v>
       </c>
       <c r="D180" s="6" t="s">
@@ -12419,16 +12458,16 @@
       <c r="E180" s="6" t="s">
         <v>1149</v>
       </c>
-      <c r="F180" s="40" t="s">
+      <c r="F180" s="6" t="s">
         <v>1686</v>
       </c>
-      <c r="G180" s="41">
-        <v>46212</v>
-      </c>
-      <c r="H180" s="42" t="s">
+      <c r="G180" s="2">
+        <v>46212</v>
+      </c>
+      <c r="H180" s="39" t="s">
         <v>1687</v>
       </c>
-      <c r="I180" s="37" t="s">
+      <c r="I180" t="s">
         <v>1688</v>
       </c>
     </row>
@@ -12439,7 +12478,7 @@
       <c r="B181" t="s">
         <v>963</v>
       </c>
-      <c r="C181" s="37" t="s">
+      <c r="C181" t="s">
         <v>1456</v>
       </c>
       <c r="D181" s="6" t="s">
@@ -12448,16 +12487,16 @@
       <c r="E181" s="6" t="s">
         <v>1150</v>
       </c>
-      <c r="F181" s="40" t="s">
+      <c r="F181" s="6" t="s">
         <v>1689</v>
       </c>
-      <c r="G181" s="41">
-        <v>46212</v>
-      </c>
-      <c r="H181" s="42" t="s">
+      <c r="G181" s="2">
+        <v>46212</v>
+      </c>
+      <c r="H181" s="39" t="s">
         <v>1489</v>
       </c>
-      <c r="I181" s="37" t="s">
+      <c r="I181" t="s">
         <v>1690</v>
       </c>
     </row>
@@ -12468,7 +12507,7 @@
       <c r="B182" t="s">
         <v>964</v>
       </c>
-      <c r="C182" s="37" t="s">
+      <c r="C182" t="s">
         <v>1463</v>
       </c>
       <c r="D182" s="6" t="s">
@@ -12477,16 +12516,16 @@
       <c r="E182" s="6" t="s">
         <v>1151</v>
       </c>
-      <c r="F182" s="40" t="s">
+      <c r="F182" s="6" t="s">
         <v>1691</v>
       </c>
-      <c r="G182" s="41">
-        <v>46212</v>
-      </c>
-      <c r="H182" s="42" t="s">
+      <c r="G182" s="2">
+        <v>46212</v>
+      </c>
+      <c r="H182" s="39" t="s">
         <v>1692</v>
       </c>
-      <c r="I182" s="37" t="s">
+      <c r="I182" t="s">
         <v>1693</v>
       </c>
     </row>
@@ -12497,7 +12536,7 @@
       <c r="B183" t="s">
         <v>965</v>
       </c>
-      <c r="C183" s="37" t="s">
+      <c r="C183" t="s">
         <v>1456</v>
       </c>
       <c r="D183" s="6" t="s">
@@ -12506,16 +12545,16 @@
       <c r="E183" s="6" t="s">
         <v>1152</v>
       </c>
-      <c r="F183" s="40" t="s">
+      <c r="F183" s="6" t="s">
         <v>1694</v>
       </c>
-      <c r="G183" s="41">
-        <v>46212</v>
-      </c>
-      <c r="H183" s="42" t="s">
+      <c r="G183" s="2">
+        <v>46212</v>
+      </c>
+      <c r="H183" s="39" t="s">
         <v>1695</v>
       </c>
-      <c r="I183" s="37" t="s">
+      <c r="I183" t="s">
         <v>1696</v>
       </c>
     </row>
@@ -12526,7 +12565,7 @@
       <c r="B184" t="s">
         <v>966</v>
       </c>
-      <c r="C184" s="37" t="s">
+      <c r="C184" t="s">
         <v>1456</v>
       </c>
       <c r="D184" s="6" t="s">
@@ -12535,16 +12574,16 @@
       <c r="E184" s="6" t="s">
         <v>1153</v>
       </c>
-      <c r="F184" s="40" t="s">
+      <c r="F184" s="6" t="s">
         <v>1697</v>
       </c>
-      <c r="G184" s="41">
-        <v>46212</v>
-      </c>
-      <c r="H184" s="42" t="s">
+      <c r="G184" s="2">
+        <v>46212</v>
+      </c>
+      <c r="H184" s="39" t="s">
         <v>1698</v>
       </c>
-      <c r="I184" s="37" t="s">
+      <c r="I184" t="s">
         <v>1699</v>
       </c>
     </row>
@@ -12555,7 +12594,7 @@
       <c r="B185" t="s">
         <v>967</v>
       </c>
-      <c r="C185" s="37" t="s">
+      <c r="C185" t="s">
         <v>1456</v>
       </c>
       <c r="D185" s="6" t="s">
@@ -12564,16 +12603,16 @@
       <c r="E185" s="6" t="s">
         <v>1154</v>
       </c>
-      <c r="F185" s="40" t="s">
+      <c r="F185" s="6" t="s">
         <v>1700</v>
       </c>
-      <c r="G185" s="41">
-        <v>46212</v>
-      </c>
-      <c r="H185" s="42" t="s">
+      <c r="G185" s="2">
+        <v>46212</v>
+      </c>
+      <c r="H185" s="39" t="s">
         <v>1578</v>
       </c>
-      <c r="I185" s="37" t="s">
+      <c r="I185" t="s">
         <v>1701</v>
       </c>
     </row>
@@ -12584,7 +12623,7 @@
       <c r="B186" t="s">
         <v>968</v>
       </c>
-      <c r="C186" s="37" t="s">
+      <c r="C186" t="s">
         <v>1448</v>
       </c>
       <c r="D186" s="6" t="s">
@@ -12593,16 +12632,16 @@
       <c r="E186" s="6" t="s">
         <v>1155</v>
       </c>
-      <c r="F186" s="40" t="s">
+      <c r="F186" s="6" t="s">
         <v>1702</v>
       </c>
-      <c r="G186" s="41">
-        <v>46212</v>
-      </c>
-      <c r="H186" s="42" t="s">
+      <c r="G186" s="2">
+        <v>46212</v>
+      </c>
+      <c r="H186" s="39" t="s">
         <v>1662</v>
       </c>
-      <c r="I186" s="37" t="s">
+      <c r="I186" t="s">
         <v>1703</v>
       </c>
     </row>
@@ -12613,7 +12652,7 @@
       <c r="B187" t="s">
         <v>969</v>
       </c>
-      <c r="C187" s="37" t="s">
+      <c r="C187" t="s">
         <v>1497</v>
       </c>
       <c r="D187" s="6" t="s">
@@ -12622,16 +12661,16 @@
       <c r="E187" s="6" t="s">
         <v>1156</v>
       </c>
-      <c r="F187" s="40" t="s">
+      <c r="F187" s="6" t="s">
         <v>1704</v>
       </c>
-      <c r="G187" s="41">
-        <v>46212</v>
-      </c>
-      <c r="H187" s="42" t="s">
+      <c r="G187" s="2">
+        <v>46212</v>
+      </c>
+      <c r="H187" s="39" t="s">
         <v>344</v>
       </c>
-      <c r="I187" s="37" t="s">
+      <c r="I187" t="s">
         <v>1705</v>
       </c>
     </row>
@@ -12642,7 +12681,7 @@
       <c r="B188" t="s">
         <v>970</v>
       </c>
-      <c r="C188" s="37" t="s">
+      <c r="C188" t="s">
         <v>1501</v>
       </c>
       <c r="D188" s="6" t="s">
@@ -12651,16 +12690,16 @@
       <c r="E188" s="6" t="s">
         <v>1077</v>
       </c>
-      <c r="F188" s="40" t="s">
+      <c r="F188" s="6" t="s">
         <v>1485</v>
       </c>
-      <c r="G188" s="41">
-        <v>46212</v>
-      </c>
-      <c r="H188" s="42" t="s">
+      <c r="G188" s="2">
+        <v>46212</v>
+      </c>
+      <c r="H188" s="39" t="s">
         <v>1706</v>
       </c>
-      <c r="I188" s="37" t="s">
+      <c r="I188" t="s">
         <v>1707</v>
       </c>
     </row>
@@ -12671,7 +12710,7 @@
       <c r="B189" t="s">
         <v>971</v>
       </c>
-      <c r="C189" s="37" t="s">
+      <c r="C189" t="s">
         <v>1463</v>
       </c>
       <c r="D189" s="6" t="s">
@@ -12680,16 +12719,16 @@
       <c r="E189" s="6" t="s">
         <v>1157</v>
       </c>
-      <c r="F189" s="40" t="s">
+      <c r="F189" s="6" t="s">
         <v>1708</v>
       </c>
-      <c r="G189" s="41">
-        <v>46212</v>
-      </c>
-      <c r="H189" s="42" t="s">
+      <c r="G189" s="2">
+        <v>46212</v>
+      </c>
+      <c r="H189" s="39" t="s">
         <v>1578</v>
       </c>
-      <c r="I189" s="37" t="s">
+      <c r="I189" t="s">
         <v>1709</v>
       </c>
     </row>
@@ -12700,7 +12739,7 @@
       <c r="B190" t="s">
         <v>972</v>
       </c>
-      <c r="C190" s="37" t="s">
+      <c r="C190" t="s">
         <v>1710</v>
       </c>
       <c r="D190" s="6" t="s">
@@ -12709,16 +12748,16 @@
       <c r="E190" s="6" t="s">
         <v>1158</v>
       </c>
-      <c r="F190" s="40" t="s">
+      <c r="F190" s="6" t="s">
         <v>1711</v>
       </c>
-      <c r="G190" s="41">
-        <v>46212</v>
-      </c>
-      <c r="H190" s="42" t="s">
+      <c r="G190" s="2">
+        <v>46212</v>
+      </c>
+      <c r="H190" s="39" t="s">
         <v>1712</v>
       </c>
-      <c r="I190" s="37" t="s">
+      <c r="I190" t="s">
         <v>1713</v>
       </c>
     </row>
@@ -12729,7 +12768,7 @@
       <c r="B191" t="s">
         <v>973</v>
       </c>
-      <c r="C191" s="37" t="s">
+      <c r="C191" t="s">
         <v>1463</v>
       </c>
       <c r="D191" s="6" t="s">
@@ -12738,16 +12777,16 @@
       <c r="E191" s="6" t="s">
         <v>1159</v>
       </c>
-      <c r="F191" s="40" t="s">
+      <c r="F191" s="6" t="s">
         <v>1714</v>
       </c>
-      <c r="G191" s="41">
-        <v>46212</v>
-      </c>
-      <c r="H191" s="42" t="s">
+      <c r="G191" s="2">
+        <v>46212</v>
+      </c>
+      <c r="H191" s="39" t="s">
         <v>1715</v>
       </c>
-      <c r="I191" s="37" t="s">
+      <c r="I191" t="s">
         <v>1716</v>
       </c>
     </row>
@@ -12758,7 +12797,7 @@
       <c r="B192" t="s">
         <v>974</v>
       </c>
-      <c r="C192" s="37" t="s">
+      <c r="C192" t="s">
         <v>1463</v>
       </c>
       <c r="D192" s="6" t="s">
@@ -12767,16 +12806,16 @@
       <c r="E192" s="6" t="s">
         <v>1160</v>
       </c>
-      <c r="F192" s="40" t="s">
+      <c r="F192" s="6" t="s">
         <v>1717</v>
       </c>
-      <c r="G192" s="41">
-        <v>46212</v>
-      </c>
-      <c r="H192" s="42" t="s">
+      <c r="G192" s="2">
+        <v>46212</v>
+      </c>
+      <c r="H192" s="39" t="s">
         <v>1718</v>
       </c>
-      <c r="I192" s="37" t="s">
+      <c r="I192" t="s">
         <v>1719</v>
       </c>
     </row>
@@ -12787,7 +12826,7 @@
       <c r="B193" t="s">
         <v>975</v>
       </c>
-      <c r="C193" s="37" t="s">
+      <c r="C193" t="s">
         <v>1456</v>
       </c>
       <c r="D193" s="6" t="s">
@@ -12796,16 +12835,16 @@
       <c r="E193" s="6" t="s">
         <v>1161</v>
       </c>
-      <c r="F193" s="40" t="s">
+      <c r="F193" s="6" t="s">
         <v>1720</v>
       </c>
-      <c r="G193" s="41">
-        <v>46212</v>
-      </c>
-      <c r="H193" s="42" t="s">
+      <c r="G193" s="2">
+        <v>46212</v>
+      </c>
+      <c r="H193" s="39" t="s">
         <v>1721</v>
       </c>
-      <c r="I193" s="37" t="s">
+      <c r="I193" t="s">
         <v>1722</v>
       </c>
     </row>
@@ -12816,7 +12855,7 @@
       <c r="B194" t="s">
         <v>976</v>
       </c>
-      <c r="C194" s="37" t="s">
+      <c r="C194" t="s">
         <v>1456</v>
       </c>
       <c r="D194" s="6" t="s">
@@ -12825,16 +12864,16 @@
       <c r="E194" s="6" t="s">
         <v>1162</v>
       </c>
-      <c r="F194" s="40" t="s">
+      <c r="F194" s="6" t="s">
         <v>1723</v>
       </c>
-      <c r="G194" s="41">
-        <v>46212</v>
-      </c>
-      <c r="H194" s="42" t="s">
+      <c r="G194" s="2">
+        <v>46212</v>
+      </c>
+      <c r="H194" s="39" t="s">
         <v>1724</v>
       </c>
-      <c r="I194" s="37" t="s">
+      <c r="I194" t="s">
         <v>1725</v>
       </c>
     </row>
@@ -12845,7 +12884,7 @@
       <c r="B195" t="s">
         <v>977</v>
       </c>
-      <c r="C195" s="37" t="s">
+      <c r="C195" t="s">
         <v>1463</v>
       </c>
       <c r="D195" s="6" t="s">
@@ -12854,16 +12893,16 @@
       <c r="E195" s="6" t="s">
         <v>1163</v>
       </c>
-      <c r="F195" s="40" t="s">
+      <c r="F195" s="6" t="s">
         <v>1726</v>
       </c>
-      <c r="G195" s="41">
-        <v>46212</v>
-      </c>
-      <c r="H195" s="42" t="s">
+      <c r="G195" s="2">
+        <v>46212</v>
+      </c>
+      <c r="H195" s="39" t="s">
         <v>1727</v>
       </c>
-      <c r="I195" s="37" t="s">
+      <c r="I195" t="s">
         <v>1728</v>
       </c>
     </row>
@@ -12874,7 +12913,7 @@
       <c r="B196" t="s">
         <v>978</v>
       </c>
-      <c r="C196" s="37" t="s">
+      <c r="C196" t="s">
         <v>1463</v>
       </c>
       <c r="D196" s="6" t="s">
@@ -12883,16 +12922,16 @@
       <c r="E196" s="6" t="s">
         <v>1164</v>
       </c>
-      <c r="F196" s="40" t="s">
+      <c r="F196" s="6" t="s">
         <v>1505</v>
       </c>
-      <c r="G196" s="41">
-        <v>46212</v>
-      </c>
-      <c r="H196" s="42" t="s">
+      <c r="G196" s="2">
+        <v>46212</v>
+      </c>
+      <c r="H196" s="39" t="s">
         <v>1729</v>
       </c>
-      <c r="I196" s="37" t="s">
+      <c r="I196" t="s">
         <v>1730</v>
       </c>
     </row>
@@ -12903,7 +12942,7 @@
       <c r="B197" t="s">
         <v>979</v>
       </c>
-      <c r="C197" s="37" t="s">
+      <c r="C197" t="s">
         <v>1448</v>
       </c>
       <c r="D197" s="6" t="s">
@@ -12912,16 +12951,16 @@
       <c r="E197" s="6" t="s">
         <v>1165</v>
       </c>
-      <c r="F197" s="40" t="s">
+      <c r="F197" s="6" t="s">
         <v>1731</v>
       </c>
-      <c r="G197" s="41">
-        <v>46212</v>
-      </c>
-      <c r="H197" s="42" t="s">
+      <c r="G197" s="2">
+        <v>46212</v>
+      </c>
+      <c r="H197" s="39" t="s">
         <v>1636</v>
       </c>
-      <c r="I197" s="37" t="s">
+      <c r="I197" t="s">
         <v>1732</v>
       </c>
     </row>
@@ -12932,7 +12971,7 @@
       <c r="B198" t="s">
         <v>980</v>
       </c>
-      <c r="C198" s="37" t="s">
+      <c r="C198" t="s">
         <v>1448</v>
       </c>
       <c r="D198" s="6" t="s">
@@ -12941,16 +12980,16 @@
       <c r="E198" s="6" t="s">
         <v>1166</v>
       </c>
-      <c r="F198" s="40" t="s">
+      <c r="F198" s="6" t="s">
         <v>1733</v>
       </c>
-      <c r="G198" s="41">
-        <v>46212</v>
-      </c>
-      <c r="H198" s="42" t="s">
+      <c r="G198" s="2">
+        <v>46212</v>
+      </c>
+      <c r="H198" s="39" t="s">
         <v>1734</v>
       </c>
-      <c r="I198" s="37" t="s">
+      <c r="I198" t="s">
         <v>1735</v>
       </c>
     </row>
@@ -12961,7 +13000,7 @@
       <c r="B199" t="s">
         <v>981</v>
       </c>
-      <c r="C199" s="37" t="s">
+      <c r="C199" t="s">
         <v>1448</v>
       </c>
       <c r="D199" s="6" t="s">
@@ -12970,16 +13009,16 @@
       <c r="E199" s="6" t="s">
         <v>1167</v>
       </c>
-      <c r="F199" s="40" t="s">
+      <c r="F199" s="6" t="s">
         <v>1736</v>
       </c>
-      <c r="G199" s="41">
-        <v>46212</v>
-      </c>
-      <c r="H199" s="42" t="s">
+      <c r="G199" s="2">
+        <v>46212</v>
+      </c>
+      <c r="H199" s="39" t="s">
         <v>1649</v>
       </c>
-      <c r="I199" s="37" t="s">
+      <c r="I199" t="s">
         <v>1737</v>
       </c>
     </row>
@@ -12990,7 +13029,7 @@
       <c r="B200" t="s">
         <v>982</v>
       </c>
-      <c r="C200" s="37" t="s">
+      <c r="C200" t="s">
         <v>1463</v>
       </c>
       <c r="D200" s="6" t="s">
@@ -12999,16 +13038,16 @@
       <c r="E200" s="6" t="s">
         <v>1168</v>
       </c>
-      <c r="F200" s="40" t="s">
+      <c r="F200" s="6" t="s">
         <v>1738</v>
       </c>
-      <c r="G200" s="41">
-        <v>46212</v>
-      </c>
-      <c r="H200" s="42" t="s">
+      <c r="G200" s="2">
+        <v>46212</v>
+      </c>
+      <c r="H200" s="39" t="s">
         <v>1509</v>
       </c>
-      <c r="I200" s="37" t="s">
+      <c r="I200" t="s">
         <v>1739</v>
       </c>
     </row>
@@ -13019,7 +13058,7 @@
       <c r="B201" t="s">
         <v>983</v>
       </c>
-      <c r="C201" s="37" t="s">
+      <c r="C201" t="s">
         <v>1444</v>
       </c>
       <c r="D201" s="6" t="s">
@@ -13028,16 +13067,16 @@
       <c r="E201" s="6" t="s">
         <v>1169</v>
       </c>
-      <c r="F201" s="40" t="s">
+      <c r="F201" s="6" t="s">
         <v>1740</v>
       </c>
-      <c r="G201" s="41">
-        <v>46212</v>
-      </c>
-      <c r="H201" s="42" t="s">
+      <c r="G201" s="2">
+        <v>46212</v>
+      </c>
+      <c r="H201" s="39" t="s">
         <v>1741</v>
       </c>
-      <c r="I201" s="37" t="s">
+      <c r="I201" t="s">
         <v>1742</v>
       </c>
     </row>
@@ -13048,7 +13087,7 @@
       <c r="B202" t="s">
         <v>984</v>
       </c>
-      <c r="C202" s="37" t="s">
+      <c r="C202" t="s">
         <v>1452</v>
       </c>
       <c r="D202" s="6" t="s">
@@ -13057,16 +13096,16 @@
       <c r="E202" s="6" t="s">
         <v>1170</v>
       </c>
-      <c r="F202" s="40" t="s">
+      <c r="F202" s="6" t="s">
         <v>1743</v>
       </c>
-      <c r="G202" s="41">
-        <v>46212</v>
-      </c>
-      <c r="H202" s="42" t="s">
+      <c r="G202" s="2">
+        <v>46212</v>
+      </c>
+      <c r="H202" s="39" t="s">
         <v>354</v>
       </c>
-      <c r="I202" s="37" t="s">
+      <c r="I202" t="s">
         <v>1744</v>
       </c>
     </row>
@@ -13077,7 +13116,7 @@
       <c r="B203" t="s">
         <v>985</v>
       </c>
-      <c r="C203" s="37" t="s">
+      <c r="C203" t="s">
         <v>1448</v>
       </c>
       <c r="D203" s="6" t="s">
@@ -13086,16 +13125,16 @@
       <c r="E203" s="6" t="s">
         <v>1171</v>
       </c>
-      <c r="F203" s="40" t="s">
+      <c r="F203" s="6" t="s">
         <v>1745</v>
       </c>
-      <c r="G203" s="41">
-        <v>46212</v>
-      </c>
-      <c r="H203" s="42" t="s">
+      <c r="G203" s="2">
+        <v>46212</v>
+      </c>
+      <c r="H203" s="39" t="s">
         <v>343</v>
       </c>
-      <c r="I203" s="37" t="s">
+      <c r="I203" t="s">
         <v>1746</v>
       </c>
     </row>
@@ -13106,7 +13145,7 @@
       <c r="B204" t="s">
         <v>986</v>
       </c>
-      <c r="C204" s="37" t="s">
+      <c r="C204" t="s">
         <v>1448</v>
       </c>
       <c r="D204" s="6" t="s">
@@ -13115,16 +13154,16 @@
       <c r="E204" s="6" t="s">
         <v>1172</v>
       </c>
-      <c r="F204" s="40" t="s">
+      <c r="F204" s="6" t="s">
         <v>1747</v>
       </c>
-      <c r="G204" s="41">
-        <v>46212</v>
-      </c>
-      <c r="H204" s="42" t="s">
+      <c r="G204" s="2">
+        <v>46212</v>
+      </c>
+      <c r="H204" s="39" t="s">
         <v>1748</v>
       </c>
-      <c r="I204" s="37" t="s">
+      <c r="I204" t="s">
         <v>1749</v>
       </c>
     </row>
@@ -13135,7 +13174,7 @@
       <c r="B205" t="s">
         <v>987</v>
       </c>
-      <c r="C205" s="37" t="s">
+      <c r="C205" t="s">
         <v>1440</v>
       </c>
       <c r="D205" s="6" t="s">
@@ -13144,16 +13183,16 @@
       <c r="E205" s="6" t="s">
         <v>1173</v>
       </c>
-      <c r="F205" s="40" t="s">
+      <c r="F205" s="6" t="s">
         <v>1750</v>
       </c>
-      <c r="G205" s="41">
-        <v>46212</v>
-      </c>
-      <c r="H205" s="42" t="s">
+      <c r="G205" s="2">
+        <v>46212</v>
+      </c>
+      <c r="H205" s="39" t="s">
         <v>1578</v>
       </c>
-      <c r="I205" s="37" t="s">
+      <c r="I205" t="s">
         <v>1751</v>
       </c>
     </row>
@@ -13164,7 +13203,7 @@
       <c r="B206" t="s">
         <v>988</v>
       </c>
-      <c r="C206" s="37" t="s">
+      <c r="C206" t="s">
         <v>1436</v>
       </c>
       <c r="D206" s="6" t="s">
@@ -13173,16 +13212,16 @@
       <c r="E206" s="6" t="s">
         <v>1174</v>
       </c>
-      <c r="F206" s="40" t="s">
+      <c r="F206" s="6" t="s">
         <v>1752</v>
       </c>
-      <c r="G206" s="41">
-        <v>46212</v>
-      </c>
-      <c r="H206" s="42" t="s">
+      <c r="G206" s="2">
+        <v>46212</v>
+      </c>
+      <c r="H206" s="39" t="s">
         <v>1438</v>
       </c>
-      <c r="I206" s="37" t="s">
+      <c r="I206" t="s">
         <v>1753</v>
       </c>
     </row>
@@ -13193,7 +13232,7 @@
       <c r="B207" t="s">
         <v>989</v>
       </c>
-      <c r="C207" s="37" t="s">
+      <c r="C207" t="s">
         <v>1456</v>
       </c>
       <c r="D207" s="6" t="s">
@@ -13202,16 +13241,16 @@
       <c r="E207" s="6" t="s">
         <v>1175</v>
       </c>
-      <c r="F207" s="40" t="s">
+      <c r="F207" s="6" t="s">
         <v>1754</v>
       </c>
-      <c r="G207" s="41">
-        <v>46212</v>
-      </c>
-      <c r="H207" s="42" t="s">
+      <c r="G207" s="2">
+        <v>46212</v>
+      </c>
+      <c r="H207" s="39" t="s">
         <v>1755</v>
       </c>
-      <c r="I207" s="37" t="s">
+      <c r="I207" t="s">
         <v>1756</v>
       </c>
     </row>
@@ -13222,7 +13261,7 @@
       <c r="B208" t="s">
         <v>990</v>
       </c>
-      <c r="C208" s="37" t="s">
+      <c r="C208" t="s">
         <v>1452</v>
       </c>
       <c r="D208" s="6" t="s">
@@ -13231,16 +13270,16 @@
       <c r="E208" s="6" t="s">
         <v>1176</v>
       </c>
-      <c r="F208" s="40" t="s">
+      <c r="F208" s="6" t="s">
         <v>1757</v>
       </c>
-      <c r="G208" s="41">
-        <v>46212</v>
-      </c>
-      <c r="H208" s="42" t="s">
+      <c r="G208" s="2">
+        <v>46212</v>
+      </c>
+      <c r="H208" s="39" t="s">
         <v>1758</v>
       </c>
-      <c r="I208" s="37" t="s">
+      <c r="I208" t="s">
         <v>1759</v>
       </c>
     </row>
@@ -13251,7 +13290,7 @@
       <c r="B209" t="s">
         <v>991</v>
       </c>
-      <c r="C209" s="37" t="s">
+      <c r="C209" t="s">
         <v>1463</v>
       </c>
       <c r="D209" s="6" t="s">
@@ -13260,16 +13299,16 @@
       <c r="E209" s="6" t="s">
         <v>1177</v>
       </c>
-      <c r="F209" s="40" t="s">
+      <c r="F209" s="6" t="s">
         <v>1760</v>
       </c>
-      <c r="G209" s="41">
-        <v>46212</v>
-      </c>
-      <c r="H209" s="42" t="s">
+      <c r="G209" s="2">
+        <v>46212</v>
+      </c>
+      <c r="H209" s="39" t="s">
         <v>1477</v>
       </c>
-      <c r="I209" s="37" t="s">
+      <c r="I209" t="s">
         <v>1761</v>
       </c>
     </row>
@@ -13280,7 +13319,7 @@
       <c r="B210" t="s">
         <v>992</v>
       </c>
-      <c r="C210" s="37" t="s">
+      <c r="C210" t="s">
         <v>1456</v>
       </c>
       <c r="D210" s="6" t="s">
@@ -13289,16 +13328,16 @@
       <c r="E210" s="6" t="s">
         <v>1178</v>
       </c>
-      <c r="F210" s="40" t="s">
+      <c r="F210" s="6" t="s">
         <v>1762</v>
       </c>
-      <c r="G210" s="41">
-        <v>46212</v>
-      </c>
-      <c r="H210" s="42" t="s">
+      <c r="G210" s="2">
+        <v>46212</v>
+      </c>
+      <c r="H210" s="39" t="s">
         <v>1763</v>
       </c>
-      <c r="I210" s="37" t="s">
+      <c r="I210" t="s">
         <v>1764</v>
       </c>
     </row>
@@ -13309,7 +13348,7 @@
       <c r="B211" t="s">
         <v>993</v>
       </c>
-      <c r="C211" s="37" t="s">
+      <c r="C211" t="s">
         <v>1456</v>
       </c>
       <c r="D211" s="6" t="s">
@@ -13318,16 +13357,16 @@
       <c r="E211" s="6" t="s">
         <v>1179</v>
       </c>
-      <c r="F211" s="40" t="s">
+      <c r="F211" s="6" t="s">
         <v>1765</v>
       </c>
-      <c r="G211" s="41">
-        <v>46212</v>
-      </c>
-      <c r="H211" s="42" t="s">
+      <c r="G211" s="2">
+        <v>46212</v>
+      </c>
+      <c r="H211" s="39" t="s">
         <v>1766</v>
       </c>
-      <c r="I211" s="37" t="s">
+      <c r="I211" t="s">
         <v>1767</v>
       </c>
     </row>
@@ -13338,7 +13377,7 @@
       <c r="B212" t="s">
         <v>994</v>
       </c>
-      <c r="C212" s="37" t="s">
+      <c r="C212" t="s">
         <v>1448</v>
       </c>
       <c r="D212" s="6" t="s">
@@ -13347,16 +13386,16 @@
       <c r="E212" s="6" t="s">
         <v>1181</v>
       </c>
-      <c r="F212" s="40" t="s">
+      <c r="F212" s="6" t="s">
         <v>1769</v>
       </c>
-      <c r="G212" s="41">
-        <v>46212</v>
-      </c>
-      <c r="H212" s="42" t="s">
+      <c r="G212" s="2">
+        <v>46212</v>
+      </c>
+      <c r="H212" s="39" t="s">
         <v>1770</v>
       </c>
-      <c r="I212" s="37" t="s">
+      <c r="I212" t="s">
         <v>1771</v>
       </c>
     </row>
@@ -13367,7 +13406,7 @@
       <c r="B213" t="s">
         <v>995</v>
       </c>
-      <c r="C213" s="37" t="s">
+      <c r="C213" t="s">
         <v>1452</v>
       </c>
       <c r="D213" s="6" t="s">
@@ -13376,16 +13415,16 @@
       <c r="E213" s="6" t="s">
         <v>1182</v>
       </c>
-      <c r="F213" s="40" t="s">
+      <c r="F213" s="6" t="s">
         <v>1772</v>
       </c>
-      <c r="G213" s="41">
-        <v>46212</v>
-      </c>
-      <c r="H213" s="42" t="s">
+      <c r="G213" s="2">
+        <v>46212</v>
+      </c>
+      <c r="H213" s="39" t="s">
         <v>1578</v>
       </c>
-      <c r="I213" s="37" t="s">
+      <c r="I213" t="s">
         <v>1773</v>
       </c>
     </row>
@@ -13396,7 +13435,7 @@
       <c r="B214" t="s">
         <v>996</v>
       </c>
-      <c r="C214" s="37" t="s">
+      <c r="C214" t="s">
         <v>1508</v>
       </c>
       <c r="D214" s="6" t="s">
@@ -13405,16 +13444,16 @@
       <c r="E214" s="6" t="s">
         <v>1183</v>
       </c>
-      <c r="F214" s="40" t="s">
+      <c r="F214" s="6" t="s">
         <v>1774</v>
       </c>
-      <c r="G214" s="41">
-        <v>46212</v>
-      </c>
-      <c r="H214" s="42" t="s">
+      <c r="G214" s="2">
+        <v>46212</v>
+      </c>
+      <c r="H214" s="39" t="s">
         <v>346</v>
       </c>
-      <c r="I214" s="37" t="s">
+      <c r="I214" t="s">
         <v>1775</v>
       </c>
     </row>
@@ -13425,7 +13464,7 @@
       <c r="B215" t="s">
         <v>997</v>
       </c>
-      <c r="C215" s="37" t="s">
+      <c r="C215" t="s">
         <v>1501</v>
       </c>
       <c r="D215" s="6" t="s">
@@ -13434,16 +13473,16 @@
       <c r="E215" s="6" t="s">
         <v>1180</v>
       </c>
-      <c r="F215" s="40" t="s">
+      <c r="F215" s="6" t="s">
         <v>1776</v>
       </c>
-      <c r="G215" s="41">
-        <v>46212</v>
-      </c>
-      <c r="H215" s="42" t="s">
+      <c r="G215" s="2">
+        <v>46212</v>
+      </c>
+      <c r="H215" s="39" t="s">
         <v>1777</v>
       </c>
-      <c r="I215" s="37" t="s">
+      <c r="I215" t="s">
         <v>1778</v>
       </c>
     </row>
@@ -13454,7 +13493,7 @@
       <c r="B216" t="s">
         <v>998</v>
       </c>
-      <c r="C216" s="37" t="s">
+      <c r="C216" t="s">
         <v>1448</v>
       </c>
       <c r="D216" s="6" t="s">
@@ -13463,16 +13502,16 @@
       <c r="E216" s="6" t="s">
         <v>1184</v>
       </c>
-      <c r="F216" s="40" t="s">
+      <c r="F216" s="6" t="s">
         <v>1779</v>
       </c>
-      <c r="G216" s="41">
-        <v>46212</v>
-      </c>
-      <c r="H216" s="42" t="s">
+      <c r="G216" s="2">
+        <v>46212</v>
+      </c>
+      <c r="H216" s="39" t="s">
         <v>1495</v>
       </c>
-      <c r="I216" s="37" t="s">
+      <c r="I216" t="s">
         <v>1780</v>
       </c>
     </row>
@@ -13483,7 +13522,7 @@
       <c r="B217" t="s">
         <v>999</v>
       </c>
-      <c r="C217" s="37" t="s">
+      <c r="C217" t="s">
         <v>1463</v>
       </c>
       <c r="D217" s="6" t="s">
@@ -13492,16 +13531,16 @@
       <c r="E217" s="6" t="s">
         <v>1185</v>
       </c>
-      <c r="F217" s="40" t="s">
+      <c r="F217" s="6" t="s">
         <v>1781</v>
       </c>
-      <c r="G217" s="41">
-        <v>46212</v>
-      </c>
-      <c r="H217" s="42" t="s">
+      <c r="G217" s="2">
+        <v>46212</v>
+      </c>
+      <c r="H217" s="39" t="s">
         <v>1782</v>
       </c>
-      <c r="I217" s="37" t="s">
+      <c r="I217" t="s">
         <v>1783</v>
       </c>
     </row>
@@ -13512,7 +13551,7 @@
       <c r="B218" t="s">
         <v>1000</v>
       </c>
-      <c r="C218" s="37" t="s">
+      <c r="C218" t="s">
         <v>1448</v>
       </c>
       <c r="D218" s="6" t="s">
@@ -13521,16 +13560,16 @@
       <c r="E218" s="6" t="s">
         <v>1186</v>
       </c>
-      <c r="F218" s="40" t="s">
+      <c r="F218" s="6" t="s">
         <v>1784</v>
       </c>
-      <c r="G218" s="41">
-        <v>46212</v>
-      </c>
-      <c r="H218" s="42" t="s">
+      <c r="G218" s="2">
+        <v>46212</v>
+      </c>
+      <c r="H218" s="39" t="s">
         <v>1785</v>
       </c>
-      <c r="I218" s="37" t="s">
+      <c r="I218" t="s">
         <v>1786</v>
       </c>
     </row>
@@ -13541,7 +13580,7 @@
       <c r="B219" t="s">
         <v>1001</v>
       </c>
-      <c r="C219" s="37" t="s">
+      <c r="C219" t="s">
         <v>1787</v>
       </c>
       <c r="D219" s="6" t="s">
@@ -13550,16 +13589,16 @@
       <c r="E219" s="6" t="s">
         <v>1187</v>
       </c>
-      <c r="F219" s="40" t="s">
+      <c r="F219" s="6" t="s">
         <v>1788</v>
       </c>
-      <c r="G219" s="41">
-        <v>46212</v>
-      </c>
-      <c r="H219" s="42" t="s">
+      <c r="G219" s="2">
+        <v>46212</v>
+      </c>
+      <c r="H219" s="39" t="s">
         <v>1789</v>
       </c>
-      <c r="I219" s="37" t="s">
+      <c r="I219" t="s">
         <v>1790</v>
       </c>
     </row>
@@ -13570,7 +13609,7 @@
       <c r="B220" t="s">
         <v>1002</v>
       </c>
-      <c r="C220" s="37" t="s">
+      <c r="C220" t="s">
         <v>1463</v>
       </c>
       <c r="D220" s="6" t="s">
@@ -13579,16 +13618,16 @@
       <c r="E220" s="6" t="s">
         <v>1188</v>
       </c>
-      <c r="F220" s="40" t="s">
+      <c r="F220" s="6" t="s">
         <v>1791</v>
       </c>
-      <c r="G220" s="41">
-        <v>46212</v>
-      </c>
-      <c r="H220" s="42" t="s">
+      <c r="G220" s="2">
+        <v>46212</v>
+      </c>
+      <c r="H220" s="39" t="s">
         <v>1550</v>
       </c>
-      <c r="I220" s="37" t="s">
+      <c r="I220" t="s">
         <v>1792</v>
       </c>
     </row>
@@ -13599,7 +13638,7 @@
       <c r="B221" t="s">
         <v>1003</v>
       </c>
-      <c r="C221" s="37" t="s">
+      <c r="C221" t="s">
         <v>1448</v>
       </c>
       <c r="D221" s="6" t="s">
@@ -13608,16 +13647,16 @@
       <c r="E221" s="6" t="s">
         <v>1189</v>
       </c>
-      <c r="F221" s="40" t="s">
+      <c r="F221" s="6" t="s">
         <v>1793</v>
       </c>
-      <c r="G221" s="41">
-        <v>46212</v>
-      </c>
-      <c r="H221" s="42" t="s">
+      <c r="G221" s="2">
+        <v>46212</v>
+      </c>
+      <c r="H221" s="39" t="s">
         <v>1794</v>
       </c>
-      <c r="I221" s="37" t="s">
+      <c r="I221" t="s">
         <v>1795</v>
       </c>
     </row>
@@ -13628,7 +13667,7 @@
       <c r="B222" t="s">
         <v>1004</v>
       </c>
-      <c r="C222" s="37" t="s">
+      <c r="C222" t="s">
         <v>1448</v>
       </c>
       <c r="D222" s="6" t="s">
@@ -13637,16 +13676,16 @@
       <c r="E222" s="6" t="s">
         <v>1190</v>
       </c>
-      <c r="F222" s="40" t="s">
+      <c r="F222" s="6" t="s">
         <v>1796</v>
       </c>
-      <c r="G222" s="41">
-        <v>46212</v>
-      </c>
-      <c r="H222" s="42" t="s">
+      <c r="G222" s="2">
+        <v>46212</v>
+      </c>
+      <c r="H222" s="39" t="s">
         <v>346</v>
       </c>
-      <c r="I222" s="37" t="s">
+      <c r="I222" t="s">
         <v>1797</v>
       </c>
     </row>
@@ -13657,7 +13696,7 @@
       <c r="B223" t="s">
         <v>1005</v>
       </c>
-      <c r="C223" s="37" t="s">
+      <c r="C223" t="s">
         <v>1456</v>
       </c>
       <c r="D223" s="6" t="s">
@@ -13666,16 +13705,16 @@
       <c r="E223" s="6" t="s">
         <v>1191</v>
       </c>
-      <c r="F223" s="40" t="s">
+      <c r="F223" s="6" t="s">
         <v>1798</v>
       </c>
-      <c r="G223" s="41">
-        <v>46212</v>
-      </c>
-      <c r="H223" s="42" t="s">
+      <c r="G223" s="2">
+        <v>46212</v>
+      </c>
+      <c r="H223" s="39" t="s">
         <v>1799</v>
       </c>
-      <c r="I223" s="37" t="s">
+      <c r="I223" t="s">
         <v>1800</v>
       </c>
     </row>
@@ -13686,7 +13725,7 @@
       <c r="B224" t="s">
         <v>1006</v>
       </c>
-      <c r="C224" s="37" t="s">
+      <c r="C224" t="s">
         <v>1452</v>
       </c>
       <c r="D224" s="6" t="s">
@@ -13695,16 +13734,16 @@
       <c r="E224" s="6" t="s">
         <v>1192</v>
       </c>
-      <c r="F224" s="40" t="s">
+      <c r="F224" s="6" t="s">
         <v>1801</v>
       </c>
-      <c r="G224" s="41">
-        <v>46212</v>
-      </c>
-      <c r="H224" s="42" t="s">
+      <c r="G224" s="2">
+        <v>46212</v>
+      </c>
+      <c r="H224" s="39" t="s">
         <v>1802</v>
       </c>
-      <c r="I224" s="37" t="s">
+      <c r="I224" t="s">
         <v>1803</v>
       </c>
     </row>
@@ -13715,7 +13754,7 @@
       <c r="B225" t="s">
         <v>1007</v>
       </c>
-      <c r="C225" s="37" t="s">
+      <c r="C225" t="s">
         <v>1444</v>
       </c>
       <c r="D225" s="6" t="s">
@@ -13724,16 +13763,16 @@
       <c r="E225" s="6" t="s">
         <v>1193</v>
       </c>
-      <c r="F225" s="40" t="s">
+      <c r="F225" s="6" t="s">
         <v>1804</v>
       </c>
-      <c r="G225" s="41">
-        <v>46212</v>
-      </c>
-      <c r="H225" s="42" t="s">
+      <c r="G225" s="2">
+        <v>46212</v>
+      </c>
+      <c r="H225" s="39" t="s">
         <v>1805</v>
       </c>
-      <c r="I225" s="37" t="s">
+      <c r="I225" t="s">
         <v>1806</v>
       </c>
     </row>
@@ -13744,7 +13783,7 @@
       <c r="B226" t="s">
         <v>1008</v>
       </c>
-      <c r="C226" s="37" t="s">
+      <c r="C226" t="s">
         <v>1501</v>
       </c>
       <c r="D226" s="6" t="s">
@@ -13753,16 +13792,16 @@
       <c r="E226" s="6" t="s">
         <v>1194</v>
       </c>
-      <c r="F226" s="40" t="s">
+      <c r="F226" s="6" t="s">
         <v>1807</v>
       </c>
-      <c r="G226" s="41">
-        <v>46212</v>
-      </c>
-      <c r="H226" s="42" t="s">
+      <c r="G226" s="2">
+        <v>46212</v>
+      </c>
+      <c r="H226" s="39" t="s">
         <v>1468</v>
       </c>
-      <c r="I226" s="37" t="s">
+      <c r="I226" t="s">
         <v>1808</v>
       </c>
     </row>
@@ -13773,7 +13812,7 @@
       <c r="B227" t="s">
         <v>1009</v>
       </c>
-      <c r="C227" s="37" t="s">
+      <c r="C227" t="s">
         <v>1452</v>
       </c>
       <c r="D227" s="6" t="s">
@@ -13782,16 +13821,16 @@
       <c r="E227" s="6" t="s">
         <v>1195</v>
       </c>
-      <c r="F227" s="40" t="s">
+      <c r="F227" s="6" t="s">
         <v>1704</v>
       </c>
-      <c r="G227" s="41">
-        <v>46212</v>
-      </c>
-      <c r="H227" s="42" t="s">
+      <c r="G227" s="2">
+        <v>46212</v>
+      </c>
+      <c r="H227" s="39" t="s">
         <v>1809</v>
       </c>
-      <c r="I227" s="37" t="s">
+      <c r="I227" t="s">
         <v>1810</v>
       </c>
     </row>
@@ -13802,7 +13841,7 @@
       <c r="B228" t="s">
         <v>1010</v>
       </c>
-      <c r="C228" s="37" t="s">
+      <c r="C228" t="s">
         <v>1448</v>
       </c>
       <c r="D228" s="6" t="s">
@@ -13811,16 +13850,16 @@
       <c r="E228" s="6" t="s">
         <v>1196</v>
       </c>
-      <c r="F228" s="40" t="s">
+      <c r="F228" s="6" t="s">
         <v>1811</v>
       </c>
-      <c r="G228" s="41">
-        <v>46212</v>
-      </c>
-      <c r="H228" s="42" t="s">
+      <c r="G228" s="2">
+        <v>46212</v>
+      </c>
+      <c r="H228" s="39" t="s">
         <v>1510</v>
       </c>
-      <c r="I228" s="37" t="s">
+      <c r="I228" t="s">
         <v>1812</v>
       </c>
     </row>
@@ -13831,7 +13870,7 @@
       <c r="B229" t="s">
         <v>1011</v>
       </c>
-      <c r="C229" s="37" t="s">
+      <c r="C229" t="s">
         <v>1463</v>
       </c>
       <c r="D229" s="6" t="s">
@@ -13840,16 +13879,16 @@
       <c r="E229" s="6" t="s">
         <v>1197</v>
       </c>
-      <c r="F229" s="40" t="s">
+      <c r="F229" s="6" t="s">
         <v>1813</v>
       </c>
-      <c r="G229" s="41">
-        <v>46212</v>
-      </c>
-      <c r="H229" s="42" t="s">
+      <c r="G229" s="2">
+        <v>46212</v>
+      </c>
+      <c r="H229" s="39" t="s">
         <v>1814</v>
       </c>
-      <c r="I229" s="37" t="s">
+      <c r="I229" t="s">
         <v>1815</v>
       </c>
     </row>
@@ -13860,7 +13899,7 @@
       <c r="B230" t="s">
         <v>1012</v>
       </c>
-      <c r="C230" s="37" t="s">
+      <c r="C230" t="s">
         <v>1436</v>
       </c>
       <c r="D230" s="6" t="s">
@@ -13869,16 +13908,16 @@
       <c r="E230" s="6" t="s">
         <v>1198</v>
       </c>
-      <c r="F230" s="40" t="s">
+      <c r="F230" s="6" t="s">
         <v>1816</v>
       </c>
-      <c r="G230" s="41">
-        <v>46212</v>
-      </c>
-      <c r="H230" s="42" t="s">
+      <c r="G230" s="2">
+        <v>46212</v>
+      </c>
+      <c r="H230" s="39" t="s">
         <v>1597</v>
       </c>
-      <c r="I230" s="37" t="s">
+      <c r="I230" t="s">
         <v>1817</v>
       </c>
     </row>
@@ -13889,7 +13928,7 @@
       <c r="B231" t="s">
         <v>1013</v>
       </c>
-      <c r="C231" s="37" t="s">
+      <c r="C231" t="s">
         <v>1463</v>
       </c>
       <c r="D231" s="6" t="s">
@@ -13898,16 +13937,16 @@
       <c r="E231" s="6" t="s">
         <v>1199</v>
       </c>
-      <c r="F231" s="40" t="s">
+      <c r="F231" s="6" t="s">
         <v>1818</v>
       </c>
-      <c r="G231" s="41">
-        <v>46212</v>
-      </c>
-      <c r="H231" s="42" t="s">
+      <c r="G231" s="2">
+        <v>46212</v>
+      </c>
+      <c r="H231" s="39" t="s">
         <v>1509</v>
       </c>
-      <c r="I231" s="37" t="s">
+      <c r="I231" t="s">
         <v>1819</v>
       </c>
     </row>
@@ -13918,7 +13957,7 @@
       <c r="B232" t="s">
         <v>1014</v>
       </c>
-      <c r="C232" s="37" t="s">
+      <c r="C232" t="s">
         <v>1463</v>
       </c>
       <c r="D232" s="6" t="s">
@@ -13927,16 +13966,16 @@
       <c r="E232" s="6" t="s">
         <v>1200</v>
       </c>
-      <c r="F232" s="40" t="s">
+      <c r="F232" s="6" t="s">
         <v>1820</v>
       </c>
-      <c r="G232" s="41">
-        <v>46212</v>
-      </c>
-      <c r="H232" s="42" t="s">
+      <c r="G232" s="2">
+        <v>46212</v>
+      </c>
+      <c r="H232" s="39" t="s">
         <v>1821</v>
       </c>
-      <c r="I232" s="37" t="s">
+      <c r="I232" t="s">
         <v>1822</v>
       </c>
     </row>
@@ -13947,7 +13986,7 @@
       <c r="B233" t="s">
         <v>1015</v>
       </c>
-      <c r="C233" s="37" t="s">
+      <c r="C233" t="s">
         <v>1565</v>
       </c>
       <c r="D233" s="6" t="s">
@@ -13956,16 +13995,16 @@
       <c r="E233" s="6" t="s">
         <v>1201</v>
       </c>
-      <c r="F233" s="40" t="s">
+      <c r="F233" s="6" t="s">
         <v>1823</v>
       </c>
-      <c r="G233" s="41">
-        <v>46212</v>
-      </c>
-      <c r="H233" s="42" t="s">
+      <c r="G233" s="2">
+        <v>46212</v>
+      </c>
+      <c r="H233" s="39" t="s">
         <v>1824</v>
       </c>
-      <c r="I233" s="37" t="s">
+      <c r="I233" t="s">
         <v>1825</v>
       </c>
     </row>
@@ -13976,7 +14015,7 @@
       <c r="B234" t="s">
         <v>1016</v>
       </c>
-      <c r="C234" s="37" t="s">
+      <c r="C234" t="s">
         <v>1497</v>
       </c>
       <c r="D234" s="6" t="s">
@@ -13985,16 +14024,16 @@
       <c r="E234" s="6" t="s">
         <v>1202</v>
       </c>
-      <c r="F234" s="40" t="s">
+      <c r="F234" s="6" t="s">
         <v>1826</v>
       </c>
-      <c r="G234" s="41">
-        <v>46212</v>
-      </c>
-      <c r="H234" s="42" t="s">
+      <c r="G234" s="2">
+        <v>46212</v>
+      </c>
+      <c r="H234" s="39" t="s">
         <v>1675</v>
       </c>
-      <c r="I234" s="37" t="s">
+      <c r="I234" t="s">
         <v>1827</v>
       </c>
     </row>
@@ -14005,7 +14044,7 @@
       <c r="B235" t="s">
         <v>1017</v>
       </c>
-      <c r="C235" s="37" t="s">
+      <c r="C235" t="s">
         <v>1452</v>
       </c>
       <c r="D235" s="6" t="s">
@@ -14014,16 +14053,16 @@
       <c r="E235" s="6" t="s">
         <v>1203</v>
       </c>
-      <c r="F235" s="40" t="s">
+      <c r="F235" s="6" t="s">
         <v>1828</v>
       </c>
-      <c r="G235" s="41">
-        <v>46212</v>
-      </c>
-      <c r="H235" s="42" t="s">
+      <c r="G235" s="2">
+        <v>46212</v>
+      </c>
+      <c r="H235" s="39" t="s">
         <v>1768</v>
       </c>
-      <c r="I235" s="37" t="s">
+      <c r="I235" t="s">
         <v>1829</v>
       </c>
     </row>
@@ -14034,7 +14073,7 @@
       <c r="B236" t="s">
         <v>1018</v>
       </c>
-      <c r="C236" s="37" t="s">
+      <c r="C236" t="s">
         <v>1508</v>
       </c>
       <c r="D236" s="6" t="s">
@@ -14043,16 +14082,16 @@
       <c r="E236" s="6" t="s">
         <v>1204</v>
       </c>
-      <c r="F236" s="40" t="s">
+      <c r="F236" s="6" t="s">
         <v>1830</v>
       </c>
-      <c r="G236" s="41">
-        <v>46212</v>
-      </c>
-      <c r="H236" s="42" t="s">
+      <c r="G236" s="2">
+        <v>46212</v>
+      </c>
+      <c r="H236" s="39" t="s">
         <v>1503</v>
       </c>
-      <c r="I236" s="37" t="s">
+      <c r="I236" t="s">
         <v>1831</v>
       </c>
     </row>
@@ -14063,7 +14102,7 @@
       <c r="B237" t="s">
         <v>1019</v>
       </c>
-      <c r="C237" s="37" t="s">
+      <c r="C237" t="s">
         <v>1501</v>
       </c>
       <c r="D237" s="6" t="s">
@@ -14072,16 +14111,16 @@
       <c r="E237" s="6" t="s">
         <v>1205</v>
       </c>
-      <c r="F237" s="40" t="s">
+      <c r="F237" s="6" t="s">
         <v>1833</v>
       </c>
-      <c r="G237" s="41">
-        <v>46212</v>
-      </c>
-      <c r="H237" s="42" t="s">
+      <c r="G237" s="2">
+        <v>46212</v>
+      </c>
+      <c r="H237" s="39" t="s">
         <v>1503</v>
       </c>
-      <c r="I237" s="37" t="s">
+      <c r="I237" t="s">
         <v>1834</v>
       </c>
     </row>
@@ -14092,7 +14131,7 @@
       <c r="B238" t="s">
         <v>1020</v>
       </c>
-      <c r="C238" s="37" t="s">
+      <c r="C238" t="s">
         <v>1497</v>
       </c>
       <c r="D238" s="6" t="s">
@@ -14101,16 +14140,16 @@
       <c r="E238" s="6" t="s">
         <v>1206</v>
       </c>
-      <c r="F238" s="40" t="s">
+      <c r="F238" s="6" t="s">
         <v>1835</v>
       </c>
-      <c r="G238" s="41">
-        <v>46212</v>
-      </c>
-      <c r="H238" s="42" t="s">
+      <c r="G238" s="2">
+        <v>46212</v>
+      </c>
+      <c r="H238" s="39" t="s">
         <v>1509</v>
       </c>
-      <c r="I238" s="37" t="s">
+      <c r="I238" t="s">
         <v>1836</v>
       </c>
     </row>
@@ -14121,7 +14160,7 @@
       <c r="B239" t="s">
         <v>1021</v>
       </c>
-      <c r="C239" s="37" t="s">
+      <c r="C239" t="s">
         <v>1452</v>
       </c>
       <c r="D239" s="6" t="s">
@@ -14130,16 +14169,16 @@
       <c r="E239" s="6" t="s">
         <v>1180</v>
       </c>
-      <c r="F239" s="40" t="s">
+      <c r="F239" s="6" t="s">
         <v>1837</v>
       </c>
-      <c r="G239" s="41">
-        <v>46212</v>
-      </c>
-      <c r="H239" s="42" t="s">
+      <c r="G239" s="2">
+        <v>46212</v>
+      </c>
+      <c r="H239" s="39" t="s">
         <v>1649</v>
       </c>
-      <c r="I239" s="37" t="s">
+      <c r="I239" t="s">
         <v>1838</v>
       </c>
     </row>
@@ -14150,7 +14189,7 @@
       <c r="B240" t="s">
         <v>1022</v>
       </c>
-      <c r="C240" s="37" t="s">
+      <c r="C240" t="s">
         <v>1452</v>
       </c>
       <c r="D240" s="6" t="s">
@@ -14159,16 +14198,16 @@
       <c r="E240" s="6" t="s">
         <v>1180</v>
       </c>
-      <c r="F240" s="40" t="s">
+      <c r="F240" s="6" t="s">
         <v>1776</v>
       </c>
-      <c r="G240" s="41">
-        <v>46212</v>
-      </c>
-      <c r="H240" s="42" t="s">
+      <c r="G240" s="2">
+        <v>46212</v>
+      </c>
+      <c r="H240" s="39" t="s">
         <v>1839</v>
       </c>
-      <c r="I240" s="37" t="s">
+      <c r="I240" t="s">
         <v>1840</v>
       </c>
     </row>
@@ -14179,7 +14218,7 @@
       <c r="B241" t="s">
         <v>1023</v>
       </c>
-      <c r="C241" s="37" t="s">
+      <c r="C241" t="s">
         <v>1456</v>
       </c>
       <c r="D241" s="6" t="s">
@@ -14188,16 +14227,16 @@
       <c r="E241" s="6" t="s">
         <v>1207</v>
       </c>
-      <c r="F241" s="40" t="s">
+      <c r="F241" s="6" t="s">
         <v>1841</v>
       </c>
-      <c r="G241" s="41">
-        <v>46212</v>
-      </c>
-      <c r="H241" s="42" t="s">
+      <c r="G241" s="2">
+        <v>46212</v>
+      </c>
+      <c r="H241" s="39" t="s">
         <v>343</v>
       </c>
-      <c r="I241" s="37" t="s">
+      <c r="I241" t="s">
         <v>1842</v>
       </c>
     </row>
@@ -14208,7 +14247,7 @@
       <c r="B242" t="s">
         <v>1024</v>
       </c>
-      <c r="C242" s="37" t="s">
+      <c r="C242" t="s">
         <v>1456</v>
       </c>
       <c r="D242" s="6" t="s">
@@ -14217,16 +14256,16 @@
       <c r="E242" s="6" t="s">
         <v>1208</v>
       </c>
-      <c r="F242" s="40" t="s">
+      <c r="F242" s="6" t="s">
         <v>1505</v>
       </c>
-      <c r="G242" s="41">
-        <v>46212</v>
-      </c>
-      <c r="H242" s="42" t="s">
+      <c r="G242" s="2">
+        <v>46212</v>
+      </c>
+      <c r="H242" s="39" t="s">
         <v>1558</v>
       </c>
-      <c r="I242" s="37" t="s">
+      <c r="I242" t="s">
         <v>1843</v>
       </c>
     </row>
@@ -14237,7 +14276,7 @@
       <c r="B243" t="s">
         <v>1025</v>
       </c>
-      <c r="C243" s="37" t="s">
+      <c r="C243" t="s">
         <v>1456</v>
       </c>
       <c r="D243" s="6" t="s">
@@ -14246,16 +14285,16 @@
       <c r="E243" s="6" t="s">
         <v>1209</v>
       </c>
-      <c r="F243" s="40" t="s">
+      <c r="F243" s="6" t="s">
         <v>1844</v>
       </c>
-      <c r="G243" s="41">
-        <v>46212</v>
-      </c>
-      <c r="H243" s="42" t="s">
+      <c r="G243" s="2">
+        <v>46212</v>
+      </c>
+      <c r="H243" s="39" t="s">
         <v>1578</v>
       </c>
-      <c r="I243" s="37" t="s">
+      <c r="I243" t="s">
         <v>1845</v>
       </c>
     </row>
@@ -14266,7 +14305,7 @@
       <c r="B244" t="s">
         <v>1026</v>
       </c>
-      <c r="C244" s="37" t="s">
+      <c r="C244" t="s">
         <v>1456</v>
       </c>
       <c r="D244" s="6" t="s">
@@ -14275,16 +14314,16 @@
       <c r="E244" s="6" t="s">
         <v>1210</v>
       </c>
-      <c r="F244" s="40" t="s">
+      <c r="F244" s="6" t="s">
         <v>1776</v>
       </c>
-      <c r="G244" s="41">
-        <v>46212</v>
-      </c>
-      <c r="H244" s="42" t="s">
+      <c r="G244" s="2">
+        <v>46212</v>
+      </c>
+      <c r="H244" s="39" t="s">
         <v>1454</v>
       </c>
-      <c r="I244" s="37" t="s">
+      <c r="I244" t="s">
         <v>1846</v>
       </c>
     </row>
@@ -14295,7 +14334,7 @@
       <c r="B245" t="s">
         <v>1027</v>
       </c>
-      <c r="C245" s="37" t="s">
+      <c r="C245" t="s">
         <v>1114</v>
       </c>
       <c r="D245" s="6" t="s">
@@ -14304,16 +14343,16 @@
       <c r="E245" s="6" t="s">
         <v>1211</v>
       </c>
-      <c r="F245" s="40" t="s">
+      <c r="F245" s="6" t="s">
         <v>1847</v>
       </c>
-      <c r="G245" s="41">
-        <v>46212</v>
-      </c>
-      <c r="H245" s="42" t="s">
+      <c r="G245" s="2">
+        <v>46212</v>
+      </c>
+      <c r="H245" s="39" t="s">
         <v>346</v>
       </c>
-      <c r="I245" s="37" t="s">
+      <c r="I245" t="s">
         <v>1848</v>
       </c>
     </row>
@@ -14324,7 +14363,7 @@
       <c r="B246" t="s">
         <v>1028</v>
       </c>
-      <c r="C246" s="37" t="s">
+      <c r="C246" t="s">
         <v>1456</v>
       </c>
       <c r="D246" s="6" t="s">
@@ -14333,16 +14372,16 @@
       <c r="E246" s="6" t="s">
         <v>1212</v>
       </c>
-      <c r="F246" s="40" t="s">
+      <c r="F246" s="6" t="s">
         <v>1849</v>
       </c>
-      <c r="G246" s="41">
-        <v>46212</v>
-      </c>
-      <c r="H246" s="42" t="s">
+      <c r="G246" s="2">
+        <v>46212</v>
+      </c>
+      <c r="H246" s="39" t="s">
         <v>1832</v>
       </c>
-      <c r="I246" s="37" t="s">
+      <c r="I246" t="s">
         <v>1850</v>
       </c>
     </row>
@@ -14353,7 +14392,7 @@
       <c r="B247" t="s">
         <v>1029</v>
       </c>
-      <c r="C247" s="37" t="s">
+      <c r="C247" t="s">
         <v>1456</v>
       </c>
       <c r="D247" s="6" t="s">
@@ -14362,16 +14401,16 @@
       <c r="E247" s="6" t="s">
         <v>1213</v>
       </c>
-      <c r="F247" s="40" t="s">
+      <c r="F247" s="6" t="s">
         <v>1851</v>
       </c>
-      <c r="G247" s="41">
-        <v>46212</v>
-      </c>
-      <c r="H247" s="42" t="s">
+      <c r="G247" s="2">
+        <v>46212</v>
+      </c>
+      <c r="H247" s="39" t="s">
         <v>1852</v>
       </c>
-      <c r="I247" s="37" t="s">
+      <c r="I247" t="s">
         <v>1853</v>
       </c>
     </row>
@@ -14382,7 +14421,7 @@
       <c r="B248" t="s">
         <v>1030</v>
       </c>
-      <c r="C248" s="37" t="s">
+      <c r="C248" t="s">
         <v>1452</v>
       </c>
       <c r="D248" s="6" t="s">
@@ -14391,16 +14430,16 @@
       <c r="E248" s="6" t="s">
         <v>1214</v>
       </c>
-      <c r="F248" s="40" t="s">
+      <c r="F248" s="6" t="s">
         <v>1854</v>
       </c>
-      <c r="G248" s="41">
-        <v>46212</v>
-      </c>
-      <c r="H248" s="42" t="s">
+      <c r="G248" s="2">
+        <v>46212</v>
+      </c>
+      <c r="H248" s="39" t="s">
         <v>1855</v>
       </c>
-      <c r="I248" s="37" t="s">
+      <c r="I248" t="s">
         <v>1856</v>
       </c>
     </row>
@@ -14411,7 +14450,7 @@
       <c r="B249" t="s">
         <v>1031</v>
       </c>
-      <c r="C249" s="37" t="s">
+      <c r="C249" t="s">
         <v>1463</v>
       </c>
       <c r="D249" s="6" t="s">
@@ -14420,16 +14459,16 @@
       <c r="E249" s="6" t="s">
         <v>1215</v>
       </c>
-      <c r="F249" s="40" t="s">
+      <c r="F249" s="6" t="s">
         <v>1857</v>
       </c>
-      <c r="G249" s="41">
-        <v>46212</v>
-      </c>
-      <c r="H249" s="42" t="s">
+      <c r="G249" s="2">
+        <v>46212</v>
+      </c>
+      <c r="H249" s="39" t="s">
         <v>1858</v>
       </c>
-      <c r="I249" s="37" t="s">
+      <c r="I249" t="s">
         <v>1859</v>
       </c>
     </row>
@@ -14440,7 +14479,7 @@
       <c r="B250" t="s">
         <v>1032</v>
       </c>
-      <c r="C250" s="37" t="s">
+      <c r="C250" t="s">
         <v>1565</v>
       </c>
       <c r="D250" s="6" t="s">
@@ -14449,16 +14488,16 @@
       <c r="E250" s="6" t="s">
         <v>1216</v>
       </c>
-      <c r="F250" s="40" t="s">
+      <c r="F250" s="6" t="s">
         <v>1860</v>
       </c>
-      <c r="G250" s="41">
-        <v>46212</v>
-      </c>
-      <c r="H250" s="42" t="s">
+      <c r="G250" s="2">
+        <v>46212</v>
+      </c>
+      <c r="H250" s="39" t="s">
         <v>1578</v>
       </c>
-      <c r="I250" s="37" t="s">
+      <c r="I250" t="s">
         <v>1861</v>
       </c>
     </row>
@@ -14469,7 +14508,7 @@
       <c r="B251" t="s">
         <v>1033</v>
       </c>
-      <c r="C251" s="37" t="s">
+      <c r="C251" t="s">
         <v>1444</v>
       </c>
       <c r="D251" s="6" t="s">
@@ -14478,16 +14517,16 @@
       <c r="E251" s="6" t="s">
         <v>1180</v>
       </c>
-      <c r="F251" s="40" t="s">
+      <c r="F251" s="6" t="s">
         <v>1776</v>
       </c>
-      <c r="G251" s="41">
-        <v>46212</v>
-      </c>
-      <c r="H251" s="42" t="s">
+      <c r="G251" s="2">
+        <v>46212</v>
+      </c>
+      <c r="H251" s="39" t="s">
         <v>1468</v>
       </c>
-      <c r="I251" s="37" t="s">
+      <c r="I251" t="s">
         <v>1862</v>
       </c>
     </row>
@@ -14498,7 +14537,7 @@
       <c r="B252" t="s">
         <v>1034</v>
       </c>
-      <c r="C252" s="37" t="s">
+      <c r="C252" t="s">
         <v>1508</v>
       </c>
       <c r="D252" s="6" t="s">
@@ -14507,16 +14546,16 @@
       <c r="E252" s="6" t="s">
         <v>1217</v>
       </c>
-      <c r="F252" s="40" t="s">
+      <c r="F252" s="6" t="s">
         <v>1863</v>
       </c>
-      <c r="G252" s="41">
-        <v>46212</v>
-      </c>
-      <c r="H252" s="42" t="s">
+      <c r="G252" s="2">
+        <v>46212</v>
+      </c>
+      <c r="H252" s="39" t="s">
         <v>348</v>
       </c>
-      <c r="I252" s="37" t="s">
+      <c r="I252" t="s">
         <v>1864</v>
       </c>
     </row>
@@ -14527,7 +14566,7 @@
       <c r="B253" t="s">
         <v>1035</v>
       </c>
-      <c r="C253" s="37" t="s">
+      <c r="C253" t="s">
         <v>1448</v>
       </c>
       <c r="D253" s="6" t="s">
@@ -14536,16 +14575,16 @@
       <c r="E253" s="6" t="s">
         <v>1218</v>
       </c>
-      <c r="F253" s="40" t="s">
+      <c r="F253" s="6" t="s">
         <v>1661</v>
       </c>
-      <c r="G253" s="41">
-        <v>46212</v>
-      </c>
-      <c r="H253" s="42" t="s">
+      <c r="G253" s="2">
+        <v>46212</v>
+      </c>
+      <c r="H253" s="39" t="s">
         <v>346</v>
       </c>
-      <c r="I253" s="37" t="s">
+      <c r="I253" t="s">
         <v>1865</v>
       </c>
     </row>
@@ -14556,7 +14595,7 @@
       <c r="B254" t="s">
         <v>1036</v>
       </c>
-      <c r="C254" s="37" t="s">
+      <c r="C254" t="s">
         <v>1448</v>
       </c>
       <c r="D254" s="6" t="s">
@@ -14565,16 +14604,16 @@
       <c r="E254" s="6" t="s">
         <v>1219</v>
       </c>
-      <c r="F254" s="40" t="s">
+      <c r="F254" s="6" t="s">
         <v>1866</v>
       </c>
-      <c r="G254" s="41">
-        <v>46212</v>
-      </c>
-      <c r="H254" s="42" t="s">
+      <c r="G254" s="2">
+        <v>46212</v>
+      </c>
+      <c r="H254" s="39" t="s">
         <v>1794</v>
       </c>
-      <c r="I254" s="37" t="s">
+      <c r="I254" t="s">
         <v>1867</v>
       </c>
     </row>
@@ -14585,7 +14624,7 @@
       <c r="B255" t="s">
         <v>1037</v>
       </c>
-      <c r="C255" s="37" t="s">
+      <c r="C255" t="s">
         <v>1448</v>
       </c>
       <c r="D255" s="6" t="s">
@@ -14594,16 +14633,16 @@
       <c r="E255" s="6" t="s">
         <v>1220</v>
       </c>
-      <c r="F255" s="40" t="s">
+      <c r="F255" s="6" t="s">
         <v>1868</v>
       </c>
-      <c r="G255" s="41">
-        <v>46212</v>
-      </c>
-      <c r="H255" s="42" t="s">
+      <c r="G255" s="2">
+        <v>46212</v>
+      </c>
+      <c r="H255" s="39" t="s">
         <v>1636</v>
       </c>
-      <c r="I255" s="37" t="s">
+      <c r="I255" t="s">
         <v>1869</v>
       </c>
     </row>
@@ -14614,7 +14653,7 @@
       <c r="B256" t="s">
         <v>1038</v>
       </c>
-      <c r="C256" s="37" t="s">
+      <c r="C256" t="s">
         <v>1448</v>
       </c>
       <c r="D256" s="6" t="s">
@@ -14623,16 +14662,16 @@
       <c r="E256" s="6" t="s">
         <v>1221</v>
       </c>
-      <c r="F256" s="40" t="s">
+      <c r="F256" s="6" t="s">
         <v>1870</v>
       </c>
-      <c r="G256" s="41">
-        <v>46212</v>
-      </c>
-      <c r="H256" s="42" t="s">
+      <c r="G256" s="2">
+        <v>46212</v>
+      </c>
+      <c r="H256" s="39" t="s">
         <v>1578</v>
       </c>
-      <c r="I256" s="37" t="s">
+      <c r="I256" t="s">
         <v>1871</v>
       </c>
     </row>
@@ -14643,7 +14682,7 @@
       <c r="B257" t="s">
         <v>1039</v>
       </c>
-      <c r="C257" s="37" t="s">
+      <c r="C257" t="s">
         <v>1448</v>
       </c>
       <c r="D257" s="6" t="s">
@@ -14652,16 +14691,16 @@
       <c r="E257" s="6" t="s">
         <v>1222</v>
       </c>
-      <c r="F257" s="40" t="s">
+      <c r="F257" s="6" t="s">
         <v>1872</v>
       </c>
-      <c r="G257" s="41">
-        <v>46212</v>
-      </c>
-      <c r="H257" s="42" t="s">
+      <c r="G257" s="2">
+        <v>46212</v>
+      </c>
+      <c r="H257" s="39" t="s">
         <v>1873</v>
       </c>
-      <c r="I257" s="37" t="s">
+      <c r="I257" t="s">
         <v>1874</v>
       </c>
     </row>
@@ -14672,7 +14711,7 @@
       <c r="B258" t="s">
         <v>1040</v>
       </c>
-      <c r="C258" s="37" t="s">
+      <c r="C258" t="s">
         <v>1448</v>
       </c>
       <c r="D258" s="6" t="s">
@@ -14681,16 +14720,16 @@
       <c r="E258" s="6" t="s">
         <v>1223</v>
       </c>
-      <c r="F258" s="40" t="s">
+      <c r="F258" s="6" t="s">
         <v>1875</v>
       </c>
-      <c r="G258" s="41">
-        <v>46212</v>
-      </c>
-      <c r="H258" s="42" t="s">
+      <c r="G258" s="2">
+        <v>46212</v>
+      </c>
+      <c r="H258" s="39" t="s">
         <v>1876</v>
       </c>
-      <c r="I258" s="37" t="s">
+      <c r="I258" t="s">
         <v>1877</v>
       </c>
     </row>
@@ -14701,7 +14740,7 @@
       <c r="B259" t="s">
         <v>1041</v>
       </c>
-      <c r="C259" s="37" t="s">
+      <c r="C259" t="s">
         <v>1448</v>
       </c>
       <c r="D259" s="6" t="s">
@@ -14710,16 +14749,16 @@
       <c r="E259" s="6" t="s">
         <v>1224</v>
       </c>
-      <c r="F259" s="40" t="s">
+      <c r="F259" s="6" t="s">
         <v>1760</v>
       </c>
-      <c r="G259" s="41">
-        <v>46212</v>
-      </c>
-      <c r="H259" s="42" t="s">
+      <c r="G259" s="2">
+        <v>46212</v>
+      </c>
+      <c r="H259" s="39" t="s">
         <v>1578</v>
       </c>
-      <c r="I259" s="37" t="s">
+      <c r="I259" t="s">
         <v>1878</v>
       </c>
     </row>
@@ -14730,7 +14769,7 @@
       <c r="B260" t="s">
         <v>1042</v>
       </c>
-      <c r="C260" s="37" t="s">
+      <c r="C260" t="s">
         <v>1463</v>
       </c>
       <c r="D260" s="6" t="s">
@@ -14739,16 +14778,16 @@
       <c r="E260" s="6" t="s">
         <v>1225</v>
       </c>
-      <c r="F260" s="40" t="s">
+      <c r="F260" s="6" t="s">
         <v>1879</v>
       </c>
-      <c r="G260" s="41">
-        <v>46212</v>
-      </c>
-      <c r="H260" s="42" t="s">
+      <c r="G260" s="2">
+        <v>46212</v>
+      </c>
+      <c r="H260" s="39" t="s">
         <v>1880</v>
       </c>
-      <c r="I260" s="37" t="s">
+      <c r="I260" t="s">
         <v>1881</v>
       </c>
     </row>
@@ -14759,7 +14798,7 @@
       <c r="B261" t="s">
         <v>1043</v>
       </c>
-      <c r="C261" s="37" t="s">
+      <c r="C261" t="s">
         <v>1456</v>
       </c>
       <c r="D261" s="6" t="s">
@@ -14768,16 +14807,16 @@
       <c r="E261" s="6" t="s">
         <v>1226</v>
       </c>
-      <c r="F261" s="40" t="s">
+      <c r="F261" s="6" t="s">
         <v>1882</v>
       </c>
-      <c r="G261" s="41">
-        <v>46212</v>
-      </c>
-      <c r="H261" s="42" t="s">
+      <c r="G261" s="2">
+        <v>46212</v>
+      </c>
+      <c r="H261" s="39" t="s">
         <v>1883</v>
       </c>
-      <c r="I261" s="37" t="s">
+      <c r="I261" t="s">
         <v>1884</v>
       </c>
     </row>
@@ -14788,7 +14827,7 @@
       <c r="B262" t="s">
         <v>1044</v>
       </c>
-      <c r="C262" s="37" t="s">
+      <c r="C262" t="s">
         <v>1885</v>
       </c>
       <c r="D262" s="6" t="s">
@@ -14797,16 +14836,16 @@
       <c r="E262" s="6" t="s">
         <v>1227</v>
       </c>
-      <c r="F262" s="40" t="s">
+      <c r="F262" s="6" t="s">
         <v>1886</v>
       </c>
-      <c r="G262" s="41">
-        <v>46212</v>
-      </c>
-      <c r="H262" s="42" t="s">
+      <c r="G262" s="2">
+        <v>46212</v>
+      </c>
+      <c r="H262" s="39" t="s">
         <v>1887</v>
       </c>
-      <c r="I262" s="37" t="s">
+      <c r="I262" t="s">
         <v>1888</v>
       </c>
     </row>
@@ -14817,7 +14856,7 @@
       <c r="B263" t="s">
         <v>1045</v>
       </c>
-      <c r="C263" s="37" t="s">
+      <c r="C263" t="s">
         <v>1444</v>
       </c>
       <c r="D263" s="6" t="s">
@@ -14826,16 +14865,16 @@
       <c r="E263" s="6" t="s">
         <v>1228</v>
       </c>
-      <c r="F263" s="40" t="s">
+      <c r="F263" s="6" t="s">
         <v>1505</v>
       </c>
-      <c r="G263" s="41">
-        <v>46212</v>
-      </c>
-      <c r="H263" s="42" t="s">
+      <c r="G263" s="2">
+        <v>46212</v>
+      </c>
+      <c r="H263" s="39" t="s">
         <v>1468</v>
       </c>
-      <c r="I263" s="37" t="s">
+      <c r="I263" t="s">
         <v>1889</v>
       </c>
     </row>
@@ -14846,7 +14885,7 @@
       <c r="B264" t="s">
         <v>1046</v>
       </c>
-      <c r="C264" s="37" t="s">
+      <c r="C264" t="s">
         <v>1463</v>
       </c>
       <c r="D264" s="6" t="s">
@@ -14855,16 +14894,16 @@
       <c r="E264" s="6" t="s">
         <v>1229</v>
       </c>
-      <c r="F264" s="40" t="s">
+      <c r="F264" s="6" t="s">
         <v>1890</v>
       </c>
-      <c r="G264" s="41">
-        <v>46212</v>
-      </c>
-      <c r="H264" s="42" t="s">
+      <c r="G264" s="2">
+        <v>46212</v>
+      </c>
+      <c r="H264" s="39" t="s">
         <v>1891</v>
       </c>
-      <c r="I264" s="37" t="s">
+      <c r="I264" t="s">
         <v>1892</v>
       </c>
     </row>
@@ -14875,7 +14914,7 @@
       <c r="B265" t="s">
         <v>1047</v>
       </c>
-      <c r="C265" s="37" t="s">
+      <c r="C265" t="s">
         <v>1444</v>
       </c>
       <c r="D265" s="6" t="s">
@@ -14884,16 +14923,16 @@
       <c r="E265" s="6" t="s">
         <v>1230</v>
       </c>
-      <c r="F265" s="40" t="s">
+      <c r="F265" s="6" t="s">
         <v>1893</v>
       </c>
-      <c r="G265" s="41">
-        <v>46212</v>
-      </c>
-      <c r="H265" s="42" t="s">
+      <c r="G265" s="2">
+        <v>46212</v>
+      </c>
+      <c r="H265" s="39" t="s">
         <v>1894</v>
       </c>
-      <c r="I265" s="37" t="s">
+      <c r="I265" t="s">
         <v>1895</v>
       </c>
     </row>
@@ -14904,7 +14943,7 @@
       <c r="B266" t="s">
         <v>1048</v>
       </c>
-      <c r="C266" s="37" t="s">
+      <c r="C266" t="s">
         <v>1456</v>
       </c>
       <c r="D266" s="6" t="s">
@@ -14913,16 +14952,16 @@
       <c r="E266" s="6" t="s">
         <v>1231</v>
       </c>
-      <c r="F266" s="40" t="s">
+      <c r="F266" s="6" t="s">
         <v>1896</v>
       </c>
-      <c r="G266" s="41">
-        <v>46212</v>
-      </c>
-      <c r="H266" s="42" t="s">
+      <c r="G266" s="2">
+        <v>46212</v>
+      </c>
+      <c r="H266" s="39" t="s">
         <v>1495</v>
       </c>
-      <c r="I266" s="37" t="s">
+      <c r="I266" t="s">
         <v>1897</v>
       </c>
     </row>
@@ -14933,7 +14972,7 @@
       <c r="B267" t="s">
         <v>1049</v>
       </c>
-      <c r="C267" s="37" t="s">
+      <c r="C267" t="s">
         <v>1501</v>
       </c>
       <c r="D267" s="6" t="s">
@@ -14942,16 +14981,16 @@
       <c r="E267" s="6" t="s">
         <v>1232</v>
       </c>
-      <c r="F267" s="40" t="s">
+      <c r="F267" s="6" t="s">
         <v>1898</v>
       </c>
-      <c r="G267" s="41">
-        <v>46212</v>
-      </c>
-      <c r="H267" s="42" t="s">
+      <c r="G267" s="2">
+        <v>46212</v>
+      </c>
+      <c r="H267" s="39" t="s">
         <v>1578</v>
       </c>
-      <c r="I267" s="37" t="s">
+      <c r="I267" t="s">
         <v>1899</v>
       </c>
     </row>
@@ -14962,7 +15001,7 @@
       <c r="B268" t="s">
         <v>1050</v>
       </c>
-      <c r="C268" s="37" t="s">
+      <c r="C268" t="s">
         <v>1501</v>
       </c>
       <c r="D268" s="6" t="s">
@@ -14971,16 +15010,16 @@
       <c r="E268" s="6" t="s">
         <v>1233</v>
       </c>
-      <c r="F268" s="40" t="s">
+      <c r="F268" s="6" t="s">
         <v>1900</v>
       </c>
-      <c r="G268" s="41">
-        <v>46212</v>
-      </c>
-      <c r="H268" s="42" t="s">
+      <c r="G268" s="2">
+        <v>46212</v>
+      </c>
+      <c r="H268" s="39" t="s">
         <v>1468</v>
       </c>
-      <c r="I268" s="37" t="s">
+      <c r="I268" t="s">
         <v>1901</v>
       </c>
     </row>
@@ -14991,7 +15030,7 @@
       <c r="B269" t="s">
         <v>1051</v>
       </c>
-      <c r="C269" s="37" t="s">
+      <c r="C269" t="s">
         <v>1902</v>
       </c>
       <c r="D269" s="6" t="s">
@@ -15000,16 +15039,16 @@
       <c r="E269" s="6" t="s">
         <v>1234</v>
       </c>
-      <c r="F269" s="40" t="s">
+      <c r="F269" s="6" t="s">
         <v>1903</v>
       </c>
-      <c r="G269" s="41">
-        <v>46212</v>
-      </c>
-      <c r="H269" s="42" t="s">
+      <c r="G269" s="2">
+        <v>46212</v>
+      </c>
+      <c r="H269" s="39" t="s">
         <v>1904</v>
       </c>
-      <c r="I269" s="37" t="s">
+      <c r="I269" t="s">
         <v>1905</v>
       </c>
     </row>
@@ -15020,7 +15059,7 @@
       <c r="B270" t="s">
         <v>1052</v>
       </c>
-      <c r="C270" s="37" t="s">
+      <c r="C270" t="s">
         <v>1463</v>
       </c>
       <c r="D270" s="6" t="s">
@@ -15029,16 +15068,16 @@
       <c r="E270" s="6" t="s">
         <v>1235</v>
       </c>
-      <c r="F270" s="40" t="s">
+      <c r="F270" s="6" t="s">
         <v>1906</v>
       </c>
-      <c r="G270" s="41">
-        <v>46212</v>
-      </c>
-      <c r="H270" s="42" t="s">
+      <c r="G270" s="2">
+        <v>46212</v>
+      </c>
+      <c r="H270" s="39" t="s">
         <v>1907</v>
       </c>
-      <c r="I270" s="37" t="s">
+      <c r="I270" t="s">
         <v>1908</v>
       </c>
     </row>
@@ -15049,7 +15088,7 @@
       <c r="B271" t="s">
         <v>1053</v>
       </c>
-      <c r="C271" s="37" t="s">
+      <c r="C271" t="s">
         <v>1452</v>
       </c>
       <c r="D271" s="6" t="s">
@@ -15058,16 +15097,16 @@
       <c r="E271" s="6" t="s">
         <v>1236</v>
       </c>
-      <c r="F271" s="40" t="s">
+      <c r="F271" s="6" t="s">
         <v>1909</v>
       </c>
-      <c r="G271" s="41">
-        <v>46212</v>
-      </c>
-      <c r="H271" s="42" t="s">
+      <c r="G271" s="2">
+        <v>46212</v>
+      </c>
+      <c r="H271" s="39" t="s">
         <v>1910</v>
       </c>
-      <c r="I271" s="37" t="s">
+      <c r="I271" t="s">
         <v>1911</v>
       </c>
     </row>
@@ -15078,7 +15117,7 @@
       <c r="B272" t="s">
         <v>1054</v>
       </c>
-      <c r="C272" s="37" t="s">
+      <c r="C272" t="s">
         <v>1501</v>
       </c>
       <c r="D272" s="6" t="s">
@@ -15087,16 +15126,16 @@
       <c r="E272" s="6" t="s">
         <v>1237</v>
       </c>
-      <c r="F272" s="40" t="s">
+      <c r="F272" s="6" t="s">
         <v>1912</v>
       </c>
-      <c r="G272" s="41">
-        <v>46212</v>
-      </c>
-      <c r="H272" s="42" t="s">
+      <c r="G272" s="2">
+        <v>46212</v>
+      </c>
+      <c r="H272" s="39" t="s">
         <v>1876</v>
       </c>
-      <c r="I272" s="37" t="s">
+      <c r="I272" t="s">
         <v>1913</v>
       </c>
     </row>
@@ -15107,7 +15146,7 @@
       <c r="B273" t="s">
         <v>1055</v>
       </c>
-      <c r="C273" s="37" t="s">
+      <c r="C273" t="s">
         <v>1456</v>
       </c>
       <c r="D273" s="6" t="s">
@@ -15116,16 +15155,16 @@
       <c r="E273" s="6" t="s">
         <v>1238</v>
       </c>
-      <c r="F273" s="40" t="s">
+      <c r="F273" s="6" t="s">
         <v>1914</v>
       </c>
-      <c r="G273" s="41">
-        <v>46212</v>
-      </c>
-      <c r="H273" s="42" t="s">
+      <c r="G273" s="2">
+        <v>46212</v>
+      </c>
+      <c r="H273" s="39" t="s">
         <v>1915</v>
       </c>
-      <c r="I273" s="37" t="s">
+      <c r="I273" t="s">
         <v>1916</v>
       </c>
     </row>
@@ -15136,7 +15175,7 @@
       <c r="B274" t="s">
         <v>1056</v>
       </c>
-      <c r="C274" s="37" t="s">
+      <c r="C274" t="s">
         <v>1452</v>
       </c>
       <c r="D274" s="6" t="s">
@@ -15145,16 +15184,16 @@
       <c r="E274" s="6" t="s">
         <v>1239</v>
       </c>
-      <c r="F274" s="40" t="s">
+      <c r="F274" s="6" t="s">
         <v>1917</v>
       </c>
-      <c r="G274" s="41">
-        <v>46212</v>
-      </c>
-      <c r="H274" s="42" t="s">
+      <c r="G274" s="2">
+        <v>46212</v>
+      </c>
+      <c r="H274" s="39" t="s">
         <v>1620</v>
       </c>
-      <c r="I274" s="37" t="s">
+      <c r="I274" t="s">
         <v>1918</v>
       </c>
     </row>
@@ -15165,7 +15204,7 @@
       <c r="B275" t="s">
         <v>1057</v>
       </c>
-      <c r="C275" s="37" t="s">
+      <c r="C275" t="s">
         <v>1452</v>
       </c>
       <c r="D275" s="6" t="s">
@@ -15174,16 +15213,16 @@
       <c r="E275" s="6" t="s">
         <v>1240</v>
       </c>
-      <c r="F275" s="40" t="s">
+      <c r="F275" s="6" t="s">
         <v>1919</v>
       </c>
-      <c r="G275" s="41">
-        <v>46212</v>
-      </c>
-      <c r="H275" s="42" t="s">
+      <c r="G275" s="2">
+        <v>46212</v>
+      </c>
+      <c r="H275" s="39" t="s">
         <v>1920</v>
       </c>
-      <c r="I275" s="37" t="s">
+      <c r="I275" t="s">
         <v>1921</v>
       </c>
     </row>
@@ -15194,7 +15233,7 @@
       <c r="B276" t="s">
         <v>1058</v>
       </c>
-      <c r="C276" s="37" t="s">
+      <c r="C276" t="s">
         <v>1508</v>
       </c>
       <c r="D276" s="6" t="s">
@@ -15203,16 +15242,16 @@
       <c r="E276" s="6" t="s">
         <v>1241</v>
       </c>
-      <c r="F276" s="40" t="s">
+      <c r="F276" s="6" t="s">
         <v>1922</v>
       </c>
-      <c r="G276" s="41">
-        <v>46212</v>
-      </c>
-      <c r="H276" s="42" t="s">
+      <c r="G276" s="2">
+        <v>46212</v>
+      </c>
+      <c r="H276" s="39" t="s">
         <v>351</v>
       </c>
-      <c r="I276" s="37" t="s">
+      <c r="I276" t="s">
         <v>1923</v>
       </c>
     </row>
@@ -15223,7 +15262,7 @@
       <c r="B277" t="s">
         <v>1059</v>
       </c>
-      <c r="C277" s="37" t="s">
+      <c r="C277" t="s">
         <v>1924</v>
       </c>
       <c r="D277" s="6" t="s">
@@ -15232,16 +15271,16 @@
       <c r="E277" s="6" t="s">
         <v>1242</v>
       </c>
-      <c r="F277" s="40" t="s">
+      <c r="F277" s="6" t="s">
         <v>1925</v>
       </c>
-      <c r="G277" s="41">
-        <v>46212</v>
-      </c>
-      <c r="H277" s="42" t="s">
+      <c r="G277" s="2">
+        <v>46212</v>
+      </c>
+      <c r="H277" s="39" t="s">
         <v>354</v>
       </c>
-      <c r="I277" s="37" t="s">
+      <c r="I277" t="s">
         <v>1926</v>
       </c>
     </row>
@@ -15252,7 +15291,7 @@
       <c r="B278" t="s">
         <v>1060</v>
       </c>
-      <c r="C278" s="37" t="s">
+      <c r="C278" t="s">
         <v>1456</v>
       </c>
       <c r="D278" s="6" t="s">
@@ -15261,16 +15300,16 @@
       <c r="E278" s="6" t="s">
         <v>1243</v>
       </c>
-      <c r="F278" s="40" t="s">
+      <c r="F278" s="6" t="s">
         <v>1927</v>
       </c>
-      <c r="G278" s="41">
-        <v>46212</v>
-      </c>
-      <c r="H278" s="42" t="s">
+      <c r="G278" s="2">
+        <v>46212</v>
+      </c>
+      <c r="H278" s="39" t="s">
         <v>1578</v>
       </c>
-      <c r="I278" s="37" t="s">
+      <c r="I278" t="s">
         <v>1928</v>
       </c>
     </row>
@@ -15281,7 +15320,7 @@
       <c r="B279" t="s">
         <v>1061</v>
       </c>
-      <c r="C279" s="37" t="s">
+      <c r="C279" t="s">
         <v>1508</v>
       </c>
       <c r="D279" s="6" t="s">
@@ -15290,27 +15329,59 @@
       <c r="E279" s="6" t="s">
         <v>1244</v>
       </c>
-      <c r="F279" s="40" t="s">
+      <c r="F279" s="6" t="s">
         <v>1929</v>
       </c>
-      <c r="G279" s="41">
-        <v>46212</v>
-      </c>
-      <c r="H279" s="42" t="s">
+      <c r="G279" s="2">
+        <v>46212</v>
+      </c>
+      <c r="H279" s="39" t="s">
         <v>1558</v>
       </c>
-      <c r="I279" s="37" t="s">
+      <c r="I279" t="s">
         <v>1930</v>
+      </c>
+    </row>
+    <row r="280" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A280" s="32" t="s">
+        <v>1931</v>
+      </c>
+      <c r="B280" t="s">
+        <v>1932</v>
+      </c>
+      <c r="C280" t="s">
+        <v>1937</v>
+      </c>
+      <c r="D280" s="6" t="s">
+        <v>1933</v>
+      </c>
+      <c r="E280" s="6" t="s">
+        <v>1934</v>
+      </c>
+      <c r="F280" s="40" t="s">
+        <v>1935</v>
+      </c>
+      <c r="G280" s="2">
+        <v>46213</v>
+      </c>
+      <c r="H280" s="9" t="s">
+        <v>1938</v>
+      </c>
+      <c r="I280" t="s">
+        <v>1936</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
+  <conditionalFormatting sqref="A1:B1048576">
+    <cfRule type="duplicateValues" dxfId="1" priority="3"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="I1:I1048576">
-    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A1:B1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
-  </conditionalFormatting>
+  <hyperlinks>
+    <hyperlink ref="F280" r:id="rId1" xr:uid="{5B12B451-33AF-4080-AE37-8D2C8E07BC51}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/database.xlsx
+++ b/database.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A7ABB26-C60D-4450-8D89-60F1BFE832B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{227B1389-FE07-4A64-B206-C521D927C583}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28284" yWindow="768" windowWidth="26376" windowHeight="15420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20052" yWindow="216" windowWidth="26376" windowHeight="15420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2366" uniqueCount="1939">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2374" uniqueCount="1947">
   <si>
     <t>425-81-02924</t>
   </si>
@@ -6246,13 +6246,43 @@
   <si>
     <t>08717</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>791-12-02771</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>신미우역</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>JIN MEIHONG</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>010-6618-8331</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>momokim331@naver.com</t>
+  </si>
+  <si>
+    <t>22006</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>인천광역시 연수구 센트럴로 313, 비동 2409호 12-9호</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>신미무역5241015</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -6334,14 +6364,6 @@
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
-      <name val="맑은 고딕"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -6389,9 +6411,8 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -6486,13 +6507,10 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
-    <cellStyle name="하이퍼링크" xfId="1" builtinId="8"/>
   </cellStyles>
   <dxfs count="2">
     <dxf>
@@ -6850,7 +6868,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE6138A4-676B-44A6-82D7-1ADA43310F48}">
-  <dimension ref="A1:K280"/>
+  <dimension ref="A1:K281"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -15371,6 +15389,35 @@
         <v>1936</v>
       </c>
     </row>
+    <row r="281" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A281" s="32" t="s">
+        <v>1939</v>
+      </c>
+      <c r="B281" t="s">
+        <v>1940</v>
+      </c>
+      <c r="C281" t="s">
+        <v>1946</v>
+      </c>
+      <c r="D281" s="6" t="s">
+        <v>1941</v>
+      </c>
+      <c r="E281" s="6" t="s">
+        <v>1942</v>
+      </c>
+      <c r="F281" s="6" t="s">
+        <v>1943</v>
+      </c>
+      <c r="G281" s="2">
+        <v>46213</v>
+      </c>
+      <c r="H281" s="9" t="s">
+        <v>1944</v>
+      </c>
+      <c r="I281" t="s">
+        <v>1945</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A1:B1048576">
@@ -15379,9 +15426,6 @@
   <conditionalFormatting sqref="I1:I1048576">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
-  <hyperlinks>
-    <hyperlink ref="F280" r:id="rId1" xr:uid="{5B12B451-33AF-4080-AE37-8D2C8E07BC51}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/database.xlsx
+++ b/database.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{227B1389-FE07-4A64-B206-C521D927C583}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9464E5EF-64C0-429F-B598-6202AD575E25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20052" yWindow="216" windowWidth="26376" windowHeight="15420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-29952" yWindow="768" windowWidth="26376" windowHeight="15420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2374" uniqueCount="1947">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2382" uniqueCount="1955">
   <si>
     <t>425-81-02924</t>
   </si>
@@ -6276,6 +6276,38 @@
   </si>
   <si>
     <t>신미무역5241015</t>
+  </si>
+  <si>
+    <t>08371</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>서울특별시 구로구 디지털로31길 119, 201동 1003호</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>010-5678-9899</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>qthyzq123@naver.com</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LIU CHUNYING</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>434-13-02759</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>라엔</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>라엔****5251017</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -6868,7 +6900,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE6138A4-676B-44A6-82D7-1ADA43310F48}">
-  <dimension ref="A1:K281"/>
+  <dimension ref="A1:K282"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -15376,7 +15408,7 @@
       <c r="E280" s="6" t="s">
         <v>1934</v>
       </c>
-      <c r="F280" s="40" t="s">
+      <c r="F280" t="s">
         <v>1935</v>
       </c>
       <c r="G280" s="2">
@@ -15416,6 +15448,35 @@
       </c>
       <c r="I281" t="s">
         <v>1945</v>
+      </c>
+    </row>
+    <row r="282" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A282" s="32" t="s">
+        <v>1952</v>
+      </c>
+      <c r="B282" t="s">
+        <v>1953</v>
+      </c>
+      <c r="C282" t="s">
+        <v>1954</v>
+      </c>
+      <c r="D282" s="6" t="s">
+        <v>1951</v>
+      </c>
+      <c r="E282" s="6" t="s">
+        <v>1949</v>
+      </c>
+      <c r="F282" s="40" t="s">
+        <v>1950</v>
+      </c>
+      <c r="G282" s="2">
+        <v>46213</v>
+      </c>
+      <c r="H282" s="9" t="s">
+        <v>1947</v>
+      </c>
+      <c r="I282" t="s">
+        <v>1948</v>
       </c>
     </row>
   </sheetData>

--- a/database.xlsx
+++ b/database.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5B5C9E4-B683-4B27-9D5A-12D8613C8EB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDB1931A-71A7-4108-8EBD-7E0E32ABCB49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-29088" yWindow="252" windowWidth="26376" windowHeight="15420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28164" yWindow="360" windowWidth="26376" windowHeight="15420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2382" uniqueCount="2124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2992" uniqueCount="2657">
   <si>
     <t>425-81-02924</t>
   </si>
@@ -6817,6 +6817,1605 @@
   </si>
   <si>
     <t>블루밍로1251013</t>
+  </si>
+  <si>
+    <t>유한회사 비즈랜드코리아</t>
+  </si>
+  <si>
+    <t>비즈랜드1241013</t>
+  </si>
+  <si>
+    <t>WANG HUAXIAO</t>
+  </si>
+  <si>
+    <t>01088721688</t>
+  </si>
+  <si>
+    <t>beadslandshop@163.com</t>
+  </si>
+  <si>
+    <t>경기도 화성시 동탄중심상가2길 26-15(반송동)지성프라자</t>
+  </si>
+  <si>
+    <t>전자상거래</t>
+  </si>
+  <si>
+    <t>전자상거래 외</t>
+  </si>
+  <si>
+    <t>이매력</t>
+  </si>
+  <si>
+    <t>이매력**5241013</t>
+  </si>
+  <si>
+    <t>LI YINGHAI</t>
+  </si>
+  <si>
+    <t>01076886588</t>
+  </si>
+  <si>
+    <t>liyinghai512@naver.com</t>
+  </si>
+  <si>
+    <t>17921</t>
+  </si>
+  <si>
+    <t>경기도 평택시 원평로75번길 39(평택동)</t>
+  </si>
+  <si>
+    <t>피카루샵 유한회사</t>
+  </si>
+  <si>
+    <t>피카루샵1261017</t>
+  </si>
+  <si>
+    <t>LIU SHIYANG</t>
+  </si>
+  <si>
+    <t>010-5722-8444</t>
+  </si>
+  <si>
+    <t>lshy202603@163.com</t>
+  </si>
+  <si>
+    <t>08536</t>
+  </si>
+  <si>
+    <t>서울특별시 금천구 시흥대로152길 11-31 (독산동)3층303-비49호</t>
+  </si>
+  <si>
+    <t>다우기업 (주)</t>
+  </si>
+  <si>
+    <t>다우기업1921018</t>
+  </si>
+  <si>
+    <t>전향진</t>
+  </si>
+  <si>
+    <t>010-3601-1375</t>
+  </si>
+  <si>
+    <t>dawoo2626@hanmail.net</t>
+  </si>
+  <si>
+    <t>58256</t>
+  </si>
+  <si>
+    <t>전라남도 나주시 중앙로 45 (성북동)</t>
+  </si>
+  <si>
+    <t>건설업</t>
+  </si>
+  <si>
+    <t>냉난방위생배관설비공</t>
+  </si>
+  <si>
+    <t>굿앱더몰</t>
+  </si>
+  <si>
+    <t>굿앱더몰5221010</t>
+  </si>
+  <si>
+    <t>박주연</t>
+  </si>
+  <si>
+    <t>01051988982</t>
+  </si>
+  <si>
+    <t>qufrb16@naver.com</t>
+  </si>
+  <si>
+    <t>08814</t>
+  </si>
+  <si>
+    <t>서울특별시 관악구 신림로 99(신림동)센터스퀘어 서울대점</t>
+  </si>
+  <si>
+    <t>월간리빙</t>
+  </si>
+  <si>
+    <t>월간리빙5221013</t>
+  </si>
+  <si>
+    <t>심재원</t>
+  </si>
+  <si>
+    <t>01057497765</t>
+  </si>
+  <si>
+    <t>monthliv@naver.com</t>
+  </si>
+  <si>
+    <t>12913</t>
+  </si>
+  <si>
+    <t>경기도 하남시 미사강변중앙로 208(망월동)부강타워</t>
+  </si>
+  <si>
+    <t>엠에이치케미칼</t>
+  </si>
+  <si>
+    <t>엠에이치522C018</t>
+  </si>
+  <si>
+    <t>이규배</t>
+  </si>
+  <si>
+    <t>01054793509</t>
+  </si>
+  <si>
+    <t>Kblee@mhchem1.com</t>
+  </si>
+  <si>
+    <t>18126</t>
+  </si>
+  <si>
+    <t>경기도 오산시 수목원로88번길 35 (가수동)</t>
+  </si>
+  <si>
+    <t>제조업 외</t>
+  </si>
+  <si>
+    <t>기타화학약품</t>
+  </si>
+  <si>
+    <t>주식회사 데이무드</t>
+  </si>
+  <si>
+    <t>데이무드1232015</t>
+  </si>
+  <si>
+    <t>박영선</t>
+  </si>
+  <si>
+    <t>01022982289</t>
+  </si>
+  <si>
+    <t>oppo2022@naver.com</t>
+  </si>
+  <si>
+    <t>46557</t>
+  </si>
+  <si>
+    <t>부산광역시 북구 상학로 36 (만덕동, 이편한세상 금정산) 201동 1004호</t>
+  </si>
+  <si>
+    <t>도매및소매업</t>
+  </si>
+  <si>
+    <t>전자상거래소매업</t>
+  </si>
+  <si>
+    <t>포커스포인트 유한회사</t>
+  </si>
+  <si>
+    <t>포커스포1251018</t>
+  </si>
+  <si>
+    <t>NING YAWEN</t>
+  </si>
+  <si>
+    <t>010-7980-0389</t>
+  </si>
+  <si>
+    <t>188862017@qq.com</t>
+  </si>
+  <si>
+    <t>11673</t>
+  </si>
+  <si>
+    <t>경기도 의정부시 둔야로33번길 9(의정부동)덕암오피스텔</t>
+  </si>
+  <si>
+    <t>도소매업</t>
+  </si>
+  <si>
+    <t>센리</t>
+  </si>
+  <si>
+    <t>센리****5242018</t>
+  </si>
+  <si>
+    <t>이정민</t>
+  </si>
+  <si>
+    <t>01076302141</t>
+  </si>
+  <si>
+    <t>cs_01@cenli.co.kr</t>
+  </si>
+  <si>
+    <t>41922</t>
+  </si>
+  <si>
+    <t>대구광역시 중구 달성로 123(달성동)달성파크푸르지오힐스테이트</t>
+  </si>
+  <si>
+    <t>어드레스팔공팔</t>
+  </si>
+  <si>
+    <t>어드레스5162010</t>
+  </si>
+  <si>
+    <t>이자원</t>
+  </si>
+  <si>
+    <t>010-5036-8089</t>
+  </si>
+  <si>
+    <t>address808@naver.com</t>
+  </si>
+  <si>
+    <t>18403</t>
+  </si>
+  <si>
+    <t>경기도 화성시 병점구 병점동로 78 (병점동)</t>
+  </si>
+  <si>
+    <t>소매업</t>
+  </si>
+  <si>
+    <t>의류 외</t>
+  </si>
+  <si>
+    <t>(주)엔시스</t>
+  </si>
+  <si>
+    <t>엔시스**1061012</t>
+  </si>
+  <si>
+    <t>진승언</t>
+  </si>
+  <si>
+    <t>041-568-7222</t>
+  </si>
+  <si>
+    <t>yjhwang@n-sys.co.kr</t>
+  </si>
+  <si>
+    <t>31418</t>
+  </si>
+  <si>
+    <t>충청남도 아산시 음봉면 스마트산단3로 18</t>
+  </si>
+  <si>
+    <t>제조 외</t>
+  </si>
+  <si>
+    <t>자동화설비제작및가공</t>
+  </si>
+  <si>
+    <t>젠올데이</t>
+  </si>
+  <si>
+    <t>젠올데이5241010</t>
+  </si>
+  <si>
+    <t>김은호</t>
+  </si>
+  <si>
+    <t>01048461415</t>
+  </si>
+  <si>
+    <t>euniory@naver.com</t>
+  </si>
+  <si>
+    <t>15476</t>
+  </si>
+  <si>
+    <t>경기도 안산시 단원구 광덕서로 54 (고잔동)</t>
+  </si>
+  <si>
+    <t>혜준스토어</t>
+  </si>
+  <si>
+    <t>혜준스토5231015</t>
+  </si>
+  <si>
+    <t>최혜림</t>
+  </si>
+  <si>
+    <t>010-7313-8356</t>
+  </si>
+  <si>
+    <t>en2zz@naver.com</t>
+  </si>
+  <si>
+    <t>경기도 파주시 소리천로 203 (와동동, 가람마을14단지)1402동 1605호</t>
+  </si>
+  <si>
+    <t>피즈모 유한회사</t>
+  </si>
+  <si>
+    <t>피즈모**1251015</t>
+  </si>
+  <si>
+    <t>WANG QIN</t>
+  </si>
+  <si>
+    <t>01082916183</t>
+  </si>
+  <si>
+    <t>1527303592@qq.com</t>
+  </si>
+  <si>
+    <t>부산광역시 강서구 신호삼로 66(신호동)삼성빌딩</t>
+  </si>
+  <si>
+    <t>글로벌픽</t>
+  </si>
+  <si>
+    <t>글로벌픽5181011</t>
+  </si>
+  <si>
+    <t>노복순</t>
+  </si>
+  <si>
+    <t>01076050760</t>
+  </si>
+  <si>
+    <t>bubbleman24@naver.com</t>
+  </si>
+  <si>
+    <t>58115</t>
+  </si>
+  <si>
+    <t>전라남도 화순군 화순읍 용곡3길 106</t>
+  </si>
+  <si>
+    <t>서비스 외</t>
+  </si>
+  <si>
+    <t>무인빨래방 외</t>
+  </si>
+  <si>
+    <t>주식회사 하이올렛</t>
+  </si>
+  <si>
+    <t>하이올렛1221019</t>
+  </si>
+  <si>
+    <t>김진아</t>
+  </si>
+  <si>
+    <t>01080626455</t>
+  </si>
+  <si>
+    <t>hhiolet@naver.com</t>
+  </si>
+  <si>
+    <t>인천광역시 연수구 송도미래로 30, E동 2310호</t>
+  </si>
+  <si>
+    <t>전자상거래소매업외</t>
+  </si>
+  <si>
+    <t>모두바잉</t>
+  </si>
+  <si>
+    <t>모두바잉5221015</t>
+  </si>
+  <si>
+    <t>한은정</t>
+  </si>
+  <si>
+    <t>01099968433</t>
+  </si>
+  <si>
+    <t>hej2220@naver.com</t>
+  </si>
+  <si>
+    <t>05275</t>
+  </si>
+  <si>
+    <t>서울특별시 강동구 상일로 55 (상일동, 고덕자이)118동 403호</t>
+  </si>
+  <si>
+    <t>한민국제화학(주)안성제2공장</t>
+  </si>
+  <si>
+    <t>한민국제1901038</t>
+  </si>
+  <si>
+    <t>나용택</t>
+  </si>
+  <si>
+    <t>010-9034-9467</t>
+  </si>
+  <si>
+    <t>hanminch@daum.net</t>
+  </si>
+  <si>
+    <t>17524</t>
+  </si>
+  <si>
+    <t>경기도 안성시 죽산면 걸미로 363-10</t>
+  </si>
+  <si>
+    <t>제조업</t>
+  </si>
+  <si>
+    <t>유리,복층유리</t>
+  </si>
+  <si>
+    <t>(주)블루건설</t>
+  </si>
+  <si>
+    <t>블루건설1072014</t>
+  </si>
+  <si>
+    <t>박찬우</t>
+  </si>
+  <si>
+    <t>010-3513-2393</t>
+  </si>
+  <si>
+    <t>5553100@naver.com</t>
+  </si>
+  <si>
+    <t>41491</t>
+  </si>
+  <si>
+    <t>대구광역시 북구 문주길 29-9 (금호동)</t>
+  </si>
+  <si>
+    <t>건설업외</t>
+  </si>
+  <si>
+    <t>일반건축외</t>
+  </si>
+  <si>
+    <t>마녀홀릭</t>
+  </si>
+  <si>
+    <t>마녀홀릭5231018</t>
+  </si>
+  <si>
+    <t>하리나</t>
+  </si>
+  <si>
+    <t>01050956180</t>
+  </si>
+  <si>
+    <t>rina1082@naver.com</t>
+  </si>
+  <si>
+    <t>15010</t>
+  </si>
+  <si>
+    <t>경기도 시흥시 배곧4로 106-25(배곧동)호반베르디움 센트로하임아파트</t>
+  </si>
+  <si>
+    <t>아온</t>
+  </si>
+  <si>
+    <t>아온****5211013</t>
+  </si>
+  <si>
+    <t>임상현</t>
+  </si>
+  <si>
+    <t>01096085548</t>
+  </si>
+  <si>
+    <t>dqd2134@naver.com</t>
+  </si>
+  <si>
+    <t>03601</t>
+  </si>
+  <si>
+    <t>서울특별시 서대문구 홍은중앙로 128-13(홍은동)</t>
+  </si>
+  <si>
+    <t>해외직구대행업 외</t>
+  </si>
+  <si>
+    <t>주식회사 케이씨씨실리콘 전주</t>
+  </si>
+  <si>
+    <t>케이씨씨1202035</t>
+  </si>
+  <si>
+    <t>송영근</t>
+  </si>
+  <si>
+    <t>55321</t>
+  </si>
+  <si>
+    <t>전북특별자치도 완주군 봉동읍 과학로 801</t>
+  </si>
+  <si>
+    <t>화합물 및 화학제품</t>
+  </si>
+  <si>
+    <t>주식회사 케이씨씨실리콘 영업</t>
+  </si>
+  <si>
+    <t>케이씨씨1202028</t>
+  </si>
+  <si>
+    <t>02-3495-2115</t>
+  </si>
+  <si>
+    <t>06608</t>
+  </si>
+  <si>
+    <t>서울특별시 서초구 사평대로 344 (서초동)</t>
+  </si>
+  <si>
+    <t>화학물질 및 화학제품</t>
+  </si>
+  <si>
+    <t>케이앤피컴퍼니</t>
+  </si>
+  <si>
+    <t>케이앤피5222019</t>
+  </si>
+  <si>
+    <t>김일</t>
+  </si>
+  <si>
+    <t>01063735668</t>
+  </si>
+  <si>
+    <t>kimil1107@naver.com</t>
+  </si>
+  <si>
+    <t>08314</t>
+  </si>
+  <si>
+    <t>서울특별시 구로구 구로동로8길 50 (구로동)</t>
+  </si>
+  <si>
+    <t>소매 외</t>
+  </si>
+  <si>
+    <t>주식회사이레건설산업</t>
+  </si>
+  <si>
+    <t>이레건설1081017</t>
+  </si>
+  <si>
+    <t>정민혁</t>
+  </si>
+  <si>
+    <t>01032497934</t>
+  </si>
+  <si>
+    <t>jyyoon@ereenc.com</t>
+  </si>
+  <si>
+    <t>13002</t>
+  </si>
+  <si>
+    <t>경기도 하남시 감일로72번길 19 (감일동)</t>
+  </si>
+  <si>
+    <t>종합건설 외</t>
+  </si>
+  <si>
+    <t>셀리온 유한회사</t>
+  </si>
+  <si>
+    <t>셀리온**1251014</t>
+  </si>
+  <si>
+    <t>YU LANHAI</t>
+  </si>
+  <si>
+    <t>01073956352</t>
+  </si>
+  <si>
+    <t>404836164@qq.com</t>
+  </si>
+  <si>
+    <t>충청북도 청주시 상당구 성안로74번길 18-1 (남문로1가)</t>
+  </si>
+  <si>
+    <t>전자상거래 소매업 외</t>
+  </si>
+  <si>
+    <t>트리풀마켓</t>
+  </si>
+  <si>
+    <t>트리풀마5251019</t>
+  </si>
+  <si>
+    <t>최아영</t>
+  </si>
+  <si>
+    <t>01038403477</t>
+  </si>
+  <si>
+    <t>trifullmarket@gmail.com</t>
+  </si>
+  <si>
+    <t>29022</t>
+  </si>
+  <si>
+    <t>충청북도 옥천군 동이면 우산로1길 131-8</t>
+  </si>
+  <si>
+    <t>소매업 외</t>
+  </si>
+  <si>
+    <t>명진</t>
+  </si>
+  <si>
+    <t>명진****5081011</t>
+  </si>
+  <si>
+    <t>김주홍</t>
+  </si>
+  <si>
+    <t>01022503800</t>
+  </si>
+  <si>
+    <t>mj5299@naver.com</t>
+  </si>
+  <si>
+    <t>18515</t>
+  </si>
+  <si>
+    <t>경기도 화성시 효행구 정남면 정남동로 33-29</t>
+  </si>
+  <si>
+    <t>LCD,반도체장비,부품</t>
+  </si>
+  <si>
+    <t>(주)유에이아이</t>
+  </si>
+  <si>
+    <t>유에이아1031017</t>
+  </si>
+  <si>
+    <t>노기환</t>
+  </si>
+  <si>
+    <t>01025769650</t>
+  </si>
+  <si>
+    <t>yuna@uai.kr?</t>
+  </si>
+  <si>
+    <t>13516</t>
+  </si>
+  <si>
+    <t>경기도 성남시 분당구 판교로 700 (야탑동)</t>
+  </si>
+  <si>
+    <t>소프트웨어개발및공급</t>
+  </si>
+  <si>
+    <t>엑스마시르트레이딩 유한회사</t>
+  </si>
+  <si>
+    <t>엑스마시1251010</t>
+  </si>
+  <si>
+    <t>QIN WEIWEI</t>
+  </si>
+  <si>
+    <t>07077716872</t>
+  </si>
+  <si>
+    <t>1753625128@qq.com</t>
+  </si>
+  <si>
+    <t>경기도 이천시 향교로 68(창전동)</t>
+  </si>
+  <si>
+    <t>반야월소</t>
+  </si>
+  <si>
+    <t>반야월소5181019</t>
+  </si>
+  <si>
+    <t>황현숙</t>
+  </si>
+  <si>
+    <t>01045337428</t>
+  </si>
+  <si>
+    <t>banyawolso@gmail.com</t>
+  </si>
+  <si>
+    <t>41128</t>
+  </si>
+  <si>
+    <t>대구광역시 동구 반야월북로2길 28, 1층</t>
+  </si>
+  <si>
+    <t>제조업외</t>
+  </si>
+  <si>
+    <t>기타목재가구제조업외</t>
+  </si>
+  <si>
+    <t>인포테크 유한회사</t>
+  </si>
+  <si>
+    <t>인포테크1251019</t>
+  </si>
+  <si>
+    <t>CHEN GEYANG</t>
+  </si>
+  <si>
+    <t>07047321871</t>
+  </si>
+  <si>
+    <t>i6270959@gmail.com</t>
+  </si>
+  <si>
+    <t>경기도 김포시 김포한강9로75번길 22(구래동)</t>
+  </si>
+  <si>
+    <t>스티브잉크 유한회사</t>
+  </si>
+  <si>
+    <t>스티브잉1261019</t>
+  </si>
+  <si>
+    <t>GUO XIANGAN</t>
+  </si>
+  <si>
+    <t>07077329074</t>
+  </si>
+  <si>
+    <t>19940322gxg@gmail.com</t>
+  </si>
+  <si>
+    <t>05043</t>
+  </si>
+  <si>
+    <t>서울특별시 광진구 자양로18길 17 (구의동)</t>
+  </si>
+  <si>
+    <t>청양구기자원예농업협동조합</t>
+  </si>
+  <si>
+    <t>청양구기2941016</t>
+  </si>
+  <si>
+    <t>복영수</t>
+  </si>
+  <si>
+    <t>01062313652</t>
+  </si>
+  <si>
+    <t>cykukija@hanmail.net</t>
+  </si>
+  <si>
+    <t>33332</t>
+  </si>
+  <si>
+    <t>충청남도 청양군 청양읍 칠갑산로4길 28</t>
+  </si>
+  <si>
+    <t>서비스,제조 외</t>
+  </si>
+  <si>
+    <t>위탁,다류 외</t>
+  </si>
+  <si>
+    <t>성선백화점</t>
+  </si>
+  <si>
+    <t>성선백화5251012</t>
+  </si>
+  <si>
+    <t>LI YAJU</t>
+  </si>
+  <si>
+    <t>01084128876</t>
+  </si>
+  <si>
+    <t>ly133334450@163.com</t>
+  </si>
+  <si>
+    <t>05037</t>
+  </si>
+  <si>
+    <t>서울 광진구 광나루로38길 63</t>
+  </si>
+  <si>
+    <t>소매</t>
+  </si>
+  <si>
+    <t>일용잡화</t>
+  </si>
+  <si>
+    <t>(주)노디너리</t>
+  </si>
+  <si>
+    <t>노디너리1201015</t>
+  </si>
+  <si>
+    <t>백문기</t>
+  </si>
+  <si>
+    <t>01022381263</t>
+  </si>
+  <si>
+    <t>sales@nordinary.co.kr</t>
+  </si>
+  <si>
+    <t>18469</t>
+  </si>
+  <si>
+    <t>경기도 화성시 동탄구 동탄첨단산업1로 27 (영천동)</t>
+  </si>
+  <si>
+    <t>화장품 원료 외</t>
+  </si>
+  <si>
+    <t>오성홀딩스 주식회사</t>
+  </si>
+  <si>
+    <t>오성홀딩1211015</t>
+  </si>
+  <si>
+    <t>서일현</t>
+  </si>
+  <si>
+    <t>01031122210</t>
+  </si>
+  <si>
+    <t>finetex77@naver.com</t>
+  </si>
+  <si>
+    <t>22530</t>
+  </si>
+  <si>
+    <t>인천광역시 동구 방축로83번길 23 (송림동)</t>
+  </si>
+  <si>
+    <t>공업자재 외</t>
+  </si>
+  <si>
+    <t>샵큐</t>
+  </si>
+  <si>
+    <t>샵큐****5191018</t>
+  </si>
+  <si>
+    <t>이상범</t>
+  </si>
+  <si>
+    <t>01052416606</t>
+  </si>
+  <si>
+    <t>shopq2@shopq.co.kr</t>
+  </si>
+  <si>
+    <t>12285</t>
+  </si>
+  <si>
+    <t>경기도 남양주시 다산순환로 365(다산동)힐스테이트 다산</t>
+  </si>
+  <si>
+    <t>도매 및 소매업 외</t>
+  </si>
+  <si>
+    <t>키맨</t>
+  </si>
+  <si>
+    <t>키맨****5261019</t>
+  </si>
+  <si>
+    <t>김시현</t>
+  </si>
+  <si>
+    <t>01093188386</t>
+  </si>
+  <si>
+    <t>foremost.keyman@gmail.com</t>
+  </si>
+  <si>
+    <t>10908</t>
+  </si>
+  <si>
+    <t>경기도 파주시 와석순환로 16 (야당동, 롯데캐슬파크타운)</t>
+  </si>
+  <si>
+    <t>업튼</t>
+  </si>
+  <si>
+    <t>업튼****5151014</t>
+  </si>
+  <si>
+    <t>임성건</t>
+  </si>
+  <si>
+    <t>01035827371</t>
+  </si>
+  <si>
+    <t>5827371@naver.com</t>
+  </si>
+  <si>
+    <t>48582</t>
+  </si>
+  <si>
+    <t>부산광역시 남구 용호로159번길 94 (용호동)</t>
+  </si>
+  <si>
+    <t>스포츠의류 외</t>
+  </si>
+  <si>
+    <t>전자상거래업 외</t>
+  </si>
+  <si>
+    <t>페블러스</t>
+  </si>
+  <si>
+    <t>페블러스5171017</t>
+  </si>
+  <si>
+    <t>이승진</t>
+  </si>
+  <si>
+    <t>01034240604</t>
+  </si>
+  <si>
+    <t>fabulous1030@naver.com</t>
+  </si>
+  <si>
+    <t>07264</t>
+  </si>
+  <si>
+    <t>서울특별시 영등포구 영등포로 109</t>
+  </si>
+  <si>
+    <t>주식회사 선진식품</t>
+  </si>
+  <si>
+    <t>선진식품1131019</t>
+  </si>
+  <si>
+    <t>김만제</t>
+  </si>
+  <si>
+    <t>01051330228</t>
+  </si>
+  <si>
+    <t>sunjin0063@hanmail.net</t>
+  </si>
+  <si>
+    <t>18255</t>
+  </si>
+  <si>
+    <t>경기도 화성시 만세구 남양읍 주석로184번길 69</t>
+  </si>
+  <si>
+    <t>순대 외</t>
+  </si>
+  <si>
+    <t>퍼포먼스 메이커</t>
+  </si>
+  <si>
+    <t>퍼포먼스5231012</t>
+  </si>
+  <si>
+    <t>오시훈</t>
+  </si>
+  <si>
+    <t>01092607739</t>
+  </si>
+  <si>
+    <t>sihun950405@gmail.com</t>
+  </si>
+  <si>
+    <t>46981</t>
+  </si>
+  <si>
+    <t>부산광역시 사상구 새벽로 170(감전동)</t>
+  </si>
+  <si>
+    <t>(주)안성내츄럴리조트</t>
+  </si>
+  <si>
+    <t>안성내츄1101017</t>
+  </si>
+  <si>
+    <t>곽숙자</t>
+  </si>
+  <si>
+    <t>01037290774</t>
+  </si>
+  <si>
+    <t>uni0774@naver.com</t>
+  </si>
+  <si>
+    <t>17518</t>
+  </si>
+  <si>
+    <t>경기도 안성시 죽산면 죽양대로 136-16</t>
+  </si>
+  <si>
+    <t>생수 생산업 외</t>
+  </si>
+  <si>
+    <t>천일공작소</t>
+  </si>
+  <si>
+    <t>천일공작5211010</t>
+  </si>
+  <si>
+    <t>양희순</t>
+  </si>
+  <si>
+    <t>01056430523</t>
+  </si>
+  <si>
+    <t>yhs123q@naver.com</t>
+  </si>
+  <si>
+    <t>58509</t>
+  </si>
+  <si>
+    <t>전라남도 무안군 현경면 현해로 816</t>
+  </si>
+  <si>
+    <t>(주)채움가구</t>
+  </si>
+  <si>
+    <t>채움가구1181012</t>
+  </si>
+  <si>
+    <t>김만기</t>
+  </si>
+  <si>
+    <t>01090826887</t>
+  </si>
+  <si>
+    <t>chaeum03@naver.com</t>
+  </si>
+  <si>
+    <t>11160</t>
+  </si>
+  <si>
+    <t>경기도 포천시 삼육사로 2019-32 (선단동)</t>
+  </si>
+  <si>
+    <t>가구 외</t>
+  </si>
+  <si>
+    <t>(주)메디치코리아코스메틱</t>
+  </si>
+  <si>
+    <t>메디치코1141014</t>
+  </si>
+  <si>
+    <t>오정미</t>
+  </si>
+  <si>
+    <t>031-666-3120</t>
+  </si>
+  <si>
+    <t>17749</t>
+  </si>
+  <si>
+    <t>경기도 평택시 동삭로 455-64 (칠괴동)</t>
+  </si>
+  <si>
+    <t>화장품</t>
+  </si>
+  <si>
+    <t>몽디자인</t>
+  </si>
+  <si>
+    <t>몽디자인5191017</t>
+  </si>
+  <si>
+    <t>김상엽</t>
+  </si>
+  <si>
+    <t>01049496344</t>
+  </si>
+  <si>
+    <t>mong2131@naver.com</t>
+  </si>
+  <si>
+    <t>21583</t>
+  </si>
+  <si>
+    <t>인천광역시 남동구 선수촌공원로 30 (구월동)</t>
+  </si>
+  <si>
+    <t>건설업,가구 외</t>
+  </si>
+  <si>
+    <t>실내인테리어,디자인</t>
+  </si>
+  <si>
+    <t>하오셀렉트</t>
+  </si>
+  <si>
+    <t>하오셀렉5251015</t>
+  </si>
+  <si>
+    <t>예민서</t>
+  </si>
+  <si>
+    <t>01084586884</t>
+  </si>
+  <si>
+    <t>y0331252@gmail.com</t>
+  </si>
+  <si>
+    <t>48502</t>
+  </si>
+  <si>
+    <t>부산광역시 남구 유엔로157번가길 75 (대연동)</t>
+  </si>
+  <si>
+    <t>주식회사 와클글로벌</t>
+  </si>
+  <si>
+    <t>와클글로1181016</t>
+  </si>
+  <si>
+    <t>김한용</t>
+  </si>
+  <si>
+    <t>01031467488</t>
+  </si>
+  <si>
+    <t>wacle7478@naver.com</t>
+  </si>
+  <si>
+    <t>10910</t>
+  </si>
+  <si>
+    <t>경기도 파주시 하우4길 26-26 (상지석동)</t>
+  </si>
+  <si>
+    <t>폐수처리장비 외</t>
+  </si>
+  <si>
+    <t>하나비</t>
+  </si>
+  <si>
+    <t>하나비**5261011</t>
+  </si>
+  <si>
+    <t>윤승현</t>
+  </si>
+  <si>
+    <t>01095520968</t>
+  </si>
+  <si>
+    <t>Hanabi.luke.yun@gmail.com</t>
+  </si>
+  <si>
+    <t>04968</t>
+  </si>
+  <si>
+    <t>서울특별시 광진구 아차산로73길 48 (광장동)</t>
+  </si>
+  <si>
+    <t>음식점업</t>
+  </si>
+  <si>
+    <t>카페</t>
+  </si>
+  <si>
+    <t>기억한조각</t>
+  </si>
+  <si>
+    <t>기억한조5211017</t>
+  </si>
+  <si>
+    <t>송사라</t>
+  </si>
+  <si>
+    <t>01084902486</t>
+  </si>
+  <si>
+    <t>sosu0412@naver.com</t>
+  </si>
+  <si>
+    <t>35277</t>
+  </si>
+  <si>
+    <t>대전광역시 서구 신갈마로 161 (갈마동)</t>
+  </si>
+  <si>
+    <t>휴게음식점(레터링케</t>
+  </si>
+  <si>
+    <t>(주)글로우서울</t>
+  </si>
+  <si>
+    <t>글로우서1181015</t>
+  </si>
+  <si>
+    <t>유정수,윤성혁</t>
+  </si>
+  <si>
+    <t>01095175658</t>
+  </si>
+  <si>
+    <t>dmi3302@naver.com</t>
+  </si>
+  <si>
+    <t>04351</t>
+  </si>
+  <si>
+    <t>서울특별시 용산구 이태원로17길 23-8(이태원동)오스카164B</t>
+  </si>
+  <si>
+    <t>식음료 외</t>
+  </si>
+  <si>
+    <t>조소</t>
+  </si>
+  <si>
+    <t>조소****5121017</t>
+  </si>
+  <si>
+    <t>조윤형</t>
+  </si>
+  <si>
+    <t>010-8897-8835</t>
+  </si>
+  <si>
+    <t>hw961016@naver.com</t>
+  </si>
+  <si>
+    <t>03974</t>
+  </si>
+  <si>
+    <t>서울특별시 마포구 연남로13길 31(성산동)동양하우징</t>
+  </si>
+  <si>
+    <t>제조업,임대업</t>
+  </si>
+  <si>
+    <t>공연용소품제조 외</t>
+  </si>
+  <si>
+    <t>와이제이 컴퍼니</t>
+  </si>
+  <si>
+    <t>와이제이520e018</t>
+  </si>
+  <si>
+    <t>최용</t>
+  </si>
+  <si>
+    <t>01034419856</t>
+  </si>
+  <si>
+    <t>cy728@daum.net</t>
+  </si>
+  <si>
+    <t>07635</t>
+  </si>
+  <si>
+    <t>서울특별시 강서구 강서로47길 165 (내발산동)</t>
+  </si>
+  <si>
+    <t>주식회사랩가이드</t>
+  </si>
+  <si>
+    <t>랩가이드1151015</t>
+  </si>
+  <si>
+    <t>정승남</t>
+  </si>
+  <si>
+    <t>01093884574</t>
+  </si>
+  <si>
+    <t>tax@labguide.kr</t>
+  </si>
+  <si>
+    <t>41516</t>
+  </si>
+  <si>
+    <t>대구광역시 북구 유통단지로24길 37 (산격동)</t>
+  </si>
+  <si>
+    <t>과학의료장비판매 외</t>
+  </si>
+  <si>
+    <t>주식회사 신우</t>
+  </si>
+  <si>
+    <t>신우****1251019</t>
+  </si>
+  <si>
+    <t>WANG CHENXU</t>
+  </si>
+  <si>
+    <t>010-7628-8629</t>
+  </si>
+  <si>
+    <t>SHINWOOKR2299@gmail.com</t>
+  </si>
+  <si>
+    <t>12759</t>
+  </si>
+  <si>
+    <t>경기도 광주시 경안로 23 (경안동)</t>
+  </si>
+  <si>
+    <t>세화</t>
+  </si>
+  <si>
+    <t>세화****5221010</t>
+  </si>
+  <si>
+    <t>윤명철</t>
+  </si>
+  <si>
+    <t>01058861666</t>
+  </si>
+  <si>
+    <t>seonhwa0117@gmail.com</t>
+  </si>
+  <si>
+    <t>07318</t>
+  </si>
+  <si>
+    <t>서울특별시 영등포구 영등포로79길 9 (신길동)</t>
+  </si>
+  <si>
+    <t>휴온지엑스스튜디오</t>
+  </si>
+  <si>
+    <t>휴온지엑5261010</t>
+  </si>
+  <si>
+    <t>김다슬</t>
+  </si>
+  <si>
+    <t>01033232583</t>
+  </si>
+  <si>
+    <t>hueon.gx@gmail.com</t>
+  </si>
+  <si>
+    <t>13604</t>
+  </si>
+  <si>
+    <t>경기도 성남시 분당구 불곡로 4 (정자동)</t>
+  </si>
+  <si>
+    <t>서비스업</t>
+  </si>
+  <si>
+    <t>매트운동</t>
+  </si>
+  <si>
+    <t>라비엣</t>
+  </si>
+  <si>
+    <t>라비엣**5251014</t>
+  </si>
+  <si>
+    <t>ZHAO YINGLAN</t>
+  </si>
+  <si>
+    <t>01097911588</t>
+  </si>
+  <si>
+    <t>yeongran87@naver.com</t>
+  </si>
+  <si>
+    <t>22776</t>
+  </si>
+  <si>
+    <t>인천광역시 서해구 봉오대로 270 (가정동, 루원시티2차 SK Leaders VIEW)</t>
+  </si>
+  <si>
+    <t>상품 종합 도매업</t>
+  </si>
+  <si>
+    <t>840-86-03374</t>
+  </si>
+  <si>
+    <t>875-41-01139</t>
+  </si>
+  <si>
+    <t>445-87-03647</t>
+  </si>
+  <si>
+    <t>408-81-22298</t>
+  </si>
+  <si>
+    <t>381-45-00803</t>
+  </si>
+  <si>
+    <t>272-50-00901</t>
+  </si>
+  <si>
+    <t>394-46-00994</t>
+  </si>
+  <si>
+    <t>240-87-02913</t>
+  </si>
+  <si>
+    <t>709-81-03705</t>
+  </si>
+  <si>
+    <t>740-74-00579</t>
+  </si>
+  <si>
+    <t>422-06-00497</t>
+  </si>
+  <si>
+    <t>312-81-80677</t>
+  </si>
+  <si>
+    <t>478-24-01794</t>
+  </si>
+  <si>
+    <t>409-52-00695</t>
+  </si>
+  <si>
+    <t>137-88-03573</t>
+  </si>
+  <si>
+    <t>894-06-00896</t>
+  </si>
+  <si>
+    <t>575-87-02653</t>
+  </si>
+  <si>
+    <t>789-46-00834</t>
+  </si>
+  <si>
+    <t>514-85-28353</t>
+  </si>
+  <si>
+    <t>514-81-63105</t>
+  </si>
+  <si>
+    <t>396-09-02576</t>
+  </si>
+  <si>
+    <t>409-46-12133</t>
+  </si>
+  <si>
+    <t>245-85-01462</t>
+  </si>
+  <si>
+    <t>371-85-01723</t>
+  </si>
+  <si>
+    <t>858-71-00317</t>
+  </si>
+  <si>
+    <t>226-81-37637</t>
+  </si>
+  <si>
+    <t>804-87-03716</t>
+  </si>
+  <si>
+    <t>329-08-03205</t>
+  </si>
+  <si>
+    <t>124-44-05299</t>
+  </si>
+  <si>
+    <t>214-87-42876</t>
+  </si>
+  <si>
+    <t>643-81-03521</t>
+  </si>
+  <si>
+    <t>306-31-21718</t>
+  </si>
+  <si>
+    <t>780-87-03268</t>
+  </si>
+  <si>
+    <t>761-86-03649</t>
+  </si>
+  <si>
+    <t>307-82-03603</t>
+  </si>
+  <si>
+    <t>587-07-03196</t>
+  </si>
+  <si>
+    <t>523-81-01821</t>
+  </si>
+  <si>
+    <t>552-87-01985</t>
+  </si>
+  <si>
+    <t>425-47-00427</t>
+  </si>
+  <si>
+    <t>513-24-02136</t>
+  </si>
+  <si>
+    <t>647-46-00054</t>
+  </si>
+  <si>
+    <t>417-52-00245</t>
+  </si>
+  <si>
+    <t>143-81-12952</t>
+  </si>
+  <si>
+    <t>111-13-35944</t>
+  </si>
+  <si>
+    <t>125-81-85383</t>
+  </si>
+  <si>
+    <t>343-27-01048</t>
+  </si>
+  <si>
+    <t>376-86-01050</t>
+  </si>
+  <si>
+    <t>125-86-18439</t>
+  </si>
+  <si>
+    <t>695-71-00375</t>
+  </si>
+  <si>
+    <t>398-06-03191</t>
+  </si>
+  <si>
+    <t>569-88-01068</t>
+  </si>
+  <si>
+    <t>720-22-02050</t>
+  </si>
+  <si>
+    <t>158-02-02029</t>
+  </si>
+  <si>
+    <t>451-88-01049</t>
+  </si>
+  <si>
+    <t>110-18-69859</t>
+  </si>
+  <si>
+    <t>692-51-00285</t>
+  </si>
+  <si>
+    <t>471-86-00171</t>
+  </si>
+  <si>
+    <t>549-88-03363</t>
+  </si>
+  <si>
+    <t>212-26-36848</t>
+  </si>
+  <si>
+    <t>733-72-00596</t>
+  </si>
+  <si>
+    <t>418-58-00707</t>
   </si>
 </sst>
 </file>
@@ -7418,7 +9017,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE6138A4-676B-44A6-82D7-1ADA43310F48}">
-  <dimension ref="A1:K282"/>
+  <dimension ref="A1:K343"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -15707,7 +17306,7 @@
         <v>1912</v>
       </c>
     </row>
-    <row r="273" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="273" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A273" s="32" t="s">
         <v>866</v>
       </c>
@@ -15736,7 +17335,7 @@
         <v>1915</v>
       </c>
     </row>
-    <row r="274" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="274" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A274" s="32" t="s">
         <v>867</v>
       </c>
@@ -15765,7 +17364,7 @@
         <v>1917</v>
       </c>
     </row>
-    <row r="275" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="275" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A275" s="32" t="s">
         <v>868</v>
       </c>
@@ -15794,7 +17393,7 @@
         <v>1920</v>
       </c>
     </row>
-    <row r="276" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="276" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A276" s="32" t="s">
         <v>869</v>
       </c>
@@ -15823,7 +17422,7 @@
         <v>1922</v>
       </c>
     </row>
-    <row r="277" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="277" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A277" s="32" t="s">
         <v>870</v>
       </c>
@@ -15852,7 +17451,7 @@
         <v>1925</v>
       </c>
     </row>
-    <row r="278" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="278" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A278" s="32" t="s">
         <v>871</v>
       </c>
@@ -15881,7 +17480,7 @@
         <v>1927</v>
       </c>
     </row>
-    <row r="279" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="279" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A279" s="32" t="s">
         <v>872</v>
       </c>
@@ -15910,7 +17509,7 @@
         <v>1929</v>
       </c>
     </row>
-    <row r="280" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="280" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A280" s="32" t="s">
         <v>1930</v>
       </c>
@@ -15939,7 +17538,7 @@
         <v>1935</v>
       </c>
     </row>
-    <row r="281" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="281" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A281" s="32" t="s">
         <v>1938</v>
       </c>
@@ -15968,7 +17567,7 @@
         <v>1944</v>
       </c>
     </row>
-    <row r="282" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="282" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A282" s="32" t="s">
         <v>1951</v>
       </c>
@@ -15997,16 +17596,1968 @@
         <v>1947</v>
       </c>
     </row>
+    <row r="283" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A283" t="s">
+        <v>2596</v>
+      </c>
+      <c r="B283" t="s">
+        <v>2124</v>
+      </c>
+      <c r="C283" t="s">
+        <v>2125</v>
+      </c>
+      <c r="D283" s="6" t="s">
+        <v>2126</v>
+      </c>
+      <c r="E283" s="6" t="s">
+        <v>2127</v>
+      </c>
+      <c r="F283" s="6" t="s">
+        <v>2128</v>
+      </c>
+      <c r="H283" s="9" t="s">
+        <v>1508</v>
+      </c>
+      <c r="I283" t="s">
+        <v>2129</v>
+      </c>
+      <c r="J283" t="s">
+        <v>280</v>
+      </c>
+      <c r="K283" t="s">
+        <v>2130</v>
+      </c>
+    </row>
+    <row r="284" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A284" t="s">
+        <v>2597</v>
+      </c>
+      <c r="B284" t="s">
+        <v>2132</v>
+      </c>
+      <c r="C284" t="s">
+        <v>2133</v>
+      </c>
+      <c r="D284" s="6" t="s">
+        <v>2134</v>
+      </c>
+      <c r="E284" s="6" t="s">
+        <v>2135</v>
+      </c>
+      <c r="F284" s="6" t="s">
+        <v>2136</v>
+      </c>
+      <c r="H284" s="9" t="s">
+        <v>2137</v>
+      </c>
+      <c r="I284" t="s">
+        <v>2138</v>
+      </c>
+      <c r="J284" t="s">
+        <v>280</v>
+      </c>
+      <c r="K284" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="285" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A285" t="s">
+        <v>2598</v>
+      </c>
+      <c r="B285" t="s">
+        <v>2139</v>
+      </c>
+      <c r="C285" t="s">
+        <v>2140</v>
+      </c>
+      <c r="D285" s="6" t="s">
+        <v>2141</v>
+      </c>
+      <c r="E285" s="6" t="s">
+        <v>2142</v>
+      </c>
+      <c r="F285" s="6" t="s">
+        <v>2143</v>
+      </c>
+      <c r="H285" s="9" t="s">
+        <v>2144</v>
+      </c>
+      <c r="I285" t="s">
+        <v>2145</v>
+      </c>
+      <c r="J285" t="s">
+        <v>280</v>
+      </c>
+      <c r="K285" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="286" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A286" t="s">
+        <v>2599</v>
+      </c>
+      <c r="B286" t="s">
+        <v>2146</v>
+      </c>
+      <c r="C286" t="s">
+        <v>2147</v>
+      </c>
+      <c r="D286" s="6" t="s">
+        <v>2148</v>
+      </c>
+      <c r="E286" s="6" t="s">
+        <v>2149</v>
+      </c>
+      <c r="F286" s="6" t="s">
+        <v>2150</v>
+      </c>
+      <c r="H286" s="9" t="s">
+        <v>2151</v>
+      </c>
+      <c r="I286" t="s">
+        <v>2152</v>
+      </c>
+      <c r="J286" t="s">
+        <v>2153</v>
+      </c>
+      <c r="K286" t="s">
+        <v>2154</v>
+      </c>
+    </row>
+    <row r="287" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A287" t="s">
+        <v>2600</v>
+      </c>
+      <c r="B287" t="s">
+        <v>2155</v>
+      </c>
+      <c r="C287" t="s">
+        <v>2156</v>
+      </c>
+      <c r="D287" s="6" t="s">
+        <v>2157</v>
+      </c>
+      <c r="E287" s="6" t="s">
+        <v>2158</v>
+      </c>
+      <c r="F287" s="6" t="s">
+        <v>2159</v>
+      </c>
+      <c r="H287" s="9" t="s">
+        <v>2160</v>
+      </c>
+      <c r="I287" t="s">
+        <v>2161</v>
+      </c>
+      <c r="J287" t="s">
+        <v>280</v>
+      </c>
+      <c r="K287" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="288" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A288" t="s">
+        <v>2601</v>
+      </c>
+      <c r="B288" t="s">
+        <v>2162</v>
+      </c>
+      <c r="C288" t="s">
+        <v>2163</v>
+      </c>
+      <c r="D288" s="6" t="s">
+        <v>2164</v>
+      </c>
+      <c r="E288" s="6" t="s">
+        <v>2165</v>
+      </c>
+      <c r="F288" s="6" t="s">
+        <v>2166</v>
+      </c>
+      <c r="H288" s="9" t="s">
+        <v>2167</v>
+      </c>
+      <c r="I288" t="s">
+        <v>2168</v>
+      </c>
+      <c r="J288" t="s">
+        <v>280</v>
+      </c>
+      <c r="K288" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="289" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A289" t="s">
+        <v>2602</v>
+      </c>
+      <c r="B289" t="s">
+        <v>2169</v>
+      </c>
+      <c r="C289" t="s">
+        <v>2170</v>
+      </c>
+      <c r="D289" s="6" t="s">
+        <v>2171</v>
+      </c>
+      <c r="E289" s="6" t="s">
+        <v>2172</v>
+      </c>
+      <c r="F289" s="6" t="s">
+        <v>2173</v>
+      </c>
+      <c r="H289" s="9" t="s">
+        <v>2174</v>
+      </c>
+      <c r="I289" t="s">
+        <v>2175</v>
+      </c>
+      <c r="J289" t="s">
+        <v>2176</v>
+      </c>
+      <c r="K289" t="s">
+        <v>2177</v>
+      </c>
+    </row>
+    <row r="290" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A290" t="s">
+        <v>2603</v>
+      </c>
+      <c r="B290" t="s">
+        <v>2178</v>
+      </c>
+      <c r="C290" t="s">
+        <v>2179</v>
+      </c>
+      <c r="D290" s="6" t="s">
+        <v>2180</v>
+      </c>
+      <c r="E290" s="6" t="s">
+        <v>2181</v>
+      </c>
+      <c r="F290" s="6" t="s">
+        <v>2182</v>
+      </c>
+      <c r="H290" s="9" t="s">
+        <v>2183</v>
+      </c>
+      <c r="I290" t="s">
+        <v>2184</v>
+      </c>
+      <c r="J290" t="s">
+        <v>2185</v>
+      </c>
+      <c r="K290" t="s">
+        <v>2186</v>
+      </c>
+    </row>
+    <row r="291" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A291" t="s">
+        <v>2604</v>
+      </c>
+      <c r="B291" t="s">
+        <v>2187</v>
+      </c>
+      <c r="C291" t="s">
+        <v>2188</v>
+      </c>
+      <c r="D291" s="6" t="s">
+        <v>2189</v>
+      </c>
+      <c r="E291" s="6" t="s">
+        <v>2190</v>
+      </c>
+      <c r="F291" s="6" t="s">
+        <v>2191</v>
+      </c>
+      <c r="H291" s="9" t="s">
+        <v>2192</v>
+      </c>
+      <c r="I291" t="s">
+        <v>2193</v>
+      </c>
+      <c r="J291" t="s">
+        <v>2194</v>
+      </c>
+      <c r="K291" t="s">
+        <v>2130</v>
+      </c>
+    </row>
+    <row r="292" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A292" t="s">
+        <v>2605</v>
+      </c>
+      <c r="B292" t="s">
+        <v>2195</v>
+      </c>
+      <c r="C292" t="s">
+        <v>2196</v>
+      </c>
+      <c r="D292" s="6" t="s">
+        <v>2197</v>
+      </c>
+      <c r="E292" s="6" t="s">
+        <v>2198</v>
+      </c>
+      <c r="F292" s="6" t="s">
+        <v>2199</v>
+      </c>
+      <c r="H292" s="9" t="s">
+        <v>2200</v>
+      </c>
+      <c r="I292" t="s">
+        <v>2201</v>
+      </c>
+      <c r="J292" t="s">
+        <v>280</v>
+      </c>
+      <c r="K292" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="293" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A293" t="s">
+        <v>2606</v>
+      </c>
+      <c r="B293" t="s">
+        <v>2202</v>
+      </c>
+      <c r="C293" t="s">
+        <v>2203</v>
+      </c>
+      <c r="D293" s="6" t="s">
+        <v>2204</v>
+      </c>
+      <c r="E293" s="6" t="s">
+        <v>2205</v>
+      </c>
+      <c r="F293" s="6" t="s">
+        <v>2206</v>
+      </c>
+      <c r="H293" s="9" t="s">
+        <v>2207</v>
+      </c>
+      <c r="I293" t="s">
+        <v>2208</v>
+      </c>
+      <c r="J293" t="s">
+        <v>2209</v>
+      </c>
+      <c r="K293" t="s">
+        <v>2210</v>
+      </c>
+    </row>
+    <row r="294" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A294" t="s">
+        <v>2607</v>
+      </c>
+      <c r="B294" t="s">
+        <v>2211</v>
+      </c>
+      <c r="C294" t="s">
+        <v>2212</v>
+      </c>
+      <c r="D294" s="6" t="s">
+        <v>2213</v>
+      </c>
+      <c r="E294" s="6" t="s">
+        <v>2214</v>
+      </c>
+      <c r="F294" s="6" t="s">
+        <v>2215</v>
+      </c>
+      <c r="H294" s="9" t="s">
+        <v>2216</v>
+      </c>
+      <c r="I294" t="s">
+        <v>2217</v>
+      </c>
+      <c r="J294" t="s">
+        <v>2218</v>
+      </c>
+      <c r="K294" t="s">
+        <v>2219</v>
+      </c>
+    </row>
+    <row r="295" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A295" t="s">
+        <v>2608</v>
+      </c>
+      <c r="B295" t="s">
+        <v>2220</v>
+      </c>
+      <c r="C295" t="s">
+        <v>2221</v>
+      </c>
+      <c r="D295" s="6" t="s">
+        <v>2222</v>
+      </c>
+      <c r="E295" s="6" t="s">
+        <v>2223</v>
+      </c>
+      <c r="F295" s="6" t="s">
+        <v>2224</v>
+      </c>
+      <c r="H295" s="9" t="s">
+        <v>2225</v>
+      </c>
+      <c r="I295" t="s">
+        <v>2226</v>
+      </c>
+      <c r="J295" t="s">
+        <v>280</v>
+      </c>
+      <c r="K295" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="296" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A296" t="s">
+        <v>2609</v>
+      </c>
+      <c r="B296" t="s">
+        <v>2227</v>
+      </c>
+      <c r="C296" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D296" s="6" t="s">
+        <v>2229</v>
+      </c>
+      <c r="E296" s="6" t="s">
+        <v>2230</v>
+      </c>
+      <c r="F296" s="6" t="s">
+        <v>2231</v>
+      </c>
+      <c r="H296" s="9" t="s">
+        <v>1453</v>
+      </c>
+      <c r="I296" t="s">
+        <v>2232</v>
+      </c>
+      <c r="J296" t="s">
+        <v>2209</v>
+      </c>
+      <c r="K296" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="297" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A297" t="s">
+        <v>2610</v>
+      </c>
+      <c r="B297" t="s">
+        <v>2233</v>
+      </c>
+      <c r="C297" t="s">
+        <v>2234</v>
+      </c>
+      <c r="D297" s="6" t="s">
+        <v>2235</v>
+      </c>
+      <c r="E297" s="6" t="s">
+        <v>2236</v>
+      </c>
+      <c r="F297" s="6" t="s">
+        <v>2237</v>
+      </c>
+      <c r="H297" s="9" t="s">
+        <v>1635</v>
+      </c>
+      <c r="I297" t="s">
+        <v>2238</v>
+      </c>
+      <c r="J297" t="s">
+        <v>280</v>
+      </c>
+      <c r="K297" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="298" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A298" t="s">
+        <v>2611</v>
+      </c>
+      <c r="B298" t="s">
+        <v>2239</v>
+      </c>
+      <c r="C298" t="s">
+        <v>2240</v>
+      </c>
+      <c r="D298" s="6" t="s">
+        <v>2241</v>
+      </c>
+      <c r="E298" s="6" t="s">
+        <v>2242</v>
+      </c>
+      <c r="F298" s="6" t="s">
+        <v>2243</v>
+      </c>
+      <c r="H298" s="9" t="s">
+        <v>2244</v>
+      </c>
+      <c r="I298" t="s">
+        <v>2245</v>
+      </c>
+      <c r="J298" t="s">
+        <v>2246</v>
+      </c>
+      <c r="K298" t="s">
+        <v>2247</v>
+      </c>
+    </row>
+    <row r="299" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A299" t="s">
+        <v>2612</v>
+      </c>
+      <c r="B299" t="s">
+        <v>2248</v>
+      </c>
+      <c r="C299" t="s">
+        <v>2249</v>
+      </c>
+      <c r="D299" s="6" t="s">
+        <v>2250</v>
+      </c>
+      <c r="E299" s="6" t="s">
+        <v>2251</v>
+      </c>
+      <c r="F299" s="6" t="s">
+        <v>2252</v>
+      </c>
+      <c r="H299" s="9" t="s">
+        <v>1437</v>
+      </c>
+      <c r="I299" t="s">
+        <v>2253</v>
+      </c>
+      <c r="J299" t="s">
+        <v>2185</v>
+      </c>
+      <c r="K299" t="s">
+        <v>2254</v>
+      </c>
+    </row>
+    <row r="300" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A300" t="s">
+        <v>2613</v>
+      </c>
+      <c r="B300" t="s">
+        <v>2255</v>
+      </c>
+      <c r="C300" t="s">
+        <v>2256</v>
+      </c>
+      <c r="D300" s="6" t="s">
+        <v>2257</v>
+      </c>
+      <c r="E300" s="6" t="s">
+        <v>2258</v>
+      </c>
+      <c r="F300" s="6" t="s">
+        <v>2259</v>
+      </c>
+      <c r="H300" s="9" t="s">
+        <v>2260</v>
+      </c>
+      <c r="I300" t="s">
+        <v>2261</v>
+      </c>
+      <c r="J300" t="s">
+        <v>280</v>
+      </c>
+      <c r="K300" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="301" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A301" t="s">
+        <v>2614</v>
+      </c>
+      <c r="B301" t="s">
+        <v>2262</v>
+      </c>
+      <c r="C301" t="s">
+        <v>2263</v>
+      </c>
+      <c r="D301" s="6" t="s">
+        <v>2264</v>
+      </c>
+      <c r="E301" s="6" t="s">
+        <v>2265</v>
+      </c>
+      <c r="F301" s="6" t="s">
+        <v>2266</v>
+      </c>
+      <c r="H301" s="9" t="s">
+        <v>2267</v>
+      </c>
+      <c r="I301" t="s">
+        <v>2268</v>
+      </c>
+      <c r="J301" t="s">
+        <v>2269</v>
+      </c>
+      <c r="K301" t="s">
+        <v>2270</v>
+      </c>
+    </row>
+    <row r="302" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A302" t="s">
+        <v>2615</v>
+      </c>
+      <c r="B302" t="s">
+        <v>2271</v>
+      </c>
+      <c r="C302" t="s">
+        <v>2272</v>
+      </c>
+      <c r="D302" s="6" t="s">
+        <v>2273</v>
+      </c>
+      <c r="E302" s="6" t="s">
+        <v>2274</v>
+      </c>
+      <c r="F302" s="6" t="s">
+        <v>2275</v>
+      </c>
+      <c r="H302" s="9" t="s">
+        <v>2276</v>
+      </c>
+      <c r="I302" t="s">
+        <v>2277</v>
+      </c>
+      <c r="J302" t="s">
+        <v>2278</v>
+      </c>
+      <c r="K302" t="s">
+        <v>2279</v>
+      </c>
+    </row>
+    <row r="303" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A303" t="s">
+        <v>2616</v>
+      </c>
+      <c r="B303" t="s">
+        <v>2280</v>
+      </c>
+      <c r="C303" t="s">
+        <v>2281</v>
+      </c>
+      <c r="D303" s="6" t="s">
+        <v>2282</v>
+      </c>
+      <c r="E303" s="6" t="s">
+        <v>2283</v>
+      </c>
+      <c r="F303" s="6" t="s">
+        <v>2284</v>
+      </c>
+      <c r="H303" s="9" t="s">
+        <v>2285</v>
+      </c>
+      <c r="I303" t="s">
+        <v>2286</v>
+      </c>
+      <c r="J303" t="s">
+        <v>2209</v>
+      </c>
+      <c r="K303" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="304" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A304" t="s">
+        <v>2617</v>
+      </c>
+      <c r="B304" t="s">
+        <v>2287</v>
+      </c>
+      <c r="C304" t="s">
+        <v>2288</v>
+      </c>
+      <c r="D304" s="6" t="s">
+        <v>2289</v>
+      </c>
+      <c r="E304" s="6" t="s">
+        <v>2290</v>
+      </c>
+      <c r="F304" s="6" t="s">
+        <v>2291</v>
+      </c>
+      <c r="H304" s="9" t="s">
+        <v>2292</v>
+      </c>
+      <c r="I304" t="s">
+        <v>2293</v>
+      </c>
+      <c r="J304" t="s">
+        <v>280</v>
+      </c>
+      <c r="K304" t="s">
+        <v>2294</v>
+      </c>
+    </row>
+    <row r="305" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A305" t="s">
+        <v>2618</v>
+      </c>
+      <c r="B305" t="s">
+        <v>2295</v>
+      </c>
+      <c r="C305" t="s">
+        <v>2296</v>
+      </c>
+      <c r="D305" s="6" t="s">
+        <v>2297</v>
+      </c>
+      <c r="E305" s="6" t="s">
+        <v>1113</v>
+      </c>
+      <c r="F305" s="6" t="s">
+        <v>1113</v>
+      </c>
+      <c r="H305" s="9" t="s">
+        <v>2298</v>
+      </c>
+      <c r="I305" t="s">
+        <v>2299</v>
+      </c>
+      <c r="J305" t="s">
+        <v>2269</v>
+      </c>
+      <c r="K305" t="s">
+        <v>2300</v>
+      </c>
+    </row>
+    <row r="306" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A306" t="s">
+        <v>2619</v>
+      </c>
+      <c r="B306" t="s">
+        <v>2301</v>
+      </c>
+      <c r="C306" t="s">
+        <v>2302</v>
+      </c>
+      <c r="D306" s="6" t="s">
+        <v>2297</v>
+      </c>
+      <c r="E306" s="6" t="s">
+        <v>2303</v>
+      </c>
+      <c r="F306" s="6" t="s">
+        <v>1113</v>
+      </c>
+      <c r="H306" s="9" t="s">
+        <v>2304</v>
+      </c>
+      <c r="I306" t="s">
+        <v>2305</v>
+      </c>
+      <c r="J306" t="s">
+        <v>280</v>
+      </c>
+      <c r="K306" t="s">
+        <v>2306</v>
+      </c>
+    </row>
+    <row r="307" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A307" t="s">
+        <v>2620</v>
+      </c>
+      <c r="B307" t="s">
+        <v>2307</v>
+      </c>
+      <c r="C307" t="s">
+        <v>2308</v>
+      </c>
+      <c r="D307" s="6" t="s">
+        <v>2309</v>
+      </c>
+      <c r="E307" s="6" t="s">
+        <v>2310</v>
+      </c>
+      <c r="F307" s="6" t="s">
+        <v>2311</v>
+      </c>
+      <c r="H307" s="9" t="s">
+        <v>2312</v>
+      </c>
+      <c r="I307" t="s">
+        <v>2313</v>
+      </c>
+      <c r="J307" t="s">
+        <v>2314</v>
+      </c>
+      <c r="K307" t="s">
+        <v>2131</v>
+      </c>
+    </row>
+    <row r="308" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A308" t="s">
+        <v>2621</v>
+      </c>
+      <c r="B308" t="s">
+        <v>2315</v>
+      </c>
+      <c r="C308" t="s">
+        <v>2316</v>
+      </c>
+      <c r="D308" s="6" t="s">
+        <v>2317</v>
+      </c>
+      <c r="E308" s="6" t="s">
+        <v>2318</v>
+      </c>
+      <c r="F308" s="6" t="s">
+        <v>2319</v>
+      </c>
+      <c r="H308" s="9" t="s">
+        <v>2320</v>
+      </c>
+      <c r="I308" t="s">
+        <v>2321</v>
+      </c>
+      <c r="J308" t="s">
+        <v>2153</v>
+      </c>
+      <c r="K308" t="s">
+        <v>2322</v>
+      </c>
+    </row>
+    <row r="309" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A309" t="s">
+        <v>2622</v>
+      </c>
+      <c r="B309" t="s">
+        <v>2323</v>
+      </c>
+      <c r="C309" t="s">
+        <v>2324</v>
+      </c>
+      <c r="D309" s="6" t="s">
+        <v>2325</v>
+      </c>
+      <c r="E309" s="6" t="s">
+        <v>2326</v>
+      </c>
+      <c r="F309" s="6" t="s">
+        <v>2327</v>
+      </c>
+      <c r="H309" s="9" t="s">
+        <v>1494</v>
+      </c>
+      <c r="I309" t="s">
+        <v>2328</v>
+      </c>
+      <c r="J309" t="s">
+        <v>280</v>
+      </c>
+      <c r="K309" t="s">
+        <v>2329</v>
+      </c>
+    </row>
+    <row r="310" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A310" t="s">
+        <v>2623</v>
+      </c>
+      <c r="B310" t="s">
+        <v>2330</v>
+      </c>
+      <c r="C310" t="s">
+        <v>2331</v>
+      </c>
+      <c r="D310" s="6" t="s">
+        <v>2332</v>
+      </c>
+      <c r="E310" s="6" t="s">
+        <v>2333</v>
+      </c>
+      <c r="F310" s="6" t="s">
+        <v>2334</v>
+      </c>
+      <c r="H310" s="9" t="s">
+        <v>2335</v>
+      </c>
+      <c r="I310" t="s">
+        <v>2336</v>
+      </c>
+      <c r="J310" t="s">
+        <v>2337</v>
+      </c>
+      <c r="K310" t="s">
+        <v>2329</v>
+      </c>
+    </row>
+    <row r="311" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A311" t="s">
+        <v>2624</v>
+      </c>
+      <c r="B311" t="s">
+        <v>2338</v>
+      </c>
+      <c r="C311" t="s">
+        <v>2339</v>
+      </c>
+      <c r="D311" s="6" t="s">
+        <v>2340</v>
+      </c>
+      <c r="E311" s="6" t="s">
+        <v>2341</v>
+      </c>
+      <c r="F311" s="6" t="s">
+        <v>2342</v>
+      </c>
+      <c r="H311" s="9" t="s">
+        <v>2343</v>
+      </c>
+      <c r="I311" t="s">
+        <v>2344</v>
+      </c>
+      <c r="J311" t="s">
+        <v>2269</v>
+      </c>
+      <c r="K311" t="s">
+        <v>2345</v>
+      </c>
+    </row>
+    <row r="312" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A312" t="s">
+        <v>2625</v>
+      </c>
+      <c r="B312" t="s">
+        <v>2346</v>
+      </c>
+      <c r="C312" t="s">
+        <v>2347</v>
+      </c>
+      <c r="D312" s="6" t="s">
+        <v>2348</v>
+      </c>
+      <c r="E312" s="6" t="s">
+        <v>2349</v>
+      </c>
+      <c r="F312" s="6" t="s">
+        <v>2350</v>
+      </c>
+      <c r="H312" s="9" t="s">
+        <v>2351</v>
+      </c>
+      <c r="I312" t="s">
+        <v>2352</v>
+      </c>
+      <c r="J312" t="s">
+        <v>2246</v>
+      </c>
+      <c r="K312" t="s">
+        <v>2353</v>
+      </c>
+    </row>
+    <row r="313" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A313" t="s">
+        <v>2626</v>
+      </c>
+      <c r="B313" t="s">
+        <v>2354</v>
+      </c>
+      <c r="C313" t="s">
+        <v>2355</v>
+      </c>
+      <c r="D313" s="6" t="s">
+        <v>2356</v>
+      </c>
+      <c r="E313" s="6" t="s">
+        <v>2357</v>
+      </c>
+      <c r="F313" s="6" t="s">
+        <v>2358</v>
+      </c>
+      <c r="H313" s="9" t="s">
+        <v>1476</v>
+      </c>
+      <c r="I313" t="s">
+        <v>2359</v>
+      </c>
+      <c r="J313" t="s">
+        <v>280</v>
+      </c>
+      <c r="K313" t="s">
+        <v>2329</v>
+      </c>
+    </row>
+    <row r="314" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A314" t="s">
+        <v>2627</v>
+      </c>
+      <c r="B314" t="s">
+        <v>2360</v>
+      </c>
+      <c r="C314" t="s">
+        <v>2361</v>
+      </c>
+      <c r="D314" s="6" t="s">
+        <v>2362</v>
+      </c>
+      <c r="E314" s="6" t="s">
+        <v>2363</v>
+      </c>
+      <c r="F314" s="6" t="s">
+        <v>2364</v>
+      </c>
+      <c r="H314" s="9" t="s">
+        <v>2365</v>
+      </c>
+      <c r="I314" t="s">
+        <v>2366</v>
+      </c>
+      <c r="J314" t="s">
+        <v>2367</v>
+      </c>
+      <c r="K314" t="s">
+        <v>2368</v>
+      </c>
+    </row>
+    <row r="315" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A315" t="s">
+        <v>2628</v>
+      </c>
+      <c r="B315" t="s">
+        <v>2369</v>
+      </c>
+      <c r="C315" t="s">
+        <v>2370</v>
+      </c>
+      <c r="D315" s="6" t="s">
+        <v>2371</v>
+      </c>
+      <c r="E315" s="6" t="s">
+        <v>2372</v>
+      </c>
+      <c r="F315" s="6" t="s">
+        <v>2373</v>
+      </c>
+      <c r="H315" s="9" t="s">
+        <v>1577</v>
+      </c>
+      <c r="I315" t="s">
+        <v>2374</v>
+      </c>
+      <c r="J315" t="s">
+        <v>280</v>
+      </c>
+      <c r="K315" t="s">
+        <v>2131</v>
+      </c>
+    </row>
+    <row r="316" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A316" t="s">
+        <v>2629</v>
+      </c>
+      <c r="B316" t="s">
+        <v>2375</v>
+      </c>
+      <c r="C316" t="s">
+        <v>2376</v>
+      </c>
+      <c r="D316" s="6" t="s">
+        <v>2377</v>
+      </c>
+      <c r="E316" s="6" t="s">
+        <v>2378</v>
+      </c>
+      <c r="F316" s="6" t="s">
+        <v>2379</v>
+      </c>
+      <c r="H316" s="9" t="s">
+        <v>2380</v>
+      </c>
+      <c r="I316" t="s">
+        <v>2381</v>
+      </c>
+      <c r="J316" t="s">
+        <v>280</v>
+      </c>
+      <c r="K316" t="s">
+        <v>2131</v>
+      </c>
+    </row>
+    <row r="317" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A317" t="s">
+        <v>2630</v>
+      </c>
+      <c r="B317" t="s">
+        <v>2382</v>
+      </c>
+      <c r="C317" t="s">
+        <v>2383</v>
+      </c>
+      <c r="D317" s="6" t="s">
+        <v>2384</v>
+      </c>
+      <c r="E317" s="6" t="s">
+        <v>2385</v>
+      </c>
+      <c r="F317" s="6" t="s">
+        <v>2386</v>
+      </c>
+      <c r="H317" s="9" t="s">
+        <v>2387</v>
+      </c>
+      <c r="I317" t="s">
+        <v>2388</v>
+      </c>
+      <c r="J317" t="s">
+        <v>2389</v>
+      </c>
+      <c r="K317" t="s">
+        <v>2390</v>
+      </c>
+    </row>
+    <row r="318" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A318" t="s">
+        <v>2631</v>
+      </c>
+      <c r="B318" t="s">
+        <v>2391</v>
+      </c>
+      <c r="C318" t="s">
+        <v>2392</v>
+      </c>
+      <c r="D318" s="6" t="s">
+        <v>2393</v>
+      </c>
+      <c r="E318" s="6" t="s">
+        <v>2394</v>
+      </c>
+      <c r="F318" s="6" t="s">
+        <v>2395</v>
+      </c>
+      <c r="H318" s="9" t="s">
+        <v>2396</v>
+      </c>
+      <c r="I318" t="s">
+        <v>2397</v>
+      </c>
+      <c r="J318" t="s">
+        <v>2398</v>
+      </c>
+      <c r="K318" t="s">
+        <v>2399</v>
+      </c>
+    </row>
+    <row r="319" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A319" t="s">
+        <v>2632</v>
+      </c>
+      <c r="B319" t="s">
+        <v>2400</v>
+      </c>
+      <c r="C319" t="s">
+        <v>2401</v>
+      </c>
+      <c r="D319" s="6" t="s">
+        <v>2402</v>
+      </c>
+      <c r="E319" s="6" t="s">
+        <v>2403</v>
+      </c>
+      <c r="F319" s="6" t="s">
+        <v>2404</v>
+      </c>
+      <c r="H319" s="9" t="s">
+        <v>2405</v>
+      </c>
+      <c r="I319" t="s">
+        <v>2406</v>
+      </c>
+      <c r="J319" t="s">
+        <v>2176</v>
+      </c>
+      <c r="K319" t="s">
+        <v>2407</v>
+      </c>
+    </row>
+    <row r="320" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A320" t="s">
+        <v>2633</v>
+      </c>
+      <c r="B320" t="s">
+        <v>2408</v>
+      </c>
+      <c r="C320" t="s">
+        <v>2409</v>
+      </c>
+      <c r="D320" s="6" t="s">
+        <v>2410</v>
+      </c>
+      <c r="E320" s="6" t="s">
+        <v>2411</v>
+      </c>
+      <c r="F320" s="6" t="s">
+        <v>2412</v>
+      </c>
+      <c r="H320" s="9" t="s">
+        <v>2413</v>
+      </c>
+      <c r="I320" t="s">
+        <v>2414</v>
+      </c>
+      <c r="J320" t="s">
+        <v>2176</v>
+      </c>
+      <c r="K320" t="s">
+        <v>2415</v>
+      </c>
+    </row>
+    <row r="321" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A321" t="s">
+        <v>2634</v>
+      </c>
+      <c r="B321" t="s">
+        <v>2416</v>
+      </c>
+      <c r="C321" t="s">
+        <v>2417</v>
+      </c>
+      <c r="D321" s="6" t="s">
+        <v>2418</v>
+      </c>
+      <c r="E321" s="6" t="s">
+        <v>2419</v>
+      </c>
+      <c r="F321" s="6" t="s">
+        <v>2420</v>
+      </c>
+      <c r="H321" s="9" t="s">
+        <v>2421</v>
+      </c>
+      <c r="I321" t="s">
+        <v>2422</v>
+      </c>
+      <c r="J321" t="s">
+        <v>2423</v>
+      </c>
+      <c r="K321" t="s">
+        <v>2329</v>
+      </c>
+    </row>
+    <row r="322" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A322" t="s">
+        <v>2635</v>
+      </c>
+      <c r="B322" t="s">
+        <v>2424</v>
+      </c>
+      <c r="C322" t="s">
+        <v>2425</v>
+      </c>
+      <c r="D322" s="6" t="s">
+        <v>2426</v>
+      </c>
+      <c r="E322" s="6" t="s">
+        <v>2427</v>
+      </c>
+      <c r="F322" s="6" t="s">
+        <v>2428</v>
+      </c>
+      <c r="H322" s="9" t="s">
+        <v>2429</v>
+      </c>
+      <c r="I322" t="s">
+        <v>2430</v>
+      </c>
+      <c r="J322" t="s">
+        <v>280</v>
+      </c>
+      <c r="K322" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="323" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A323" t="s">
+        <v>2636</v>
+      </c>
+      <c r="B323" t="s">
+        <v>2431</v>
+      </c>
+      <c r="C323" t="s">
+        <v>2432</v>
+      </c>
+      <c r="D323" s="6" t="s">
+        <v>2433</v>
+      </c>
+      <c r="E323" s="6" t="s">
+        <v>2434</v>
+      </c>
+      <c r="F323" s="6" t="s">
+        <v>2435</v>
+      </c>
+      <c r="H323" s="9" t="s">
+        <v>2436</v>
+      </c>
+      <c r="I323" t="s">
+        <v>2437</v>
+      </c>
+      <c r="J323" t="s">
+        <v>2176</v>
+      </c>
+      <c r="K323" t="s">
+        <v>2438</v>
+      </c>
+    </row>
+    <row r="324" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A324" t="s">
+        <v>2637</v>
+      </c>
+      <c r="B324" t="s">
+        <v>2440</v>
+      </c>
+      <c r="C324" t="s">
+        <v>2441</v>
+      </c>
+      <c r="D324" s="6" t="s">
+        <v>2442</v>
+      </c>
+      <c r="E324" s="6" t="s">
+        <v>2443</v>
+      </c>
+      <c r="F324" s="6" t="s">
+        <v>2444</v>
+      </c>
+      <c r="H324" s="9" t="s">
+        <v>2445</v>
+      </c>
+      <c r="I324" t="s">
+        <v>2446</v>
+      </c>
+      <c r="J324" t="s">
+        <v>280</v>
+      </c>
+      <c r="K324" t="s">
+        <v>2439</v>
+      </c>
+    </row>
+    <row r="325" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A325" t="s">
+        <v>2638</v>
+      </c>
+      <c r="B325" t="s">
+        <v>2447</v>
+      </c>
+      <c r="C325" t="s">
+        <v>2448</v>
+      </c>
+      <c r="D325" s="6" t="s">
+        <v>2449</v>
+      </c>
+      <c r="E325" s="6" t="s">
+        <v>2450</v>
+      </c>
+      <c r="F325" s="6" t="s">
+        <v>2451</v>
+      </c>
+      <c r="H325" s="9" t="s">
+        <v>2452</v>
+      </c>
+      <c r="I325" t="s">
+        <v>2453</v>
+      </c>
+      <c r="J325" t="s">
+        <v>2176</v>
+      </c>
+      <c r="K325" t="s">
+        <v>2454</v>
+      </c>
+    </row>
+    <row r="326" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A326" t="s">
+        <v>2639</v>
+      </c>
+      <c r="B326" t="s">
+        <v>2455</v>
+      </c>
+      <c r="C326" t="s">
+        <v>2456</v>
+      </c>
+      <c r="D326" s="6" t="s">
+        <v>2457</v>
+      </c>
+      <c r="E326" s="6" t="s">
+        <v>2458</v>
+      </c>
+      <c r="F326" s="6" t="s">
+        <v>2459</v>
+      </c>
+      <c r="H326" s="9" t="s">
+        <v>2460</v>
+      </c>
+      <c r="I326" t="s">
+        <v>2461</v>
+      </c>
+      <c r="J326" t="s">
+        <v>280</v>
+      </c>
+      <c r="K326" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="327" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A327" t="s">
+        <v>2640</v>
+      </c>
+      <c r="B327" t="s">
+        <v>2462</v>
+      </c>
+      <c r="C327" t="s">
+        <v>2463</v>
+      </c>
+      <c r="D327" s="6" t="s">
+        <v>2464</v>
+      </c>
+      <c r="E327" s="6" t="s">
+        <v>2465</v>
+      </c>
+      <c r="F327" s="6" t="s">
+        <v>2466</v>
+      </c>
+      <c r="H327" s="9" t="s">
+        <v>2467</v>
+      </c>
+      <c r="I327" t="s">
+        <v>2468</v>
+      </c>
+      <c r="J327" t="s">
+        <v>2176</v>
+      </c>
+      <c r="K327" t="s">
+        <v>2469</v>
+      </c>
+    </row>
+    <row r="328" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A328" t="s">
+        <v>2641</v>
+      </c>
+      <c r="B328" t="s">
+        <v>2470</v>
+      </c>
+      <c r="C328" t="s">
+        <v>2471</v>
+      </c>
+      <c r="D328" s="6" t="s">
+        <v>2472</v>
+      </c>
+      <c r="E328" s="6" t="s">
+        <v>2473</v>
+      </c>
+      <c r="F328" s="6" t="s">
+        <v>2474</v>
+      </c>
+      <c r="H328" s="9" t="s">
+        <v>2475</v>
+      </c>
+      <c r="I328" t="s">
+        <v>2476</v>
+      </c>
+      <c r="J328" t="s">
+        <v>280</v>
+      </c>
+      <c r="K328" t="s">
+        <v>2329</v>
+      </c>
+    </row>
+    <row r="329" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A329" t="s">
+        <v>2642</v>
+      </c>
+      <c r="B329" t="s">
+        <v>2477</v>
+      </c>
+      <c r="C329" t="s">
+        <v>2478</v>
+      </c>
+      <c r="D329" s="6" t="s">
+        <v>2479</v>
+      </c>
+      <c r="E329" s="6" t="s">
+        <v>2480</v>
+      </c>
+      <c r="F329" s="6" t="s">
+        <v>2481</v>
+      </c>
+      <c r="H329" s="9" t="s">
+        <v>2482</v>
+      </c>
+      <c r="I329" t="s">
+        <v>2483</v>
+      </c>
+      <c r="J329" t="s">
+        <v>2176</v>
+      </c>
+      <c r="K329" t="s">
+        <v>2484</v>
+      </c>
+    </row>
+    <row r="330" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A330" t="s">
+        <v>2643</v>
+      </c>
+      <c r="B330" t="s">
+        <v>2485</v>
+      </c>
+      <c r="C330" t="s">
+        <v>2486</v>
+      </c>
+      <c r="D330" s="6" t="s">
+        <v>2487</v>
+      </c>
+      <c r="E330" s="6" t="s">
+        <v>2488</v>
+      </c>
+      <c r="F330" s="6" t="s">
+        <v>1113</v>
+      </c>
+      <c r="H330" s="9" t="s">
+        <v>2489</v>
+      </c>
+      <c r="I330" t="s">
+        <v>2490</v>
+      </c>
+      <c r="J330" t="s">
+        <v>2269</v>
+      </c>
+      <c r="K330" t="s">
+        <v>2491</v>
+      </c>
+    </row>
+    <row r="331" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A331" t="s">
+        <v>2644</v>
+      </c>
+      <c r="B331" t="s">
+        <v>2492</v>
+      </c>
+      <c r="C331" t="s">
+        <v>2493</v>
+      </c>
+      <c r="D331" s="6" t="s">
+        <v>2494</v>
+      </c>
+      <c r="E331" s="6" t="s">
+        <v>2495</v>
+      </c>
+      <c r="F331" s="6" t="s">
+        <v>2496</v>
+      </c>
+      <c r="H331" s="9" t="s">
+        <v>2497</v>
+      </c>
+      <c r="I331" t="s">
+        <v>2498</v>
+      </c>
+      <c r="J331" t="s">
+        <v>2499</v>
+      </c>
+      <c r="K331" t="s">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="332" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A332" t="s">
+        <v>2645</v>
+      </c>
+      <c r="B332" t="s">
+        <v>2501</v>
+      </c>
+      <c r="C332" t="s">
+        <v>2502</v>
+      </c>
+      <c r="D332" s="6" t="s">
+        <v>2503</v>
+      </c>
+      <c r="E332" s="6" t="s">
+        <v>2504</v>
+      </c>
+      <c r="F332" s="6" t="s">
+        <v>2505</v>
+      </c>
+      <c r="H332" s="9" t="s">
+        <v>2506</v>
+      </c>
+      <c r="I332" t="s">
+        <v>2507</v>
+      </c>
+      <c r="J332" t="s">
+        <v>280</v>
+      </c>
+      <c r="K332" t="s">
+        <v>2294</v>
+      </c>
+    </row>
+    <row r="333" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A333" t="s">
+        <v>2646</v>
+      </c>
+      <c r="B333" t="s">
+        <v>2508</v>
+      </c>
+      <c r="C333" t="s">
+        <v>2509</v>
+      </c>
+      <c r="D333" s="6" t="s">
+        <v>2510</v>
+      </c>
+      <c r="E333" s="6" t="s">
+        <v>2511</v>
+      </c>
+      <c r="F333" s="6" t="s">
+        <v>2512</v>
+      </c>
+      <c r="H333" s="9" t="s">
+        <v>2513</v>
+      </c>
+      <c r="I333" t="s">
+        <v>2514</v>
+      </c>
+      <c r="J333" t="s">
+        <v>2176</v>
+      </c>
+      <c r="K333" t="s">
+        <v>2515</v>
+      </c>
+    </row>
+    <row r="334" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A334" t="s">
+        <v>2647</v>
+      </c>
+      <c r="B334" t="s">
+        <v>2516</v>
+      </c>
+      <c r="C334" t="s">
+        <v>2517</v>
+      </c>
+      <c r="D334" s="6" t="s">
+        <v>2518</v>
+      </c>
+      <c r="E334" s="6" t="s">
+        <v>2519</v>
+      </c>
+      <c r="F334" s="6" t="s">
+        <v>2520</v>
+      </c>
+      <c r="H334" s="9" t="s">
+        <v>2521</v>
+      </c>
+      <c r="I334" t="s">
+        <v>2522</v>
+      </c>
+      <c r="J334" t="s">
+        <v>2523</v>
+      </c>
+      <c r="K334" t="s">
+        <v>2524</v>
+      </c>
+    </row>
+    <row r="335" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A335" t="s">
+        <v>2648</v>
+      </c>
+      <c r="B335" t="s">
+        <v>2525</v>
+      </c>
+      <c r="C335" t="s">
+        <v>2526</v>
+      </c>
+      <c r="D335" s="6" t="s">
+        <v>2527</v>
+      </c>
+      <c r="E335" s="6" t="s">
+        <v>2528</v>
+      </c>
+      <c r="F335" s="6" t="s">
+        <v>2529</v>
+      </c>
+      <c r="H335" s="9" t="s">
+        <v>2530</v>
+      </c>
+      <c r="I335" t="s">
+        <v>2531</v>
+      </c>
+      <c r="J335" t="s">
+        <v>2523</v>
+      </c>
+      <c r="K335" t="s">
+        <v>2532</v>
+      </c>
+    </row>
+    <row r="336" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A336" t="s">
+        <v>2649</v>
+      </c>
+      <c r="B336" t="s">
+        <v>2533</v>
+      </c>
+      <c r="C336" t="s">
+        <v>2534</v>
+      </c>
+      <c r="D336" s="6" t="s">
+        <v>2535</v>
+      </c>
+      <c r="E336" s="6" t="s">
+        <v>2536</v>
+      </c>
+      <c r="F336" s="6" t="s">
+        <v>2537</v>
+      </c>
+      <c r="H336" s="9" t="s">
+        <v>2538</v>
+      </c>
+      <c r="I336" t="s">
+        <v>2539</v>
+      </c>
+      <c r="J336" t="s">
+        <v>2423</v>
+      </c>
+      <c r="K336" t="s">
+        <v>2540</v>
+      </c>
+    </row>
+    <row r="337" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A337" t="s">
+        <v>2650</v>
+      </c>
+      <c r="B337" t="s">
+        <v>2541</v>
+      </c>
+      <c r="C337" t="s">
+        <v>2542</v>
+      </c>
+      <c r="D337" s="6" t="s">
+        <v>2543</v>
+      </c>
+      <c r="E337" s="6" t="s">
+        <v>2544</v>
+      </c>
+      <c r="F337" s="6" t="s">
+        <v>2545</v>
+      </c>
+      <c r="H337" s="9" t="s">
+        <v>2546</v>
+      </c>
+      <c r="I337" t="s">
+        <v>2547</v>
+      </c>
+      <c r="J337" t="s">
+        <v>2548</v>
+      </c>
+      <c r="K337" t="s">
+        <v>2549</v>
+      </c>
+    </row>
+    <row r="338" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A338" t="s">
+        <v>2651</v>
+      </c>
+      <c r="B338" t="s">
+        <v>2550</v>
+      </c>
+      <c r="C338" t="s">
+        <v>2551</v>
+      </c>
+      <c r="D338" s="6" t="s">
+        <v>2552</v>
+      </c>
+      <c r="E338" s="6" t="s">
+        <v>2553</v>
+      </c>
+      <c r="F338" s="6" t="s">
+        <v>2554</v>
+      </c>
+      <c r="H338" s="9" t="s">
+        <v>2555</v>
+      </c>
+      <c r="I338" t="s">
+        <v>2556</v>
+      </c>
+      <c r="J338" t="s">
+        <v>2423</v>
+      </c>
+      <c r="K338" t="s">
+        <v>2294</v>
+      </c>
+    </row>
+    <row r="339" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A339" t="s">
+        <v>2652</v>
+      </c>
+      <c r="B339" t="s">
+        <v>2557</v>
+      </c>
+      <c r="C339" t="s">
+        <v>2558</v>
+      </c>
+      <c r="D339" s="6" t="s">
+        <v>2559</v>
+      </c>
+      <c r="E339" s="6" t="s">
+        <v>2560</v>
+      </c>
+      <c r="F339" s="6" t="s">
+        <v>2561</v>
+      </c>
+      <c r="H339" s="9" t="s">
+        <v>2562</v>
+      </c>
+      <c r="I339" t="s">
+        <v>2563</v>
+      </c>
+      <c r="J339" t="s">
+        <v>2176</v>
+      </c>
+      <c r="K339" t="s">
+        <v>2564</v>
+      </c>
+    </row>
+    <row r="340" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A340" t="s">
+        <v>2653</v>
+      </c>
+      <c r="B340" t="s">
+        <v>2565</v>
+      </c>
+      <c r="C340" t="s">
+        <v>2566</v>
+      </c>
+      <c r="D340" s="6" t="s">
+        <v>2567</v>
+      </c>
+      <c r="E340" s="6" t="s">
+        <v>2568</v>
+      </c>
+      <c r="F340" s="6" t="s">
+        <v>2569</v>
+      </c>
+      <c r="H340" s="9" t="s">
+        <v>2570</v>
+      </c>
+      <c r="I340" t="s">
+        <v>2571</v>
+      </c>
+      <c r="J340" t="s">
+        <v>280</v>
+      </c>
+      <c r="K340" t="s">
+        <v>2131</v>
+      </c>
+    </row>
+    <row r="341" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A341" t="s">
+        <v>2654</v>
+      </c>
+      <c r="B341" t="s">
+        <v>2572</v>
+      </c>
+      <c r="C341" t="s">
+        <v>2573</v>
+      </c>
+      <c r="D341" s="6" t="s">
+        <v>2574</v>
+      </c>
+      <c r="E341" s="6" t="s">
+        <v>2575</v>
+      </c>
+      <c r="F341" s="6" t="s">
+        <v>2576</v>
+      </c>
+      <c r="H341" s="9" t="s">
+        <v>2577</v>
+      </c>
+      <c r="I341" t="s">
+        <v>2578</v>
+      </c>
+      <c r="J341" t="s">
+        <v>284</v>
+      </c>
+      <c r="K341" t="s">
+        <v>2130</v>
+      </c>
+    </row>
+    <row r="342" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A342" t="s">
+        <v>2655</v>
+      </c>
+      <c r="B342" t="s">
+        <v>2579</v>
+      </c>
+      <c r="C342" t="s">
+        <v>2580</v>
+      </c>
+      <c r="D342" s="6" t="s">
+        <v>2581</v>
+      </c>
+      <c r="E342" s="6" t="s">
+        <v>2582</v>
+      </c>
+      <c r="F342" s="6" t="s">
+        <v>2583</v>
+      </c>
+      <c r="H342" s="9" t="s">
+        <v>2584</v>
+      </c>
+      <c r="I342" t="s">
+        <v>2585</v>
+      </c>
+      <c r="J342" t="s">
+        <v>2586</v>
+      </c>
+      <c r="K342" t="s">
+        <v>2587</v>
+      </c>
+    </row>
+    <row r="343" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A343" t="s">
+        <v>2656</v>
+      </c>
+      <c r="B343" t="s">
+        <v>2588</v>
+      </c>
+      <c r="C343" t="s">
+        <v>2589</v>
+      </c>
+      <c r="D343" s="6" t="s">
+        <v>2590</v>
+      </c>
+      <c r="E343" s="6" t="s">
+        <v>2591</v>
+      </c>
+      <c r="F343" s="6" t="s">
+        <v>2592</v>
+      </c>
+      <c r="H343" s="9" t="s">
+        <v>2593</v>
+      </c>
+      <c r="I343" t="s">
+        <v>2594</v>
+      </c>
+      <c r="J343" t="s">
+        <v>280</v>
+      </c>
+      <c r="K343" t="s">
+        <v>2595</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="A1:B1048576">
-    <cfRule type="duplicateValues" dxfId="2" priority="4"/>
+  <conditionalFormatting sqref="C1:C1048576">
+    <cfRule type="duplicateValues" dxfId="2" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I1:I1048576">
     <cfRule type="duplicateValues" dxfId="1" priority="2"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C1:C1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  <conditionalFormatting sqref="A1:B1048576">
+    <cfRule type="duplicateValues" dxfId="0" priority="5"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
